--- a/school_lublino/walls/vor_lublino_walls.xlsx
+++ b/school_lublino/walls/vor_lublino_walls.xlsx
@@ -9,30 +9,32 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="23268" yWindow="5568" windowWidth="5532" windowHeight="6108" tabRatio="800" firstSheet="1" activeTab="12"/>
+    <workbookView xWindow="23268" yWindow="5568" windowWidth="5532" windowHeight="6108" tabRatio="800" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="ВОР 2 э. шт." sheetId="8" state="hidden" r:id="rId1"/>
-    <sheet name="Спец 2 э. шт." sheetId="7" r:id="rId2"/>
-    <sheet name="ВОР 3 э. шт." sheetId="10" state="hidden" r:id="rId3"/>
-    <sheet name="Спец 3 э. шт." sheetId="9" state="hidden" r:id="rId4"/>
-    <sheet name="ВОР 1.2.3 э. шт." sheetId="15" state="hidden" r:id="rId5"/>
-    <sheet name="сп1.2.3эт" sheetId="11" state="hidden" r:id="rId6"/>
-    <sheet name="Лист4" sheetId="14" state="hidden" r:id="rId7"/>
-    <sheet name="Лист2" sheetId="17" r:id="rId8"/>
-    <sheet name="2.1ШпВор" sheetId="16" r:id="rId9"/>
-    <sheet name="2.2)Шп1эт" sheetId="20" r:id="rId10"/>
-    <sheet name="2.3)Шп2эт" sheetId="21" r:id="rId11"/>
-    <sheet name="2.4)Шп3эт" sheetId="22" r:id="rId12"/>
-    <sheet name="3.1ШпФин" sheetId="23" r:id="rId13"/>
-    <sheet name="Лист5" sheetId="19" state="hidden" r:id="rId14"/>
+    <sheet name="1.7ГКЛ" sheetId="25" r:id="rId2"/>
+    <sheet name="2.5Шт5блСпртЗл" sheetId="24" r:id="rId3"/>
+    <sheet name="Спец 2 э. шт." sheetId="7" r:id="rId4"/>
+    <sheet name="ВОР 3 э. шт." sheetId="10" state="hidden" r:id="rId5"/>
+    <sheet name="Спец 3 э. шт." sheetId="9" state="hidden" r:id="rId6"/>
+    <sheet name="ВОР 1.2.3 э. шт." sheetId="15" state="hidden" r:id="rId7"/>
+    <sheet name="сп1.2.3эт" sheetId="11" state="hidden" r:id="rId8"/>
+    <sheet name="Лист4" sheetId="14" state="hidden" r:id="rId9"/>
+    <sheet name="Лист2" sheetId="17" r:id="rId10"/>
+    <sheet name="2.1ШпВор" sheetId="16" r:id="rId11"/>
+    <sheet name="2.2)Шп1эт" sheetId="20" r:id="rId12"/>
+    <sheet name="2.3)Шп2эт" sheetId="21" r:id="rId13"/>
+    <sheet name="2.4)Шп3эт" sheetId="22" r:id="rId14"/>
+    <sheet name="3.1ШпФин" sheetId="23" r:id="rId15"/>
+    <sheet name="Лист5" sheetId="19" state="hidden" r:id="rId16"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="204">
   <si>
     <t>№ п.п.</t>
   </si>
@@ -608,6 +610,54 @@
   <si>
     <t>СТ-6
 подготовка под высококачественное окрашивание</t>
+  </si>
+  <si>
+    <t>Штукатурка стен гипсовыми смесями с предварительной огрунтовкой СКБ / толщ. от 21 до 40 мм / высотой от 4,01 до 8 метров</t>
+  </si>
+  <si>
+    <t>АРОР АЙСИБИ/МФ-СТРОЙ. 2 этаж, блок 5, пом. 2.111, 2.112, 2.114, 2.115, 2.116, 2.117, 2.118, 2.166, 2.167. 
+Тип стен: ЧСТ-2.1</t>
+  </si>
+  <si>
+    <t>2.111</t>
+  </si>
+  <si>
+    <t>2.112</t>
+  </si>
+  <si>
+    <t>2.114</t>
+  </si>
+  <si>
+    <t>2.115</t>
+  </si>
+  <si>
+    <t>2.116</t>
+  </si>
+  <si>
+    <t>2.117</t>
+  </si>
+  <si>
+    <t>2.118</t>
+  </si>
+  <si>
+    <t>2.166</t>
+  </si>
+  <si>
+    <t>2.167</t>
+  </si>
+  <si>
+    <t>ЧСТ-2.1</t>
+  </si>
+  <si>
+    <t>Облицовка стен по системе Knauf / С-626 / в 2 слоя / А-6, А-9</t>
+  </si>
+  <si>
+    <t>Блок 1, блок 4.1
+1 ,2, 3 этаж
+Обшивка стояков и коллекторов</t>
+  </si>
+  <si>
+    <t>Этаж</t>
   </si>
 </sst>
 </file>
@@ -1068,7 +1118,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="172">
+  <cellXfs count="174">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1431,67 +1481,37 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="9" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="14" fillId="12" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1507,12 +1527,44 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2298,6 +2350,3050 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
+    <tabColor theme="2" tint="-9.9978637043366805E-2"/>
+  </sheetPr>
+  <dimension ref="A1:AD93"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="9.109375" style="78"/>
+    <col min="3" max="3" width="11.5546875" style="78" customWidth="1"/>
+    <col min="4" max="7" width="10.5546875" style="78" customWidth="1"/>
+    <col min="8" max="16384" width="9.109375" style="78"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A1" s="170" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="170"/>
+      <c r="C1" s="170"/>
+      <c r="D1" s="170"/>
+      <c r="E1" s="170"/>
+      <c r="F1" s="170"/>
+      <c r="G1" s="170"/>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="95" t="s">
+        <v>150</v>
+      </c>
+      <c r="E2" s="96" t="s">
+        <v>152</v>
+      </c>
+      <c r="F2" s="96" t="s">
+        <v>153</v>
+      </c>
+      <c r="G2" s="80" t="s">
+        <v>3</v>
+      </c>
+      <c r="S2" s="105"/>
+      <c r="T2" s="105"/>
+      <c r="U2" s="105" t="s">
+        <v>172</v>
+      </c>
+      <c r="V2" s="105"/>
+      <c r="W2" s="105"/>
+      <c r="Y2" s="108" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z2" s="108"/>
+      <c r="AA2" s="108"/>
+      <c r="AC2" s="78" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A3" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="79" t="s">
+        <v>154</v>
+      </c>
+      <c r="C3" s="97" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="98" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="98" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="98" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="99" t="s">
+        <v>4</v>
+      </c>
+      <c r="S3" s="106"/>
+      <c r="T3" s="106"/>
+      <c r="U3" s="106">
+        <v>1</v>
+      </c>
+      <c r="V3" s="106">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="W3" s="106" t="s">
+        <v>165</v>
+      </c>
+      <c r="Y3" s="109">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="109">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="AA3" s="109" t="s">
+        <v>165</v>
+      </c>
+      <c r="AC3" s="78" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A4" s="79">
+        <v>1</v>
+      </c>
+      <c r="B4" s="79">
+        <v>1</v>
+      </c>
+      <c r="C4" s="119">
+        <v>1.028</v>
+      </c>
+      <c r="D4" s="100">
+        <f>VLOOKUP($C4,Лист5!$A$1:$B$104,2,)+15</f>
+        <v>118.27</v>
+      </c>
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="99">
+        <f>SUM(D4:F4)</f>
+        <v>118.27</v>
+      </c>
+      <c r="S4" s="106" t="s">
+        <v>161</v>
+      </c>
+      <c r="T4" s="106" t="s">
+        <v>156</v>
+      </c>
+      <c r="U4" s="107">
+        <v>1469.99</v>
+      </c>
+      <c r="V4" s="106">
+        <v>1225.93</v>
+      </c>
+      <c r="W4" s="107">
+        <f>SUM(U4:V4)</f>
+        <v>2695.92</v>
+      </c>
+      <c r="Y4" s="109">
+        <v>1469.31</v>
+      </c>
+      <c r="Z4" s="109">
+        <v>1224.44</v>
+      </c>
+      <c r="AA4" s="110">
+        <f>SUM(Y4:Z4)</f>
+        <v>2693.75</v>
+      </c>
+      <c r="AC4" s="101">
+        <f>W4-AA4</f>
+        <v>2.1700000000000728</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A5" s="79">
+        <v>2</v>
+      </c>
+      <c r="B5" s="79">
+        <v>1</v>
+      </c>
+      <c r="C5" s="119">
+        <v>1.0269999999999999</v>
+      </c>
+      <c r="D5" s="100">
+        <f>VLOOKUP($C5,Лист5!$A$1:$B$104,2,)+15</f>
+        <v>125.55</v>
+      </c>
+      <c r="E5" s="99"/>
+      <c r="F5" s="99"/>
+      <c r="G5" s="99">
+        <f t="shared" ref="G5:G24" si="0">SUM(D5:F5)</f>
+        <v>125.55</v>
+      </c>
+      <c r="S5" s="111"/>
+      <c r="T5" s="111" t="s">
+        <v>157</v>
+      </c>
+      <c r="U5" s="111" t="s">
+        <v>164</v>
+      </c>
+      <c r="V5" s="111">
+        <v>378.74</v>
+      </c>
+      <c r="W5" s="112">
+        <f t="shared" ref="W5:W23" si="1">SUM(U5:V5)</f>
+        <v>378.74</v>
+      </c>
+      <c r="X5" s="113"/>
+      <c r="Y5" s="111" t="s">
+        <v>164</v>
+      </c>
+      <c r="Z5" s="111">
+        <v>348.14</v>
+      </c>
+      <c r="AA5" s="112">
+        <f t="shared" ref="AA5:AA21" si="2">SUM(Y5:Z5)</f>
+        <v>348.14</v>
+      </c>
+      <c r="AB5" s="113"/>
+      <c r="AC5" s="114">
+        <f t="shared" ref="AC5:AC21" si="3">W5-AA5</f>
+        <v>30.600000000000023</v>
+      </c>
+      <c r="AD5" s="113"/>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A6" s="79">
+        <v>3</v>
+      </c>
+      <c r="B6" s="79">
+        <v>1</v>
+      </c>
+      <c r="C6" s="119">
+        <v>1.026</v>
+      </c>
+      <c r="D6" s="100">
+        <f>284.86+35</f>
+        <v>319.86</v>
+      </c>
+      <c r="E6" s="99"/>
+      <c r="F6" s="99"/>
+      <c r="G6" s="99">
+        <f t="shared" si="0"/>
+        <v>319.86</v>
+      </c>
+      <c r="S6" s="106"/>
+      <c r="T6" s="106" t="s">
+        <v>158</v>
+      </c>
+      <c r="U6" s="106" t="s">
+        <v>164</v>
+      </c>
+      <c r="V6" s="106" t="s">
+        <v>164</v>
+      </c>
+      <c r="W6" s="107">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y6" s="109">
+        <v>57.81</v>
+      </c>
+      <c r="Z6" s="109">
+        <v>5.85</v>
+      </c>
+      <c r="AA6" s="110">
+        <f t="shared" si="2"/>
+        <v>63.660000000000004</v>
+      </c>
+      <c r="AC6" s="101">
+        <f t="shared" si="3"/>
+        <v>-63.660000000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A7" s="135">
+        <v>4</v>
+      </c>
+      <c r="B7" s="135">
+        <v>1</v>
+      </c>
+      <c r="C7" s="136">
+        <v>1.024</v>
+      </c>
+      <c r="D7" s="137">
+        <f>53.84</f>
+        <v>53.84</v>
+      </c>
+      <c r="E7" s="137"/>
+      <c r="F7" s="137"/>
+      <c r="G7" s="137">
+        <f t="shared" si="0"/>
+        <v>53.84</v>
+      </c>
+      <c r="S7" s="111"/>
+      <c r="T7" s="111" t="s">
+        <v>159</v>
+      </c>
+      <c r="U7" s="112">
+        <v>13.59</v>
+      </c>
+      <c r="V7" s="111">
+        <v>1.8</v>
+      </c>
+      <c r="W7" s="112">
+        <f t="shared" si="1"/>
+        <v>15.39</v>
+      </c>
+      <c r="X7" s="113"/>
+      <c r="Y7" s="111" t="s">
+        <v>164</v>
+      </c>
+      <c r="Z7" s="111" t="s">
+        <v>164</v>
+      </c>
+      <c r="AA7" s="112">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AB7" s="113"/>
+      <c r="AC7" s="114">
+        <f t="shared" si="3"/>
+        <v>15.39</v>
+      </c>
+      <c r="AD7" s="113"/>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A8" s="79">
+        <v>5</v>
+      </c>
+      <c r="B8" s="79">
+        <v>1</v>
+      </c>
+      <c r="C8" s="119">
+        <v>1.0289999999999999</v>
+      </c>
+      <c r="D8" s="100">
+        <f>VLOOKUP($C8,Лист5!$A$1:$B$104,2,)+10</f>
+        <v>102.42</v>
+      </c>
+      <c r="E8" s="99"/>
+      <c r="F8" s="99"/>
+      <c r="G8" s="99">
+        <f t="shared" si="0"/>
+        <v>102.42</v>
+      </c>
+      <c r="S8" s="106"/>
+      <c r="T8" s="106" t="s">
+        <v>160</v>
+      </c>
+      <c r="U8" s="106">
+        <v>2.4</v>
+      </c>
+      <c r="V8" s="106" t="s">
+        <v>164</v>
+      </c>
+      <c r="W8" s="107">
+        <f t="shared" si="1"/>
+        <v>2.4</v>
+      </c>
+      <c r="Y8" s="109" t="s">
+        <v>164</v>
+      </c>
+      <c r="Z8" s="109" t="s">
+        <v>164</v>
+      </c>
+      <c r="AA8" s="110">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC8" s="101">
+        <f t="shared" si="3"/>
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A9" s="79">
+        <v>6</v>
+      </c>
+      <c r="B9" s="79">
+        <v>1</v>
+      </c>
+      <c r="C9" s="119">
+        <v>1.03</v>
+      </c>
+      <c r="D9" s="100">
+        <f>VLOOKUP($C9,Лист5!$A$1:$B$104,2,)+7</f>
+        <v>101.91</v>
+      </c>
+      <c r="E9" s="99"/>
+      <c r="F9" s="99"/>
+      <c r="G9" s="99">
+        <f t="shared" si="0"/>
+        <v>101.91</v>
+      </c>
+      <c r="S9" s="111"/>
+      <c r="T9" s="111"/>
+      <c r="U9" s="111"/>
+      <c r="V9" s="111"/>
+      <c r="W9" s="112"/>
+      <c r="X9" s="113"/>
+      <c r="Y9" s="111"/>
+      <c r="Z9" s="111"/>
+      <c r="AA9" s="112"/>
+      <c r="AB9" s="113"/>
+      <c r="AC9" s="114"/>
+      <c r="AD9" s="113"/>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A10" s="79">
+        <v>7</v>
+      </c>
+      <c r="B10" s="79">
+        <v>1</v>
+      </c>
+      <c r="C10" s="119">
+        <v>1.0309999999999999</v>
+      </c>
+      <c r="D10" s="100">
+        <f>VLOOKUP($C10,Лист5!$A$1:$B$104,2,)+8</f>
+        <v>98.2</v>
+      </c>
+      <c r="E10" s="99"/>
+      <c r="F10" s="99"/>
+      <c r="G10" s="99">
+        <f t="shared" si="0"/>
+        <v>98.2</v>
+      </c>
+      <c r="S10" s="106" t="s">
+        <v>162</v>
+      </c>
+      <c r="T10" s="106" t="s">
+        <v>156</v>
+      </c>
+      <c r="U10" s="106">
+        <v>1537.74</v>
+      </c>
+      <c r="V10" s="106">
+        <v>1995.77</v>
+      </c>
+      <c r="W10" s="107">
+        <f t="shared" si="1"/>
+        <v>3533.51</v>
+      </c>
+      <c r="Y10" s="109">
+        <v>1537.34</v>
+      </c>
+      <c r="Z10" s="109">
+        <v>1673.16</v>
+      </c>
+      <c r="AA10" s="110">
+        <f t="shared" si="2"/>
+        <v>3210.5</v>
+      </c>
+      <c r="AC10" s="101">
+        <f t="shared" si="3"/>
+        <v>323.01000000000022</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A11" s="79">
+        <v>8</v>
+      </c>
+      <c r="B11" s="79">
+        <v>1</v>
+      </c>
+      <c r="C11" s="119">
+        <v>1.032</v>
+      </c>
+      <c r="D11" s="100">
+        <f>VLOOKUP($C11,Лист5!$A$1:$B$104,2,)+7</f>
+        <v>94.76</v>
+      </c>
+      <c r="E11" s="99"/>
+      <c r="F11" s="99"/>
+      <c r="G11" s="99">
+        <f t="shared" si="0"/>
+        <v>94.76</v>
+      </c>
+      <c r="S11" s="111"/>
+      <c r="T11" s="111" t="s">
+        <v>157</v>
+      </c>
+      <c r="U11" s="111">
+        <v>51.07</v>
+      </c>
+      <c r="V11" s="111">
+        <v>409.01</v>
+      </c>
+      <c r="W11" s="112">
+        <f t="shared" si="1"/>
+        <v>460.08</v>
+      </c>
+      <c r="X11" s="113"/>
+      <c r="Y11" s="111">
+        <v>51.07</v>
+      </c>
+      <c r="Z11" s="111">
+        <v>409.01</v>
+      </c>
+      <c r="AA11" s="112">
+        <f t="shared" si="2"/>
+        <v>460.08</v>
+      </c>
+      <c r="AB11" s="113"/>
+      <c r="AC11" s="114">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AD11" s="113"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A12" s="79">
+        <v>9</v>
+      </c>
+      <c r="B12" s="79">
+        <v>1</v>
+      </c>
+      <c r="C12" s="119">
+        <v>1.0329999999999999</v>
+      </c>
+      <c r="D12" s="100">
+        <f>VLOOKUP($C12,Лист5!$A$1:$B$104,2,)+10</f>
+        <v>152.44</v>
+      </c>
+      <c r="E12" s="99"/>
+      <c r="F12" s="99"/>
+      <c r="G12" s="99">
+        <f t="shared" si="0"/>
+        <v>152.44</v>
+      </c>
+      <c r="S12" s="106"/>
+      <c r="T12" s="106" t="s">
+        <v>158</v>
+      </c>
+      <c r="U12" s="106" t="s">
+        <v>164</v>
+      </c>
+      <c r="V12" s="106" t="s">
+        <v>164</v>
+      </c>
+      <c r="W12" s="107">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="109">
+        <v>60.14</v>
+      </c>
+      <c r="Z12" s="109">
+        <v>338.43</v>
+      </c>
+      <c r="AA12" s="110">
+        <f t="shared" si="2"/>
+        <v>398.57</v>
+      </c>
+      <c r="AC12" s="101">
+        <f t="shared" si="3"/>
+        <v>-398.57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A13" s="79">
+        <v>10</v>
+      </c>
+      <c r="B13" s="79">
+        <v>1</v>
+      </c>
+      <c r="C13" s="119">
+        <v>1.0389999999999999</v>
+      </c>
+      <c r="D13" s="100">
+        <f>VLOOKUP($C13,Лист5!$A$1:$B$104,2,)+15</f>
+        <v>181.2</v>
+      </c>
+      <c r="E13" s="99"/>
+      <c r="F13" s="99"/>
+      <c r="G13" s="99">
+        <f t="shared" si="0"/>
+        <v>181.2</v>
+      </c>
+      <c r="S13" s="111"/>
+      <c r="T13" s="111" t="s">
+        <v>159</v>
+      </c>
+      <c r="U13" s="111">
+        <v>16.09</v>
+      </c>
+      <c r="V13" s="111" t="s">
+        <v>164</v>
+      </c>
+      <c r="W13" s="112">
+        <f t="shared" si="1"/>
+        <v>16.09</v>
+      </c>
+      <c r="X13" s="113"/>
+      <c r="Y13" s="111" t="s">
+        <v>164</v>
+      </c>
+      <c r="Z13" s="111" t="s">
+        <v>164</v>
+      </c>
+      <c r="AA13" s="112">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AB13" s="113"/>
+      <c r="AC13" s="114">
+        <f t="shared" si="3"/>
+        <v>16.09</v>
+      </c>
+      <c r="AD13" s="113"/>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A14" s="79">
+        <v>11</v>
+      </c>
+      <c r="B14" s="79">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C14" s="119">
+        <v>1.04</v>
+      </c>
+      <c r="D14" s="100">
+        <f>164+32.45+20</f>
+        <v>216.45</v>
+      </c>
+      <c r="E14" s="99"/>
+      <c r="F14" s="99"/>
+      <c r="G14" s="99">
+        <f t="shared" si="0"/>
+        <v>216.45</v>
+      </c>
+      <c r="S14" s="106"/>
+      <c r="T14" s="106" t="s">
+        <v>160</v>
+      </c>
+      <c r="U14" s="106">
+        <v>2.4</v>
+      </c>
+      <c r="V14" s="106" t="s">
+        <v>164</v>
+      </c>
+      <c r="W14" s="107">
+        <f t="shared" si="1"/>
+        <v>2.4</v>
+      </c>
+      <c r="Y14" s="109" t="s">
+        <v>164</v>
+      </c>
+      <c r="Z14" s="109" t="s">
+        <v>164</v>
+      </c>
+      <c r="AA14" s="110">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC14" s="101">
+        <f t="shared" si="3"/>
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A15" s="79">
+        <v>12</v>
+      </c>
+      <c r="B15" s="79">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C15" s="119">
+        <v>1.0429999999999999</v>
+      </c>
+      <c r="D15" s="100">
+        <f>18+83.8</f>
+        <v>101.8</v>
+      </c>
+      <c r="E15" s="99"/>
+      <c r="F15" s="99"/>
+      <c r="G15" s="99">
+        <f t="shared" si="0"/>
+        <v>101.8</v>
+      </c>
+      <c r="S15" s="111"/>
+      <c r="T15" s="111"/>
+      <c r="U15" s="111"/>
+      <c r="V15" s="111"/>
+      <c r="W15" s="112"/>
+      <c r="X15" s="113"/>
+      <c r="Y15" s="111"/>
+      <c r="Z15" s="111"/>
+      <c r="AA15" s="112"/>
+      <c r="AB15" s="113"/>
+      <c r="AC15" s="114"/>
+      <c r="AD15" s="113"/>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A16" s="79">
+        <v>13</v>
+      </c>
+      <c r="B16" s="79">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C16" s="119">
+        <v>1.044</v>
+      </c>
+      <c r="D16" s="100">
+        <v>67.3</v>
+      </c>
+      <c r="E16" s="99"/>
+      <c r="F16" s="99"/>
+      <c r="G16" s="99">
+        <f t="shared" si="0"/>
+        <v>67.3</v>
+      </c>
+      <c r="S16" s="111" t="s">
+        <v>163</v>
+      </c>
+      <c r="T16" s="111" t="s">
+        <v>156</v>
+      </c>
+      <c r="U16" s="111">
+        <v>1765.15</v>
+      </c>
+      <c r="V16" s="111">
+        <v>642.66</v>
+      </c>
+      <c r="W16" s="112">
+        <f t="shared" si="1"/>
+        <v>2407.81</v>
+      </c>
+      <c r="X16" s="113"/>
+      <c r="Y16" s="111">
+        <v>1762.76</v>
+      </c>
+      <c r="Z16" s="111">
+        <v>642.66</v>
+      </c>
+      <c r="AA16" s="112">
+        <f t="shared" si="2"/>
+        <v>2405.42</v>
+      </c>
+      <c r="AB16" s="113"/>
+      <c r="AC16" s="114">
+        <f t="shared" si="3"/>
+        <v>2.3899999999998727</v>
+      </c>
+      <c r="AD16" s="113"/>
+    </row>
+    <row r="17" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A17" s="79">
+        <v>14</v>
+      </c>
+      <c r="B17" s="79">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C17" s="119">
+        <v>1.046</v>
+      </c>
+      <c r="D17" s="100">
+        <f>185.78+30</f>
+        <v>215.78</v>
+      </c>
+      <c r="E17" s="99"/>
+      <c r="F17" s="99"/>
+      <c r="G17" s="99">
+        <f t="shared" si="0"/>
+        <v>215.78</v>
+      </c>
+      <c r="J17" s="106" t="s">
+        <v>161</v>
+      </c>
+      <c r="K17" s="106" t="s">
+        <v>156</v>
+      </c>
+      <c r="L17" s="107">
+        <v>1469.99</v>
+      </c>
+      <c r="M17" s="106">
+        <v>1225.93</v>
+      </c>
+      <c r="N17" s="107">
+        <f>SUM(L17:M17)</f>
+        <v>2695.92</v>
+      </c>
+      <c r="S17" s="106"/>
+      <c r="T17" s="106" t="s">
+        <v>166</v>
+      </c>
+      <c r="U17" s="106"/>
+      <c r="V17" s="106">
+        <v>182.74</v>
+      </c>
+      <c r="W17" s="107">
+        <f t="shared" si="1"/>
+        <v>182.74</v>
+      </c>
+      <c r="Y17" s="109"/>
+      <c r="Z17" s="109">
+        <v>182.74</v>
+      </c>
+      <c r="AA17" s="110">
+        <f t="shared" si="2"/>
+        <v>182.74</v>
+      </c>
+      <c r="AC17" s="101">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A18" s="79">
+        <v>15</v>
+      </c>
+      <c r="B18" s="79">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C18" s="119">
+        <v>1.0449999999999999</v>
+      </c>
+      <c r="D18" s="100">
+        <f>372.12-D17+20</f>
+        <v>176.34</v>
+      </c>
+      <c r="E18" s="99"/>
+      <c r="F18" s="99"/>
+      <c r="G18" s="99">
+        <f t="shared" si="0"/>
+        <v>176.34</v>
+      </c>
+      <c r="J18" s="111"/>
+      <c r="K18" s="111" t="s">
+        <v>157</v>
+      </c>
+      <c r="L18" s="111" t="s">
+        <v>164</v>
+      </c>
+      <c r="M18" s="111">
+        <v>378.74</v>
+      </c>
+      <c r="N18" s="112">
+        <f t="shared" ref="N18:N21" si="4">SUM(L18:M18)</f>
+        <v>378.74</v>
+      </c>
+      <c r="S18" s="111"/>
+      <c r="T18" s="111" t="s">
+        <v>157</v>
+      </c>
+      <c r="U18" s="111">
+        <v>49.99</v>
+      </c>
+      <c r="V18" s="111">
+        <v>189.76</v>
+      </c>
+      <c r="W18" s="112">
+        <f t="shared" si="1"/>
+        <v>239.75</v>
+      </c>
+      <c r="X18" s="113"/>
+      <c r="Y18" s="111">
+        <v>51.07</v>
+      </c>
+      <c r="Z18" s="111">
+        <v>193.9</v>
+      </c>
+      <c r="AA18" s="112">
+        <f t="shared" si="2"/>
+        <v>244.97</v>
+      </c>
+      <c r="AB18" s="113"/>
+      <c r="AC18" s="114">
+        <f t="shared" si="3"/>
+        <v>-5.2199999999999989</v>
+      </c>
+      <c r="AD18" s="113"/>
+    </row>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A19" s="79">
+        <v>16</v>
+      </c>
+      <c r="B19" s="79">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C19" s="119">
+        <v>1.0489999999999999</v>
+      </c>
+      <c r="D19" s="100">
+        <f>VLOOKUP($C19,Лист5!$A$1:$B$104,2,)+15</f>
+        <v>167.54</v>
+      </c>
+      <c r="E19" s="99"/>
+      <c r="F19" s="99"/>
+      <c r="G19" s="99">
+        <f t="shared" si="0"/>
+        <v>167.54</v>
+      </c>
+      <c r="J19" s="106"/>
+      <c r="K19" s="106" t="s">
+        <v>158</v>
+      </c>
+      <c r="L19" s="106" t="s">
+        <v>164</v>
+      </c>
+      <c r="M19" s="106" t="s">
+        <v>164</v>
+      </c>
+      <c r="N19" s="107">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="106"/>
+      <c r="T19" s="106" t="s">
+        <v>158</v>
+      </c>
+      <c r="U19" s="106" t="s">
+        <v>164</v>
+      </c>
+      <c r="V19" s="106" t="s">
+        <v>164</v>
+      </c>
+      <c r="W19" s="107">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="109">
+        <v>60.25</v>
+      </c>
+      <c r="Z19" s="109" t="s">
+        <v>164</v>
+      </c>
+      <c r="AA19" s="110">
+        <f t="shared" si="2"/>
+        <v>60.25</v>
+      </c>
+      <c r="AC19" s="101">
+        <f t="shared" si="3"/>
+        <v>-60.25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A20" s="79">
+        <v>17</v>
+      </c>
+      <c r="B20" s="79">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C20" s="119">
+        <v>1.05</v>
+      </c>
+      <c r="D20" s="100">
+        <f>VLOOKUP($C20,Лист5!$A$1:$B$104,2,)+3</f>
+        <v>88.4</v>
+      </c>
+      <c r="E20" s="99"/>
+      <c r="F20" s="99"/>
+      <c r="G20" s="99">
+        <f t="shared" si="0"/>
+        <v>88.4</v>
+      </c>
+      <c r="J20" s="111"/>
+      <c r="K20" s="111" t="s">
+        <v>159</v>
+      </c>
+      <c r="L20" s="112">
+        <v>13.59</v>
+      </c>
+      <c r="M20" s="111">
+        <v>1.8</v>
+      </c>
+      <c r="N20" s="112">
+        <f t="shared" si="4"/>
+        <v>15.39</v>
+      </c>
+      <c r="S20" s="111"/>
+      <c r="T20" s="111" t="s">
+        <v>159</v>
+      </c>
+      <c r="U20" s="111">
+        <v>17.940000000000001</v>
+      </c>
+      <c r="V20" s="111"/>
+      <c r="W20" s="112">
+        <f t="shared" si="1"/>
+        <v>17.940000000000001</v>
+      </c>
+      <c r="X20" s="113"/>
+      <c r="Y20" s="111" t="s">
+        <v>164</v>
+      </c>
+      <c r="Z20" s="111" t="s">
+        <v>164</v>
+      </c>
+      <c r="AA20" s="112">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AB20" s="113"/>
+      <c r="AC20" s="114">
+        <f t="shared" si="3"/>
+        <v>17.940000000000001</v>
+      </c>
+      <c r="AD20" s="113"/>
+    </row>
+    <row r="21" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A21" s="79">
+        <v>18</v>
+      </c>
+      <c r="B21" s="79">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C21" s="119">
+        <v>1.0509999999999999</v>
+      </c>
+      <c r="D21" s="100">
+        <f>VLOOKUP($C21,Лист5!$A$1:$B$104,2,)+3</f>
+        <v>91.85</v>
+      </c>
+      <c r="E21" s="99"/>
+      <c r="F21" s="99"/>
+      <c r="G21" s="99">
+        <f t="shared" si="0"/>
+        <v>91.85</v>
+      </c>
+      <c r="J21" s="106"/>
+      <c r="K21" s="106" t="s">
+        <v>160</v>
+      </c>
+      <c r="L21" s="106">
+        <v>2.4</v>
+      </c>
+      <c r="M21" s="106" t="s">
+        <v>164</v>
+      </c>
+      <c r="N21" s="107">
+        <f t="shared" si="4"/>
+        <v>2.4</v>
+      </c>
+      <c r="S21" s="106"/>
+      <c r="T21" s="106" t="s">
+        <v>160</v>
+      </c>
+      <c r="U21" s="106">
+        <v>3.6</v>
+      </c>
+      <c r="V21" s="106"/>
+      <c r="W21" s="107">
+        <f t="shared" si="1"/>
+        <v>3.6</v>
+      </c>
+      <c r="Y21" s="109" t="s">
+        <v>164</v>
+      </c>
+      <c r="Z21" s="109" t="s">
+        <v>164</v>
+      </c>
+      <c r="AA21" s="110">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC21" s="101">
+        <f t="shared" si="3"/>
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A22" s="79">
+        <v>19</v>
+      </c>
+      <c r="B22" s="79">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C22" s="119">
+        <v>1.048</v>
+      </c>
+      <c r="D22" s="99"/>
+      <c r="E22" s="100">
+        <f>VLOOKUP($C22,Лист5!$A$1:$B$104,2,)</f>
+        <v>75.8</v>
+      </c>
+      <c r="F22" s="99"/>
+      <c r="G22" s="99">
+        <f t="shared" si="0"/>
+        <v>75.8</v>
+      </c>
+      <c r="S22" s="113"/>
+      <c r="T22" s="113"/>
+      <c r="U22" s="113"/>
+      <c r="V22" s="113"/>
+      <c r="W22" s="113"/>
+      <c r="X22" s="113"/>
+      <c r="Y22" s="113"/>
+      <c r="Z22" s="113"/>
+      <c r="AA22" s="113"/>
+      <c r="AB22" s="113"/>
+      <c r="AC22" s="113"/>
+      <c r="AD22" s="113"/>
+    </row>
+    <row r="23" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A23" s="79">
+        <v>20</v>
+      </c>
+      <c r="B23" s="79">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C23" s="119">
+        <v>1.0529999999999999</v>
+      </c>
+      <c r="D23" s="99"/>
+      <c r="E23" s="100">
+        <v>254.19</v>
+      </c>
+      <c r="F23" s="99"/>
+      <c r="G23" s="99">
+        <f t="shared" si="0"/>
+        <v>254.19</v>
+      </c>
+      <c r="S23" s="105"/>
+      <c r="T23" s="106" t="s">
+        <v>165</v>
+      </c>
+      <c r="U23" s="107">
+        <f>SUM(U4:U21)</f>
+        <v>4929.96</v>
+      </c>
+      <c r="V23" s="107">
+        <f>SUM(V4:V21)</f>
+        <v>5026.41</v>
+      </c>
+      <c r="W23" s="107">
+        <f t="shared" si="1"/>
+        <v>9956.369999999999</v>
+      </c>
+      <c r="Y23" s="110">
+        <f>SUM(Y4:Y21)</f>
+        <v>5049.75</v>
+      </c>
+      <c r="Z23" s="110">
+        <f>SUM(Z4:Z21)</f>
+        <v>5018.33</v>
+      </c>
+      <c r="AA23" s="110">
+        <f t="shared" ref="AA23" si="5">SUM(Y23:Z23)</f>
+        <v>10068.08</v>
+      </c>
+      <c r="AC23" s="101">
+        <f>W23-AA23</f>
+        <v>-111.71000000000095</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A24" s="79">
+        <v>21</v>
+      </c>
+      <c r="B24" s="79">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C24" s="119">
+        <v>1.054</v>
+      </c>
+      <c r="D24" s="99"/>
+      <c r="E24" s="100">
+        <f>26+8+8.48</f>
+        <v>42.480000000000004</v>
+      </c>
+      <c r="F24" s="99"/>
+      <c r="G24" s="99">
+        <f t="shared" si="0"/>
+        <v>42.480000000000004</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A25" s="79"/>
+      <c r="B25" s="79"/>
+      <c r="C25" s="79" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="99">
+        <f>SUM(D4:D24)</f>
+        <v>2473.91</v>
+      </c>
+      <c r="E25" s="99">
+        <f>SUM(E4:E24)</f>
+        <v>372.47</v>
+      </c>
+      <c r="F25" s="99">
+        <f t="shared" ref="F25:G25" si="6">SUM(F4:F24)</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="99">
+        <f t="shared" si="6"/>
+        <v>2846.38</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="B28" s="93" t="s">
+        <v>154</v>
+      </c>
+      <c r="C28" s="130"/>
+      <c r="D28" s="95" t="s">
+        <v>150</v>
+      </c>
+      <c r="E28" s="96" t="s">
+        <v>152</v>
+      </c>
+      <c r="F28" s="96" t="s">
+        <v>153</v>
+      </c>
+      <c r="J28" s="132" t="s">
+        <v>154</v>
+      </c>
+      <c r="K28" s="130"/>
+      <c r="L28" s="95" t="s">
+        <v>150</v>
+      </c>
+      <c r="M28" s="96" t="s">
+        <v>152</v>
+      </c>
+      <c r="N28" s="96" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="B29" s="130">
+        <v>1</v>
+      </c>
+      <c r="C29" s="130"/>
+      <c r="D29" s="131">
+        <f>SUM(D4:D13)</f>
+        <v>1348.45</v>
+      </c>
+      <c r="E29" s="131">
+        <v>0</v>
+      </c>
+      <c r="F29" s="131">
+        <f>F22</f>
+        <v>0</v>
+      </c>
+      <c r="J29" s="130">
+        <v>1</v>
+      </c>
+      <c r="K29" s="130"/>
+      <c r="L29" s="131">
+        <f>L17</f>
+        <v>1469.99</v>
+      </c>
+      <c r="M29" s="131" t="str">
+        <f>L18</f>
+        <v>-</v>
+      </c>
+      <c r="N29" s="131">
+        <f>N22</f>
+        <v>0</v>
+      </c>
+      <c r="P29" s="101">
+        <f>L29-D29</f>
+        <v>121.53999999999996</v>
+      </c>
+      <c r="Q29" s="101" t="e">
+        <f>M29-E29</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="B30" s="130">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C30" s="130"/>
+      <c r="D30" s="131">
+        <f>SUM(D14:D21)</f>
+        <v>1125.46</v>
+      </c>
+      <c r="E30" s="131">
+        <f>SUM(E22:E24)</f>
+        <v>372.47</v>
+      </c>
+      <c r="F30" s="131">
+        <f>SUM(F23:F25)</f>
+        <v>0</v>
+      </c>
+      <c r="J30" s="130">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="K30" s="130"/>
+      <c r="L30" s="131">
+        <f>M17</f>
+        <v>1225.93</v>
+      </c>
+      <c r="M30" s="131">
+        <f>M18</f>
+        <v>378.74</v>
+      </c>
+      <c r="N30" s="131">
+        <f>SUM(N23:N25)</f>
+        <v>0</v>
+      </c>
+      <c r="P30" s="101">
+        <f>L30-D30</f>
+        <v>100.47000000000003</v>
+      </c>
+      <c r="Q30" s="101">
+        <f>M30-E30</f>
+        <v>6.2699999999999818</v>
+      </c>
+    </row>
+    <row r="32" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A32" s="170" t="s">
+        <v>2</v>
+      </c>
+      <c r="B32" s="170"/>
+      <c r="C32" s="170"/>
+      <c r="D32" s="170"/>
+      <c r="E32" s="170"/>
+      <c r="F32" s="170"/>
+      <c r="G32" s="170"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="79"/>
+      <c r="B33" s="79"/>
+      <c r="C33" s="94"/>
+      <c r="D33" s="95" t="s">
+        <v>150</v>
+      </c>
+      <c r="E33" s="96" t="s">
+        <v>152</v>
+      </c>
+      <c r="F33" s="96" t="s">
+        <v>153</v>
+      </c>
+      <c r="G33" s="80" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="B34" s="79" t="s">
+        <v>154</v>
+      </c>
+      <c r="C34" s="97" t="s">
+        <v>5</v>
+      </c>
+      <c r="D34" s="98" t="s">
+        <v>4</v>
+      </c>
+      <c r="E34" s="98" t="s">
+        <v>4</v>
+      </c>
+      <c r="F34" s="98" t="s">
+        <v>4</v>
+      </c>
+      <c r="G34" s="99" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="79">
+        <v>1</v>
+      </c>
+      <c r="B35" s="102">
+        <v>1</v>
+      </c>
+      <c r="C35" s="104">
+        <v>2.0009999999999999</v>
+      </c>
+      <c r="D35" s="100">
+        <f>VLOOKUP($C35,Лист5!$A$1:$B$104,2,)</f>
+        <v>118.17750000000001</v>
+      </c>
+      <c r="E35" s="103"/>
+      <c r="F35" s="103"/>
+      <c r="G35" s="99">
+        <f>SUM(D35:F35)</f>
+        <v>118.17750000000001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" s="79">
+        <v>2</v>
+      </c>
+      <c r="B36" s="102">
+        <v>1</v>
+      </c>
+      <c r="C36" s="104">
+        <v>2.0019999999999998</v>
+      </c>
+      <c r="D36" s="100">
+        <f>VLOOKUP($C36,Лист5!$A$1:$B$104,2,)</f>
+        <v>113.73599999999999</v>
+      </c>
+      <c r="E36" s="103"/>
+      <c r="F36" s="103"/>
+      <c r="G36" s="99">
+        <f t="shared" ref="G36:G57" si="7">SUM(D36:F36)</f>
+        <v>113.73599999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="79">
+        <v>3</v>
+      </c>
+      <c r="B37" s="102">
+        <v>1</v>
+      </c>
+      <c r="C37" s="104">
+        <v>2.0030000000000001</v>
+      </c>
+      <c r="D37" s="100">
+        <f>VLOOKUP($C37,Лист5!$A$1:$B$104,2,)</f>
+        <v>122.50349999999997</v>
+      </c>
+      <c r="E37" s="103"/>
+      <c r="F37" s="103"/>
+      <c r="G37" s="99">
+        <f t="shared" si="7"/>
+        <v>122.50349999999997</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="79">
+        <v>4</v>
+      </c>
+      <c r="B38" s="102">
+        <v>1</v>
+      </c>
+      <c r="C38" s="104">
+        <v>2.004</v>
+      </c>
+      <c r="D38" s="100">
+        <f>VLOOKUP($C38,Лист5!$A$1:$B$104,2,)</f>
+        <v>314.601</v>
+      </c>
+      <c r="E38" s="103"/>
+      <c r="F38" s="103"/>
+      <c r="G38" s="99">
+        <f t="shared" si="7"/>
+        <v>314.601</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="79">
+        <v>5</v>
+      </c>
+      <c r="B39" s="102">
+        <v>1</v>
+      </c>
+      <c r="C39" s="104">
+        <v>2.0070000000000001</v>
+      </c>
+      <c r="D39" s="100">
+        <f>VLOOKUP($C39,Лист5!$A$1:$B$104,2,)</f>
+        <v>106.77449999999999</v>
+      </c>
+      <c r="E39" s="103"/>
+      <c r="F39" s="103"/>
+      <c r="G39" s="99">
+        <f t="shared" si="7"/>
+        <v>106.77449999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="79">
+        <v>6</v>
+      </c>
+      <c r="B40" s="102">
+        <v>1</v>
+      </c>
+      <c r="C40" s="104">
+        <v>2.008</v>
+      </c>
+      <c r="D40" s="100">
+        <f>VLOOKUP($C40,Лист5!$A$1:$B$104,2,)</f>
+        <v>111.50999999999999</v>
+      </c>
+      <c r="E40" s="103"/>
+      <c r="F40" s="103"/>
+      <c r="G40" s="99">
+        <f t="shared" si="7"/>
+        <v>111.50999999999999</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="79">
+        <v>7</v>
+      </c>
+      <c r="B41" s="102">
+        <v>1</v>
+      </c>
+      <c r="C41" s="104">
+        <v>2.0089999999999999</v>
+      </c>
+      <c r="D41" s="100">
+        <f>VLOOKUP($C41,Лист5!$A$1:$B$104,2,)</f>
+        <v>106.77449999999999</v>
+      </c>
+      <c r="E41" s="103"/>
+      <c r="F41" s="103"/>
+      <c r="G41" s="99">
+        <f t="shared" si="7"/>
+        <v>106.77449999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="79">
+        <v>8</v>
+      </c>
+      <c r="B42" s="102">
+        <v>1</v>
+      </c>
+      <c r="C42" s="115">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="D42" s="100">
+        <f>VLOOKUP($C42,Лист5!$A$1:$B$104,2,)</f>
+        <v>93.03</v>
+      </c>
+      <c r="E42" s="103"/>
+      <c r="F42" s="103"/>
+      <c r="G42" s="99">
+        <f t="shared" si="7"/>
+        <v>93.03</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="79">
+        <v>9</v>
+      </c>
+      <c r="B43" s="102">
+        <v>1</v>
+      </c>
+      <c r="C43" s="104">
+        <v>2.0110000000000001</v>
+      </c>
+      <c r="D43" s="100">
+        <f>VLOOKUP($C43,Лист5!$A$1:$B$104,2,)</f>
+        <v>106.63800000000001</v>
+      </c>
+      <c r="E43" s="103"/>
+      <c r="F43" s="103"/>
+      <c r="G43" s="99">
+        <f t="shared" si="7"/>
+        <v>106.63800000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="79">
+        <v>10</v>
+      </c>
+      <c r="B44" s="102">
+        <v>1</v>
+      </c>
+      <c r="C44" s="104">
+        <v>2.012</v>
+      </c>
+      <c r="D44" s="100">
+        <f>VLOOKUP($C44,Лист5!$A$1:$B$104,2,)</f>
+        <v>234.72750000000002</v>
+      </c>
+      <c r="E44" s="103"/>
+      <c r="F44" s="103"/>
+      <c r="G44" s="99">
+        <f t="shared" si="7"/>
+        <v>234.72750000000002</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" s="79">
+        <v>11</v>
+      </c>
+      <c r="B45" s="102">
+        <v>1</v>
+      </c>
+      <c r="C45" s="104">
+        <v>2.0129999999999999</v>
+      </c>
+      <c r="D45" s="100">
+        <f>VLOOKUP($C45,Лист5!$A$1:$B$104,2,)</f>
+        <v>83.201999999999998</v>
+      </c>
+      <c r="E45" s="103"/>
+      <c r="F45" s="103"/>
+      <c r="G45" s="99">
+        <f t="shared" si="7"/>
+        <v>83.201999999999998</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="79">
+        <v>12</v>
+      </c>
+      <c r="B46" s="102">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C46" s="104">
+        <v>2.0750000000000002</v>
+      </c>
+      <c r="D46" s="100">
+        <f>VLOOKUP($C46,Лист5!$A$1:$B$104,2,)+19</f>
+        <v>303.05650000000003</v>
+      </c>
+      <c r="E46" s="103"/>
+      <c r="F46" s="103"/>
+      <c r="G46" s="99">
+        <f t="shared" si="7"/>
+        <v>303.05650000000003</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" s="79">
+        <v>13</v>
+      </c>
+      <c r="B47" s="102">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C47" s="115">
+        <v>2.08</v>
+      </c>
+      <c r="D47" s="100">
+        <f>447.447/2+20</f>
+        <v>243.7235</v>
+      </c>
+      <c r="E47" s="103"/>
+      <c r="F47" s="103"/>
+      <c r="G47" s="99">
+        <f t="shared" si="7"/>
+        <v>243.7235</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" s="79">
+        <v>14</v>
+      </c>
+      <c r="B48" s="102">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C48" s="104">
+        <v>2.081</v>
+      </c>
+      <c r="D48" s="100">
+        <f>VLOOKUP($C48,Лист5!$A$1:$B$104,2,)+210</f>
+        <v>637.24</v>
+      </c>
+      <c r="E48" s="103"/>
+      <c r="F48" s="103"/>
+      <c r="G48" s="99">
+        <f t="shared" si="7"/>
+        <v>637.24</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A49" s="79">
+        <v>15</v>
+      </c>
+      <c r="B49" s="102">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C49" s="104">
+        <v>2.0819999999999999</v>
+      </c>
+      <c r="D49" s="100">
+        <f>447.447/2-30</f>
+        <v>193.7235</v>
+      </c>
+      <c r="E49" s="103"/>
+      <c r="F49" s="103"/>
+      <c r="G49" s="99">
+        <f t="shared" si="7"/>
+        <v>193.7235</v>
+      </c>
+      <c r="J49" s="106" t="s">
+        <v>162</v>
+      </c>
+      <c r="K49" s="106" t="s">
+        <v>156</v>
+      </c>
+      <c r="L49" s="106">
+        <v>1537.74</v>
+      </c>
+      <c r="M49" s="106">
+        <v>1995.77</v>
+      </c>
+      <c r="N49" s="107">
+        <f>SUM(L49:M49)</f>
+        <v>3533.51</v>
+      </c>
+      <c r="P49" s="109">
+        <v>1537.34</v>
+      </c>
+      <c r="Q49" s="109">
+        <v>1673.16</v>
+      </c>
+      <c r="R49" s="110">
+        <f t="shared" ref="R49:R53" si="8">SUM(P49:Q49)</f>
+        <v>3210.5</v>
+      </c>
+      <c r="T49" s="101">
+        <f>N49-R49</f>
+        <v>323.01000000000022</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A50" s="79">
+        <v>16</v>
+      </c>
+      <c r="B50" s="102">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C50" s="104">
+        <v>2.085</v>
+      </c>
+      <c r="D50" s="100">
+        <f>VLOOKUP($C50,Лист5!$A$1:$B$104,2,)+160</f>
+        <v>479.92</v>
+      </c>
+      <c r="E50" s="103"/>
+      <c r="F50" s="103"/>
+      <c r="G50" s="99">
+        <f t="shared" si="7"/>
+        <v>479.92</v>
+      </c>
+      <c r="J50" s="111"/>
+      <c r="K50" s="111" t="s">
+        <v>157</v>
+      </c>
+      <c r="L50" s="111">
+        <v>51.07</v>
+      </c>
+      <c r="M50" s="111">
+        <v>409.01</v>
+      </c>
+      <c r="N50" s="112">
+        <f>SUM(L50:M50)</f>
+        <v>460.08</v>
+      </c>
+      <c r="O50" s="113"/>
+      <c r="P50" s="111">
+        <v>51.07</v>
+      </c>
+      <c r="Q50" s="111">
+        <v>409.01</v>
+      </c>
+      <c r="R50" s="112">
+        <f t="shared" si="8"/>
+        <v>460.08</v>
+      </c>
+      <c r="S50" s="113"/>
+      <c r="T50" s="114">
+        <f>N50-R50</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A51" s="79">
+        <v>17</v>
+      </c>
+      <c r="B51" s="102">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C51" s="104">
+        <v>2.0880000000000001</v>
+      </c>
+      <c r="D51" s="100">
+        <f>VLOOKUP($C51,Лист5!$A$1:$B$104,2,)+8</f>
+        <v>61.171999999999997</v>
+      </c>
+      <c r="E51" s="103"/>
+      <c r="F51" s="103"/>
+      <c r="G51" s="99">
+        <f t="shared" si="7"/>
+        <v>61.171999999999997</v>
+      </c>
+      <c r="J51" s="106"/>
+      <c r="K51" s="106" t="s">
+        <v>158</v>
+      </c>
+      <c r="L51" s="106" t="s">
+        <v>164</v>
+      </c>
+      <c r="M51" s="106" t="s">
+        <v>164</v>
+      </c>
+      <c r="N51" s="107">
+        <f>SUM(L51:M51)</f>
+        <v>0</v>
+      </c>
+      <c r="P51" s="109">
+        <v>60.14</v>
+      </c>
+      <c r="Q51" s="109">
+        <v>338.43</v>
+      </c>
+      <c r="R51" s="110">
+        <f t="shared" si="8"/>
+        <v>398.57</v>
+      </c>
+      <c r="T51" s="101">
+        <f>N51-R51</f>
+        <v>-398.57</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A52" s="135">
+        <v>18</v>
+      </c>
+      <c r="B52" s="135">
+        <v>1</v>
+      </c>
+      <c r="C52" s="136">
+        <v>2.0049999999999999</v>
+      </c>
+      <c r="D52" s="137"/>
+      <c r="E52" s="137">
+        <v>48.22</v>
+      </c>
+      <c r="F52" s="137"/>
+      <c r="G52" s="137">
+        <f t="shared" si="7"/>
+        <v>48.22</v>
+      </c>
+      <c r="J52" s="111"/>
+      <c r="K52" s="111" t="s">
+        <v>159</v>
+      </c>
+      <c r="L52" s="111">
+        <v>16.09</v>
+      </c>
+      <c r="M52" s="111" t="s">
+        <v>164</v>
+      </c>
+      <c r="N52" s="112">
+        <f>SUM(L52:M52)</f>
+        <v>16.09</v>
+      </c>
+      <c r="O52" s="113"/>
+      <c r="P52" s="111" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q52" s="111" t="s">
+        <v>164</v>
+      </c>
+      <c r="R52" s="112">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S52" s="113"/>
+      <c r="T52" s="114">
+        <f>N52-R52</f>
+        <v>16.09</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A53" s="79">
+        <v>19</v>
+      </c>
+      <c r="B53" s="102">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C53" s="115">
+        <v>2.0840000000000001</v>
+      </c>
+      <c r="D53" s="117"/>
+      <c r="E53" s="100">
+        <f>VLOOKUP($C53,Лист5!$A$1:$B$104,2,)</f>
+        <v>77.849999999999994</v>
+      </c>
+      <c r="F53" s="103"/>
+      <c r="G53" s="99">
+        <f t="shared" si="7"/>
+        <v>77.849999999999994</v>
+      </c>
+      <c r="J53" s="106"/>
+      <c r="K53" s="106" t="s">
+        <v>160</v>
+      </c>
+      <c r="L53" s="106">
+        <v>2.4</v>
+      </c>
+      <c r="M53" s="106" t="s">
+        <v>164</v>
+      </c>
+      <c r="N53" s="107">
+        <f>SUM(L53:M53)</f>
+        <v>2.4</v>
+      </c>
+      <c r="P53" s="109" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q53" s="109" t="s">
+        <v>164</v>
+      </c>
+      <c r="R53" s="110">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T53" s="101">
+        <f>N53-R53</f>
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A54" s="79">
+        <v>20</v>
+      </c>
+      <c r="B54" s="102">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C54" s="115">
+        <v>2.0870000000000002</v>
+      </c>
+      <c r="D54" s="117"/>
+      <c r="E54" s="100">
+        <f>VLOOKUP($C54,Лист5!$A$1:$B$104,2,)</f>
+        <v>83.33</v>
+      </c>
+      <c r="F54" s="103"/>
+      <c r="G54" s="99">
+        <f t="shared" si="7"/>
+        <v>83.33</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A55" s="79">
+        <v>21</v>
+      </c>
+      <c r="B55" s="102">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C55" s="115">
+        <v>2.109</v>
+      </c>
+      <c r="D55" s="117"/>
+      <c r="E55" s="100">
+        <f>VLOOKUP($C55,Лист5!$A$1:$B$104,2,)</f>
+        <v>105.714</v>
+      </c>
+      <c r="F55" s="103"/>
+      <c r="G55" s="99">
+        <f t="shared" si="7"/>
+        <v>105.714</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A56" s="135">
+        <v>22</v>
+      </c>
+      <c r="B56" s="135">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C56" s="136">
+        <v>2.16</v>
+      </c>
+      <c r="D56" s="138"/>
+      <c r="E56" s="137">
+        <f>VLOOKUP($C56,Лист5!$A$1:$B$104,2,)</f>
+        <v>78.209999999999994</v>
+      </c>
+      <c r="F56" s="137"/>
+      <c r="G56" s="137">
+        <f t="shared" si="7"/>
+        <v>78.209999999999994</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A57" s="79">
+        <v>23</v>
+      </c>
+      <c r="B57" s="102">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C57" s="115">
+        <v>2.1680000000000001</v>
+      </c>
+      <c r="D57" s="117"/>
+      <c r="E57" s="100">
+        <f>VLOOKUP($C57,Лист5!$A$1:$B$104,2,)</f>
+        <v>42</v>
+      </c>
+      <c r="F57" s="103"/>
+      <c r="G57" s="99">
+        <f t="shared" si="7"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A58" s="79"/>
+      <c r="B58" s="79"/>
+      <c r="C58" s="79" t="s">
+        <v>19</v>
+      </c>
+      <c r="D58" s="99">
+        <f t="shared" ref="D58:E58" si="9">SUM(D35:D57)</f>
+        <v>3430.5099999999998</v>
+      </c>
+      <c r="E58" s="99">
+        <f t="shared" si="9"/>
+        <v>435.32399999999996</v>
+      </c>
+      <c r="F58" s="99">
+        <f>SUM(F35:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="99">
+        <f>SUM(G35:G51)</f>
+        <v>3430.5099999999998</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="B60" s="93" t="s">
+        <v>154</v>
+      </c>
+      <c r="C60" s="130"/>
+      <c r="D60" s="95" t="s">
+        <v>150</v>
+      </c>
+      <c r="E60" s="96" t="s">
+        <v>152</v>
+      </c>
+      <c r="F60" s="96" t="s">
+        <v>153</v>
+      </c>
+      <c r="J60" s="132" t="s">
+        <v>154</v>
+      </c>
+      <c r="K60" s="130"/>
+      <c r="L60" s="95" t="s">
+        <v>150</v>
+      </c>
+      <c r="M60" s="96" t="s">
+        <v>152</v>
+      </c>
+      <c r="N60" s="96" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="B61" s="130">
+        <v>1</v>
+      </c>
+      <c r="C61" s="130"/>
+      <c r="D61" s="131">
+        <f>SUM(D35:D45)</f>
+        <v>1511.6744999999999</v>
+      </c>
+      <c r="E61" s="131">
+        <f>E52</f>
+        <v>48.22</v>
+      </c>
+      <c r="F61" s="131">
+        <f>F54</f>
+        <v>0</v>
+      </c>
+      <c r="J61" s="130">
+        <v>1</v>
+      </c>
+      <c r="K61" s="130"/>
+      <c r="L61" s="131">
+        <f>L49</f>
+        <v>1537.74</v>
+      </c>
+      <c r="M61" s="131">
+        <f>L50</f>
+        <v>51.07</v>
+      </c>
+      <c r="N61" s="131">
+        <f>N54</f>
+        <v>0</v>
+      </c>
+      <c r="P61" s="101">
+        <f>L61-D61</f>
+        <v>26.065500000000156</v>
+      </c>
+      <c r="Q61" s="101">
+        <f>M61-E61</f>
+        <v>2.8500000000000014</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="B62" s="130">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C62" s="130"/>
+      <c r="D62" s="131">
+        <f>SUM(D46:D51)</f>
+        <v>1918.8355000000001</v>
+      </c>
+      <c r="E62" s="131">
+        <f>SUM(E53:E57)</f>
+        <v>387.10399999999998</v>
+      </c>
+      <c r="F62" s="131">
+        <f>SUM(F55:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="J62" s="130">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="K62" s="130"/>
+      <c r="L62" s="131">
+        <f>M49</f>
+        <v>1995.77</v>
+      </c>
+      <c r="M62" s="131">
+        <f>M50</f>
+        <v>409.01</v>
+      </c>
+      <c r="N62" s="131">
+        <f>SUM(N55:N57)</f>
+        <v>0</v>
+      </c>
+      <c r="P62" s="101">
+        <f>L62-D62</f>
+        <v>76.934499999999844</v>
+      </c>
+      <c r="Q62" s="101">
+        <f>M62-E62</f>
+        <v>21.906000000000006</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="D63" s="101"/>
+      <c r="E63" s="101"/>
+      <c r="F63" s="101"/>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="D64" s="101"/>
+      <c r="E64" s="101"/>
+      <c r="F64" s="101"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D65" s="101"/>
+      <c r="E65" s="101"/>
+      <c r="F65" s="101"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D66" s="101"/>
+      <c r="E66" s="101"/>
+      <c r="F66" s="101"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A67" s="170" t="s">
+        <v>2</v>
+      </c>
+      <c r="B67" s="170"/>
+      <c r="C67" s="170"/>
+      <c r="D67" s="170"/>
+      <c r="E67" s="170"/>
+      <c r="F67" s="170"/>
+      <c r="G67" s="170"/>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A68" s="79"/>
+      <c r="B68" s="79"/>
+      <c r="C68" s="94"/>
+      <c r="D68" s="95" t="s">
+        <v>150</v>
+      </c>
+      <c r="E68" s="95" t="s">
+        <v>151</v>
+      </c>
+      <c r="F68" s="96" t="s">
+        <v>152</v>
+      </c>
+      <c r="G68" s="96" t="s">
+        <v>153</v>
+      </c>
+      <c r="H68" s="80" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A69" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="B69" s="79" t="s">
+        <v>154</v>
+      </c>
+      <c r="C69" s="97" t="s">
+        <v>5</v>
+      </c>
+      <c r="D69" s="98" t="s">
+        <v>4</v>
+      </c>
+      <c r="E69" s="98" t="s">
+        <v>4</v>
+      </c>
+      <c r="F69" s="98" t="s">
+        <v>4</v>
+      </c>
+      <c r="G69" s="98" t="s">
+        <v>4</v>
+      </c>
+      <c r="H69" s="99" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A70" s="135">
+        <v>1</v>
+      </c>
+      <c r="B70" s="135">
+        <v>1</v>
+      </c>
+      <c r="C70" s="136">
+        <v>3.0009999999999999</v>
+      </c>
+      <c r="D70" s="137">
+        <f>VLOOKUP($C70,Лист5!$A$1:$B$104,2,)</f>
+        <v>168.78</v>
+      </c>
+      <c r="E70" s="137"/>
+      <c r="F70" s="137"/>
+      <c r="G70" s="137"/>
+      <c r="H70" s="137">
+        <f t="shared" ref="H70:H88" si="10">SUM(D70:G70)</f>
+        <v>168.78</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A71" s="135">
+        <v>2</v>
+      </c>
+      <c r="B71" s="135">
+        <v>1</v>
+      </c>
+      <c r="C71" s="136">
+        <v>3.0019999999999998</v>
+      </c>
+      <c r="D71" s="137">
+        <f>VLOOKUP($C71,Лист5!$A$1:$B$104,2,)</f>
+        <v>105.58</v>
+      </c>
+      <c r="E71" s="137"/>
+      <c r="F71" s="137"/>
+      <c r="G71" s="137"/>
+      <c r="H71" s="137">
+        <f t="shared" si="10"/>
+        <v>105.58</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A72" s="135">
+        <v>3</v>
+      </c>
+      <c r="B72" s="135">
+        <v>1</v>
+      </c>
+      <c r="C72" s="136">
+        <v>3.0030000000000001</v>
+      </c>
+      <c r="D72" s="137">
+        <f>VLOOKUP($C72,Лист5!$A$1:$B$104,2,)</f>
+        <v>105.79</v>
+      </c>
+      <c r="E72" s="137"/>
+      <c r="F72" s="137"/>
+      <c r="G72" s="137"/>
+      <c r="H72" s="137">
+        <f t="shared" si="10"/>
+        <v>105.79</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A73" s="79">
+        <v>4</v>
+      </c>
+      <c r="B73" s="79">
+        <v>1</v>
+      </c>
+      <c r="C73" s="115">
+        <v>3.004</v>
+      </c>
+      <c r="D73" s="100">
+        <f>VLOOKUP($C73,Лист5!$A$1:$B$104,2,)</f>
+        <v>116.51</v>
+      </c>
+      <c r="E73" s="103"/>
+      <c r="F73" s="103"/>
+      <c r="G73" s="103"/>
+      <c r="H73" s="99">
+        <f t="shared" si="10"/>
+        <v>116.51</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A74" s="135">
+        <v>5</v>
+      </c>
+      <c r="B74" s="135">
+        <v>1</v>
+      </c>
+      <c r="C74" s="136">
+        <v>3.0049999999999999</v>
+      </c>
+      <c r="D74" s="137">
+        <f>VLOOKUP($C74,Лист5!$A$1:$B$104,2,)</f>
+        <v>402.53</v>
+      </c>
+      <c r="E74" s="137"/>
+      <c r="F74" s="137"/>
+      <c r="G74" s="137"/>
+      <c r="H74" s="137">
+        <f t="shared" si="10"/>
+        <v>402.53</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A75" s="79">
+        <v>6</v>
+      </c>
+      <c r="B75" s="79">
+        <v>1</v>
+      </c>
+      <c r="C75" s="115">
+        <v>3.008</v>
+      </c>
+      <c r="D75" s="100">
+        <f>VLOOKUP($C75,Лист5!$A$1:$B$104,2,)</f>
+        <v>102.57</v>
+      </c>
+      <c r="E75" s="103"/>
+      <c r="F75" s="103"/>
+      <c r="G75" s="103"/>
+      <c r="H75" s="99">
+        <f t="shared" si="10"/>
+        <v>102.57</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A76" s="79">
+        <v>7</v>
+      </c>
+      <c r="B76" s="79">
+        <v>1</v>
+      </c>
+      <c r="C76" s="115">
+        <v>3.0089999999999999</v>
+      </c>
+      <c r="D76" s="100">
+        <f>VLOOKUP($C76,Лист5!$A$1:$B$104,2,)</f>
+        <v>104.69999999999999</v>
+      </c>
+      <c r="E76" s="103"/>
+      <c r="F76" s="103"/>
+      <c r="G76" s="103"/>
+      <c r="H76" s="99">
+        <f t="shared" si="10"/>
+        <v>104.69999999999999</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A77" s="79">
+        <v>8</v>
+      </c>
+      <c r="B77" s="79">
+        <v>1</v>
+      </c>
+      <c r="C77" s="115">
+        <v>3.01</v>
+      </c>
+      <c r="D77" s="100">
+        <f>VLOOKUP($C77,Лист5!$A$1:$B$104,2,)</f>
+        <v>101.61</v>
+      </c>
+      <c r="E77" s="103"/>
+      <c r="F77" s="103"/>
+      <c r="G77" s="103"/>
+      <c r="H77" s="99">
+        <f t="shared" si="10"/>
+        <v>101.61</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A78" s="79">
+        <v>9</v>
+      </c>
+      <c r="B78" s="79">
+        <v>1</v>
+      </c>
+      <c r="C78" s="115">
+        <v>3.0110000000000001</v>
+      </c>
+      <c r="D78" s="100">
+        <f>VLOOKUP($C78,Лист5!$A$1:$B$104,2,)</f>
+        <v>105.25</v>
+      </c>
+      <c r="E78" s="103"/>
+      <c r="F78" s="103"/>
+      <c r="G78" s="103"/>
+      <c r="H78" s="99">
+        <f t="shared" si="10"/>
+        <v>105.25</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A79" s="79">
+        <v>10</v>
+      </c>
+      <c r="B79" s="79">
+        <v>1</v>
+      </c>
+      <c r="C79" s="115">
+        <v>3.012</v>
+      </c>
+      <c r="D79" s="100">
+        <f>VLOOKUP($C79,Лист5!$A$1:$B$104,2,)</f>
+        <v>105.33</v>
+      </c>
+      <c r="E79" s="103"/>
+      <c r="F79" s="103"/>
+      <c r="G79" s="103"/>
+      <c r="H79" s="99">
+        <f t="shared" si="10"/>
+        <v>105.33</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A80" s="79">
+        <v>11</v>
+      </c>
+      <c r="B80" s="79">
+        <v>1</v>
+      </c>
+      <c r="C80" s="115">
+        <v>3.0129999999999999</v>
+      </c>
+      <c r="D80" s="100">
+        <f>VLOOKUP($C80,Лист5!$A$1:$B$104,2,)</f>
+        <v>101.95</v>
+      </c>
+      <c r="E80" s="103"/>
+      <c r="F80" s="103"/>
+      <c r="G80" s="103"/>
+      <c r="H80" s="99">
+        <f t="shared" si="10"/>
+        <v>101.95</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A81" s="79">
+        <v>12</v>
+      </c>
+      <c r="B81" s="79">
+        <v>1</v>
+      </c>
+      <c r="C81" s="115">
+        <v>3.0139999999999998</v>
+      </c>
+      <c r="D81" s="100">
+        <f>VLOOKUP($C81,Лист5!$A$1:$B$104,2,)</f>
+        <v>221.42</v>
+      </c>
+      <c r="E81" s="103"/>
+      <c r="F81" s="103"/>
+      <c r="G81" s="103"/>
+      <c r="H81" s="99">
+        <f t="shared" si="10"/>
+        <v>221.42</v>
+      </c>
+    </row>
+    <row r="82" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A82" s="79">
+        <v>13</v>
+      </c>
+      <c r="B82" s="102">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C82" s="115">
+        <v>3.0190000000000001</v>
+      </c>
+      <c r="D82" s="100">
+        <f>VLOOKUP($C82,Лист5!$A$1:$B$104,2,)</f>
+        <v>283.38</v>
+      </c>
+      <c r="E82" s="103"/>
+      <c r="F82" s="103"/>
+      <c r="G82" s="103"/>
+      <c r="H82" s="99">
+        <f t="shared" si="10"/>
+        <v>283.38</v>
+      </c>
+      <c r="J82" s="111" t="s">
+        <v>163</v>
+      </c>
+      <c r="K82" s="111" t="s">
+        <v>156</v>
+      </c>
+      <c r="L82" s="111">
+        <v>1765.15</v>
+      </c>
+      <c r="M82" s="111">
+        <v>642.66</v>
+      </c>
+      <c r="N82" s="112">
+        <f t="shared" ref="N82:N87" si="11">SUM(L82:M82)</f>
+        <v>2407.81</v>
+      </c>
+      <c r="O82" s="113"/>
+      <c r="P82" s="111">
+        <v>1762.76</v>
+      </c>
+      <c r="Q82" s="111">
+        <v>642.66</v>
+      </c>
+      <c r="R82" s="112">
+        <f t="shared" ref="R82:R87" si="12">SUM(P82:Q82)</f>
+        <v>2405.42</v>
+      </c>
+      <c r="S82" s="113"/>
+      <c r="T82" s="114">
+        <f t="shared" ref="T82:T87" si="13">N82-R82</f>
+        <v>2.3899999999998727</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A83" s="79">
+        <v>14</v>
+      </c>
+      <c r="B83" s="102">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C83" s="115">
+        <v>3.02</v>
+      </c>
+      <c r="D83" s="100">
+        <f>VLOOKUP($C83,Лист5!$A$1:$B$104,2,)</f>
+        <v>317.98</v>
+      </c>
+      <c r="E83" s="103"/>
+      <c r="F83" s="103"/>
+      <c r="G83" s="103"/>
+      <c r="H83" s="99">
+        <f t="shared" si="10"/>
+        <v>317.98</v>
+      </c>
+      <c r="J83" s="106"/>
+      <c r="K83" s="106" t="s">
+        <v>166</v>
+      </c>
+      <c r="L83" s="106"/>
+      <c r="M83" s="106">
+        <v>182.74</v>
+      </c>
+      <c r="N83" s="107">
+        <f t="shared" si="11"/>
+        <v>182.74</v>
+      </c>
+      <c r="P83" s="109"/>
+      <c r="Q83" s="109">
+        <v>182.74</v>
+      </c>
+      <c r="R83" s="110">
+        <f t="shared" si="12"/>
+        <v>182.74</v>
+      </c>
+      <c r="T83" s="101">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A84" s="79">
+        <v>15</v>
+      </c>
+      <c r="B84" s="102">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C84" s="104" t="s">
+        <v>121</v>
+      </c>
+      <c r="D84" s="103"/>
+      <c r="E84" s="100">
+        <v>182.74</v>
+      </c>
+      <c r="F84" s="103"/>
+      <c r="G84" s="103"/>
+      <c r="H84" s="99">
+        <f t="shared" si="10"/>
+        <v>182.74</v>
+      </c>
+      <c r="J84" s="111"/>
+      <c r="K84" s="111" t="s">
+        <v>157</v>
+      </c>
+      <c r="L84" s="111">
+        <v>49.99</v>
+      </c>
+      <c r="M84" s="111">
+        <v>189.76</v>
+      </c>
+      <c r="N84" s="112">
+        <f t="shared" si="11"/>
+        <v>239.75</v>
+      </c>
+      <c r="O84" s="113"/>
+      <c r="P84" s="111">
+        <v>51.07</v>
+      </c>
+      <c r="Q84" s="111">
+        <v>193.9</v>
+      </c>
+      <c r="R84" s="112">
+        <f t="shared" si="12"/>
+        <v>244.97</v>
+      </c>
+      <c r="S84" s="113"/>
+      <c r="T84" s="114">
+        <f t="shared" si="13"/>
+        <v>-5.2199999999999989</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A85" s="135">
+        <v>16</v>
+      </c>
+      <c r="B85" s="135">
+        <v>1</v>
+      </c>
+      <c r="C85" s="139">
+        <v>3.0059999999999998</v>
+      </c>
+      <c r="D85" s="137"/>
+      <c r="E85" s="137"/>
+      <c r="F85" s="137">
+        <f>VLOOKUP($C85,Лист5!$A$1:$B$104,2,)</f>
+        <v>48.730000000000004</v>
+      </c>
+      <c r="G85" s="137"/>
+      <c r="H85" s="137">
+        <f t="shared" si="10"/>
+        <v>48.730000000000004</v>
+      </c>
+      <c r="J85" s="106"/>
+      <c r="K85" s="106" t="s">
+        <v>158</v>
+      </c>
+      <c r="L85" s="106" t="s">
+        <v>164</v>
+      </c>
+      <c r="M85" s="106" t="s">
+        <v>164</v>
+      </c>
+      <c r="N85" s="107">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="P85" s="109">
+        <v>60.25</v>
+      </c>
+      <c r="Q85" s="109" t="s">
+        <v>164</v>
+      </c>
+      <c r="R85" s="110">
+        <f t="shared" si="12"/>
+        <v>60.25</v>
+      </c>
+      <c r="T85" s="101">
+        <f t="shared" si="13"/>
+        <v>-60.25</v>
+      </c>
+    </row>
+    <row r="86" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A86" s="79">
+        <v>17</v>
+      </c>
+      <c r="B86" s="102">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C86" s="104">
+        <v>3.0209999999999999</v>
+      </c>
+      <c r="D86" s="103"/>
+      <c r="E86" s="103"/>
+      <c r="F86" s="100">
+        <f>VLOOKUP($C86,Лист5!$A$1:$B$104,2,)</f>
+        <v>85.69</v>
+      </c>
+      <c r="G86" s="103"/>
+      <c r="H86" s="99">
+        <f t="shared" si="10"/>
+        <v>85.69</v>
+      </c>
+      <c r="J86" s="111"/>
+      <c r="K86" s="111" t="s">
+        <v>159</v>
+      </c>
+      <c r="L86" s="111">
+        <v>17.940000000000001</v>
+      </c>
+      <c r="M86" s="111"/>
+      <c r="N86" s="112">
+        <f t="shared" si="11"/>
+        <v>17.940000000000001</v>
+      </c>
+      <c r="O86" s="113"/>
+      <c r="P86" s="111" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q86" s="111" t="s">
+        <v>164</v>
+      </c>
+      <c r="R86" s="112">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S86" s="113"/>
+      <c r="T86" s="114">
+        <f t="shared" si="13"/>
+        <v>17.940000000000001</v>
+      </c>
+    </row>
+    <row r="87" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A87" s="135">
+        <v>18</v>
+      </c>
+      <c r="B87" s="135">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C87" s="139">
+        <v>3.085</v>
+      </c>
+      <c r="D87" s="137"/>
+      <c r="E87" s="137"/>
+      <c r="F87" s="137">
+        <f>VLOOKUP($C87,Лист5!$A$1:$B$104,2,)</f>
+        <v>54.81</v>
+      </c>
+      <c r="G87" s="137"/>
+      <c r="H87" s="137">
+        <f t="shared" si="10"/>
+        <v>54.81</v>
+      </c>
+      <c r="J87" s="106"/>
+      <c r="K87" s="106" t="s">
+        <v>160</v>
+      </c>
+      <c r="L87" s="106">
+        <v>3.6</v>
+      </c>
+      <c r="M87" s="106"/>
+      <c r="N87" s="107">
+        <f t="shared" si="11"/>
+        <v>3.6</v>
+      </c>
+      <c r="P87" s="109" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q87" s="109" t="s">
+        <v>164</v>
+      </c>
+      <c r="R87" s="110">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="T87" s="101">
+        <f t="shared" si="13"/>
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A88" s="79">
+        <v>19</v>
+      </c>
+      <c r="B88" s="102">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C88" s="104">
+        <v>3.0939999999999999</v>
+      </c>
+      <c r="D88" s="103"/>
+      <c r="E88" s="103"/>
+      <c r="F88" s="100">
+        <f>VLOOKUP($C88,Лист5!$A$1:$B$104,2,)</f>
+        <v>62.410000000000004</v>
+      </c>
+      <c r="G88" s="103"/>
+      <c r="H88" s="99">
+        <f t="shared" si="10"/>
+        <v>62.410000000000004</v>
+      </c>
+    </row>
+    <row r="89" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A89" s="79"/>
+      <c r="B89" s="79"/>
+      <c r="C89" s="79" t="s">
+        <v>19</v>
+      </c>
+      <c r="D89" s="99">
+        <f>SUM(D70:D88)</f>
+        <v>2343.38</v>
+      </c>
+      <c r="E89" s="99">
+        <f t="shared" ref="E89:F89" si="14">SUM(E70:E88)</f>
+        <v>182.74</v>
+      </c>
+      <c r="F89" s="99">
+        <f t="shared" si="14"/>
+        <v>251.64000000000001</v>
+      </c>
+      <c r="G89" s="99">
+        <f t="shared" ref="G89" si="15">SUM(G70:G88)</f>
+        <v>0</v>
+      </c>
+      <c r="H89" s="99">
+        <f t="shared" ref="H89" si="16">SUM(H70:H88)</f>
+        <v>2777.7599999999998</v>
+      </c>
+    </row>
+    <row r="91" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="B91" s="93" t="s">
+        <v>154</v>
+      </c>
+      <c r="C91" s="130"/>
+      <c r="D91" s="95" t="s">
+        <v>150</v>
+      </c>
+      <c r="E91" s="95" t="s">
+        <v>151</v>
+      </c>
+      <c r="F91" s="96" t="s">
+        <v>152</v>
+      </c>
+      <c r="G91" s="96" t="s">
+        <v>153</v>
+      </c>
+      <c r="J91" s="132" t="s">
+        <v>154</v>
+      </c>
+      <c r="K91" s="130"/>
+      <c r="L91" s="95" t="s">
+        <v>150</v>
+      </c>
+      <c r="M91" s="95" t="s">
+        <v>151</v>
+      </c>
+      <c r="N91" s="96" t="s">
+        <v>152</v>
+      </c>
+      <c r="O91" s="96" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="92" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="B92" s="130">
+        <v>1</v>
+      </c>
+      <c r="C92" s="130"/>
+      <c r="D92" s="131">
+        <f>SUM(D70:D81)</f>
+        <v>1742.02</v>
+      </c>
+      <c r="E92" s="130"/>
+      <c r="F92" s="131">
+        <f>F85</f>
+        <v>48.730000000000004</v>
+      </c>
+      <c r="G92" s="130"/>
+      <c r="J92" s="130">
+        <v>1</v>
+      </c>
+      <c r="K92" s="130"/>
+      <c r="L92" s="131">
+        <f>L82</f>
+        <v>1765.15</v>
+      </c>
+      <c r="M92" s="130">
+        <f>L83</f>
+        <v>0</v>
+      </c>
+      <c r="N92" s="131">
+        <f>L84</f>
+        <v>49.99</v>
+      </c>
+      <c r="O92" s="130"/>
+      <c r="P92" s="101">
+        <f t="shared" ref="P92:S93" si="17">L92-D92</f>
+        <v>23.130000000000109</v>
+      </c>
+      <c r="Q92" s="101">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="R92" s="101">
+        <f t="shared" si="17"/>
+        <v>1.259999999999998</v>
+      </c>
+      <c r="S92" s="101">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="B93" s="130">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C93" s="130"/>
+      <c r="D93" s="131">
+        <f>SUM(D82:D83)</f>
+        <v>601.36</v>
+      </c>
+      <c r="E93" s="131">
+        <f>E84</f>
+        <v>182.74</v>
+      </c>
+      <c r="F93" s="131">
+        <f>SUM(F86:F88)</f>
+        <v>202.91</v>
+      </c>
+      <c r="G93" s="130"/>
+      <c r="J93" s="130">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="K93" s="130"/>
+      <c r="L93" s="131">
+        <f>M82</f>
+        <v>642.66</v>
+      </c>
+      <c r="M93" s="131">
+        <f>M83</f>
+        <v>182.74</v>
+      </c>
+      <c r="N93" s="131">
+        <f>M84</f>
+        <v>189.76</v>
+      </c>
+      <c r="O93" s="130"/>
+      <c r="P93" s="101">
+        <f t="shared" si="17"/>
+        <v>41.299999999999955</v>
+      </c>
+      <c r="Q93" s="101">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="R93" s="101">
+        <f t="shared" si="17"/>
+        <v>-13.150000000000006</v>
+      </c>
+      <c r="S93" s="101">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A67:G67"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="4" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="7.5546875" style="86" customWidth="1"/>
+    <col min="2" max="2" width="61.6640625" style="90" customWidth="1"/>
+    <col min="3" max="3" width="49.109375" style="90" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" style="86" customWidth="1"/>
+    <col min="5" max="5" width="19.44140625" style="86" customWidth="1"/>
+    <col min="6" max="6" width="11.44140625" style="86" customWidth="1"/>
+    <col min="7" max="16384" width="9.109375" style="86"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="81"/>
+      <c r="B1" s="82" t="s">
+        <v>148</v>
+      </c>
+      <c r="C1" s="82"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="84"/>
+      <c r="F1" s="85"/>
+    </row>
+    <row r="2" spans="1:6" s="92" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="81" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="91" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="91" t="s">
+        <v>149</v>
+      </c>
+      <c r="D2" s="83" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="84" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="83" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="54" x14ac:dyDescent="0.35">
+      <c r="A3" s="87">
+        <v>1</v>
+      </c>
+      <c r="B3" s="88" t="s">
+        <v>145</v>
+      </c>
+      <c r="C3" s="88" t="s">
+        <v>174</v>
+      </c>
+      <c r="D3" s="87" t="s">
+        <v>82</v>
+      </c>
+      <c r="E3" s="87">
+        <v>1</v>
+      </c>
+      <c r="F3" s="129">
+        <f>'2.2)Шп1эт'!F24+'2.3)Шп2эт'!F25+'2.4)Шп3эт'!G17</f>
+        <v>8114.59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="36" x14ac:dyDescent="0.35">
+      <c r="A4" s="87">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4" s="88" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4" s="88"/>
+      <c r="D4" s="87" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="87">
+        <v>1.8</v>
+      </c>
+      <c r="F4" s="129">
+        <f>E4*F3</f>
+        <v>14606.262000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="36" x14ac:dyDescent="0.35">
+      <c r="A5" s="87">
+        <v>1.2</v>
+      </c>
+      <c r="B5" s="88" t="s">
+        <v>147</v>
+      </c>
+      <c r="C5" s="88"/>
+      <c r="D5" s="87" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="87">
+        <v>0.15</v>
+      </c>
+      <c r="F5" s="89">
+        <f>E5*F3</f>
+        <v>1217.1885</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:F24"/>
@@ -2308,14 +5404,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="170" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="142"/>
-      <c r="C1" s="142"/>
-      <c r="D1" s="142"/>
-      <c r="E1" s="142"/>
-      <c r="F1" s="142"/>
+      <c r="B1" s="170"/>
+      <c r="C1" s="170"/>
+      <c r="D1" s="170"/>
+      <c r="E1" s="170"/>
+      <c r="F1" s="170"/>
     </row>
     <row r="2" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="133"/>
@@ -2776,7 +5872,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
@@ -2789,14 +5885,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="170" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="142"/>
-      <c r="C1" s="142"/>
-      <c r="D1" s="142"/>
-      <c r="E1" s="142"/>
-      <c r="F1" s="142"/>
+      <c r="B1" s="170"/>
+      <c r="C1" s="170"/>
+      <c r="D1" s="170"/>
+      <c r="E1" s="170"/>
+      <c r="F1" s="170"/>
     </row>
     <row r="2" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="133"/>
@@ -3279,7 +6375,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
@@ -3292,15 +6388,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="170" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="142"/>
-      <c r="C1" s="142"/>
-      <c r="D1" s="142"/>
-      <c r="E1" s="142"/>
-      <c r="F1" s="142"/>
-      <c r="G1" s="142"/>
+      <c r="B1" s="170"/>
+      <c r="C1" s="170"/>
+      <c r="D1" s="170"/>
+      <c r="E1" s="170"/>
+      <c r="F1" s="170"/>
+      <c r="G1" s="170"/>
     </row>
     <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="133"/>
@@ -3645,412 +6741,413 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.21875" style="143" customWidth="1"/>
-    <col min="2" max="2" width="7" style="143" customWidth="1"/>
-    <col min="3" max="3" width="9.88671875" style="143" customWidth="1"/>
-    <col min="4" max="4" width="5.5546875" style="143" customWidth="1"/>
-    <col min="5" max="5" width="7.109375" style="143" customWidth="1"/>
-    <col min="6" max="6" width="7.6640625" style="143" customWidth="1"/>
-    <col min="7" max="7" width="10.77734375" style="143" customWidth="1"/>
-    <col min="8" max="8" width="11.6640625" style="143" customWidth="1"/>
-    <col min="9" max="10" width="8.21875" style="143" customWidth="1"/>
-    <col min="11" max="11" width="9.88671875" style="143" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="143"/>
+    <col min="1" max="1" width="7.21875" style="140" customWidth="1"/>
+    <col min="2" max="2" width="7" style="140" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" style="140" customWidth="1"/>
+    <col min="4" max="4" width="5.5546875" style="140" customWidth="1"/>
+    <col min="5" max="5" width="7.109375" style="140" customWidth="1"/>
+    <col min="6" max="6" width="7.6640625" style="140" customWidth="1"/>
+    <col min="7" max="7" width="10.77734375" style="140" customWidth="1"/>
+    <col min="8" max="8" width="11.6640625" style="140" customWidth="1"/>
+    <col min="9" max="10" width="8.21875" style="140" customWidth="1"/>
+    <col min="11" max="11" width="9.88671875" style="140" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="140"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="155" t="s">
         <v>175</v>
       </c>
-      <c r="B1" s="166"/>
-      <c r="C1" s="166"/>
-      <c r="D1" s="166"/>
-      <c r="E1" s="166"/>
-      <c r="F1" s="166"/>
-      <c r="G1" s="166"/>
-      <c r="H1" s="166"/>
-      <c r="I1" s="166"/>
-      <c r="J1" s="166"/>
-      <c r="K1" s="166"/>
-    </row>
-    <row r="2" spans="1:11" s="171" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="144" t="s">
+      <c r="B1" s="156"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
+      <c r="F1" s="156"/>
+      <c r="G1" s="156"/>
+      <c r="H1" s="156"/>
+      <c r="I1" s="156"/>
+      <c r="J1" s="156"/>
+      <c r="K1" s="156"/>
+    </row>
+    <row r="2" spans="1:11" s="153" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="141" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="167" t="s">
+      <c r="B2" s="157" t="s">
         <v>176</v>
       </c>
-      <c r="C2" s="168"/>
-      <c r="D2" s="168"/>
-      <c r="E2" s="168"/>
-      <c r="F2" s="168"/>
-      <c r="G2" s="169"/>
-      <c r="H2" s="145" t="s">
+      <c r="C2" s="158"/>
+      <c r="D2" s="158"/>
+      <c r="E2" s="158"/>
+      <c r="F2" s="158"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="160" t="s">
         <v>177</v>
       </c>
-      <c r="I2" s="146"/>
-      <c r="J2" s="147" t="s">
+      <c r="I2" s="161"/>
+      <c r="J2" s="142" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="170" t="s">
+      <c r="K2" s="152" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="148">
+      <c r="A3" s="143">
         <v>1</v>
       </c>
-      <c r="B3" s="149" t="s">
+      <c r="B3" s="162" t="s">
         <v>145</v>
       </c>
-      <c r="C3" s="150"/>
-      <c r="D3" s="150"/>
-      <c r="E3" s="150"/>
-      <c r="F3" s="150"/>
-      <c r="G3" s="151"/>
-      <c r="H3" s="152" t="s">
+      <c r="C3" s="163"/>
+      <c r="D3" s="163"/>
+      <c r="E3" s="163"/>
+      <c r="F3" s="163"/>
+      <c r="G3" s="164"/>
+      <c r="H3" s="165" t="s">
         <v>188</v>
       </c>
-      <c r="I3" s="153"/>
-      <c r="J3" s="148" t="s">
+      <c r="I3" s="166"/>
+      <c r="J3" s="143" t="s">
         <v>82</v>
       </c>
-      <c r="K3" s="154">
+      <c r="K3" s="144">
         <f>C13+G15+K13</f>
         <v>2493.81</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="155"/>
-      <c r="B4" s="155"/>
-      <c r="C4" s="155"/>
-      <c r="D4" s="155"/>
-      <c r="E4" s="155"/>
-      <c r="F4" s="155"/>
-      <c r="G4" s="155"/>
-      <c r="H4" s="155"/>
-      <c r="I4" s="155"/>
-      <c r="J4" s="155"/>
-      <c r="K4" s="155"/>
+      <c r="A4" s="167"/>
+      <c r="B4" s="167"/>
+      <c r="C4" s="167"/>
+      <c r="D4" s="167"/>
+      <c r="E4" s="167"/>
+      <c r="F4" s="167"/>
+      <c r="G4" s="167"/>
+      <c r="H4" s="167"/>
+      <c r="I4" s="167"/>
+      <c r="J4" s="167"/>
+      <c r="K4" s="167"/>
     </row>
     <row r="5" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="156" t="s">
+      <c r="A5" s="145" t="s">
         <v>178</v>
       </c>
-      <c r="B5" s="156" t="s">
+      <c r="B5" s="145" t="s">
         <v>182</v>
       </c>
-      <c r="C5" s="156" t="s">
+      <c r="C5" s="145" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="157"/>
-      <c r="E5" s="156" t="s">
+      <c r="D5" s="171"/>
+      <c r="E5" s="145" t="s">
         <v>178</v>
       </c>
-      <c r="F5" s="156" t="s">
+      <c r="F5" s="145" t="s">
         <v>182</v>
       </c>
-      <c r="G5" s="156" t="s">
+      <c r="G5" s="145" t="s">
         <v>179</v>
       </c>
-      <c r="H5" s="157"/>
-      <c r="I5" s="156" t="s">
+      <c r="H5" s="171"/>
+      <c r="I5" s="145" t="s">
         <v>178</v>
       </c>
-      <c r="J5" s="156" t="s">
+      <c r="J5" s="145" t="s">
         <v>182</v>
       </c>
-      <c r="K5" s="156" t="s">
+      <c r="K5" s="145" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="158" t="s">
+      <c r="A6" s="146" t="s">
         <v>183</v>
       </c>
-      <c r="B6" s="158" t="s">
+      <c r="B6" s="146" t="s">
         <v>150</v>
       </c>
-      <c r="C6" s="162">
+      <c r="C6" s="149">
         <v>125.55</v>
       </c>
-      <c r="D6" s="157"/>
-      <c r="E6" s="158" t="s">
+      <c r="D6" s="171"/>
+      <c r="E6" s="146" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="158" t="s">
+      <c r="F6" s="146" t="s">
         <v>150</v>
       </c>
-      <c r="G6" s="162">
+      <c r="G6" s="149">
         <v>118.18</v>
       </c>
-      <c r="H6" s="157"/>
-      <c r="I6" s="158" t="s">
+      <c r="H6" s="171"/>
+      <c r="I6" s="146" t="s">
         <v>93</v>
       </c>
-      <c r="J6" s="158" t="s">
+      <c r="J6" s="146" t="s">
         <v>150</v>
       </c>
-      <c r="K6" s="162">
+      <c r="K6" s="149">
         <v>116.51</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="159" t="s">
+      <c r="A7" s="147" t="s">
         <v>184</v>
       </c>
-      <c r="B7" s="159" t="s">
+      <c r="B7" s="147" t="s">
         <v>150</v>
       </c>
-      <c r="C7" s="163">
+      <c r="C7" s="150">
         <v>118.27</v>
       </c>
-      <c r="D7" s="157"/>
-      <c r="E7" s="159" t="s">
+      <c r="D7" s="171"/>
+      <c r="E7" s="147" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="159" t="s">
+      <c r="F7" s="147" t="s">
         <v>150</v>
       </c>
-      <c r="G7" s="163">
+      <c r="G7" s="150">
         <v>113.74</v>
       </c>
-      <c r="H7" s="157"/>
-      <c r="I7" s="159" t="s">
+      <c r="H7" s="171"/>
+      <c r="I7" s="147" t="s">
         <v>96</v>
       </c>
-      <c r="J7" s="159" t="s">
+      <c r="J7" s="147" t="s">
         <v>150</v>
       </c>
-      <c r="K7" s="163">
+      <c r="K7" s="150">
         <v>102.57</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="158" t="s">
+      <c r="A8" s="146" t="s">
         <v>185</v>
       </c>
-      <c r="B8" s="158" t="s">
+      <c r="B8" s="146" t="s">
         <v>150</v>
       </c>
-      <c r="C8" s="162">
+      <c r="C8" s="149">
         <v>102.42</v>
       </c>
-      <c r="D8" s="157"/>
-      <c r="E8" s="158" t="s">
+      <c r="D8" s="171"/>
+      <c r="E8" s="146" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="158" t="s">
+      <c r="F8" s="146" t="s">
         <v>150</v>
       </c>
-      <c r="G8" s="162">
+      <c r="G8" s="149">
         <v>122.5</v>
       </c>
-      <c r="H8" s="157"/>
-      <c r="I8" s="158" t="s">
+      <c r="H8" s="171"/>
+      <c r="I8" s="146" t="s">
         <v>97</v>
       </c>
-      <c r="J8" s="158" t="s">
+      <c r="J8" s="146" t="s">
         <v>150</v>
       </c>
-      <c r="K8" s="162">
+      <c r="K8" s="149">
         <v>104.7</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="159" t="s">
+      <c r="A9" s="147" t="s">
         <v>186</v>
       </c>
-      <c r="B9" s="159" t="s">
+      <c r="B9" s="147" t="s">
         <v>150</v>
       </c>
-      <c r="C9" s="163">
+      <c r="C9" s="150">
         <v>101.91</v>
       </c>
-      <c r="D9" s="157"/>
-      <c r="E9" s="159" t="s">
+      <c r="D9" s="171"/>
+      <c r="E9" s="147" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="159" t="s">
+      <c r="F9" s="147" t="s">
         <v>150</v>
       </c>
-      <c r="G9" s="163">
+      <c r="G9" s="150">
         <v>106.77</v>
       </c>
-      <c r="H9" s="157"/>
-      <c r="I9" s="159" t="s">
+      <c r="H9" s="171"/>
+      <c r="I9" s="147" t="s">
         <v>98</v>
       </c>
-      <c r="J9" s="159" t="s">
+      <c r="J9" s="147" t="s">
         <v>150</v>
       </c>
-      <c r="K9" s="163">
+      <c r="K9" s="150">
         <v>101.61</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="158" t="s">
+      <c r="A10" s="146" t="s">
         <v>180</v>
       </c>
-      <c r="B10" s="158" t="s">
+      <c r="B10" s="146" t="s">
         <v>150</v>
       </c>
-      <c r="C10" s="162">
+      <c r="C10" s="149">
         <v>98.2</v>
       </c>
-      <c r="D10" s="157"/>
-      <c r="E10" s="158" t="s">
+      <c r="D10" s="171"/>
+      <c r="E10" s="146" t="s">
         <v>27</v>
       </c>
-      <c r="F10" s="158" t="s">
+      <c r="F10" s="146" t="s">
         <v>150</v>
       </c>
-      <c r="G10" s="162">
+      <c r="G10" s="149">
         <v>111.51</v>
       </c>
-      <c r="H10" s="157"/>
-      <c r="I10" s="158" t="s">
+      <c r="H10" s="171"/>
+      <c r="I10" s="146" t="s">
         <v>99</v>
       </c>
-      <c r="J10" s="158" t="s">
+      <c r="J10" s="146" t="s">
         <v>150</v>
       </c>
-      <c r="K10" s="162">
+      <c r="K10" s="149">
         <v>105.25</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="159" t="s">
+      <c r="A11" s="147" t="s">
         <v>187</v>
       </c>
-      <c r="B11" s="159" t="s">
+      <c r="B11" s="147" t="s">
         <v>150</v>
       </c>
-      <c r="C11" s="163">
+      <c r="C11" s="150">
         <v>94.76</v>
       </c>
-      <c r="D11" s="157"/>
-      <c r="E11" s="159" t="s">
+      <c r="D11" s="171"/>
+      <c r="E11" s="147" t="s">
         <v>28</v>
       </c>
-      <c r="F11" s="159" t="s">
+      <c r="F11" s="147" t="s">
         <v>150</v>
       </c>
-      <c r="G11" s="163">
+      <c r="G11" s="150">
         <v>106.77</v>
       </c>
-      <c r="H11" s="157"/>
-      <c r="I11" s="159" t="s">
+      <c r="H11" s="171"/>
+      <c r="I11" s="147" t="s">
         <v>100</v>
       </c>
-      <c r="J11" s="159" t="s">
+      <c r="J11" s="147" t="s">
         <v>150</v>
       </c>
-      <c r="K11" s="163">
+      <c r="K11" s="150">
         <v>105.33</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="158" t="s">
+      <c r="A12" s="146" t="s">
         <v>181</v>
       </c>
-      <c r="B12" s="158" t="s">
+      <c r="B12" s="146" t="s">
         <v>150</v>
       </c>
-      <c r="C12" s="162">
+      <c r="C12" s="149">
         <v>152.44</v>
       </c>
-      <c r="D12" s="157"/>
-      <c r="E12" s="158" t="s">
+      <c r="D12" s="171"/>
+      <c r="E12" s="146" t="s">
         <v>29</v>
       </c>
-      <c r="F12" s="158" t="s">
+      <c r="F12" s="146" t="s">
         <v>150</v>
       </c>
-      <c r="G12" s="162">
+      <c r="G12" s="149">
         <v>93.03</v>
       </c>
-      <c r="H12" s="157"/>
-      <c r="I12" s="158" t="s">
+      <c r="H12" s="171"/>
+      <c r="I12" s="146" t="s">
         <v>101</v>
       </c>
-      <c r="J12" s="158" t="s">
+      <c r="J12" s="146" t="s">
         <v>150</v>
       </c>
-      <c r="K12" s="162">
+      <c r="K12" s="149">
         <v>101.95</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="160" t="s">
+      <c r="B13" s="148" t="s">
         <v>165</v>
       </c>
-      <c r="C13" s="164">
+      <c r="C13" s="151">
         <f>SUM(C6:C12)</f>
         <v>793.55</v>
       </c>
-      <c r="D13" s="157"/>
-      <c r="E13" s="159" t="s">
+      <c r="D13" s="171"/>
+      <c r="E13" s="147" t="s">
         <v>30</v>
       </c>
-      <c r="F13" s="159" t="s">
+      <c r="F13" s="147" t="s">
         <v>150</v>
       </c>
-      <c r="G13" s="163">
+      <c r="G13" s="150">
         <v>106.64</v>
       </c>
-      <c r="H13" s="157"/>
-      <c r="J13" s="160" t="s">
+      <c r="H13" s="171"/>
+      <c r="J13" s="148" t="s">
         <v>165</v>
       </c>
-      <c r="K13" s="164">
+      <c r="K13" s="151">
         <f>SUM(K6:K12)</f>
         <v>737.92000000000007</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="161"/>
-      <c r="B14" s="161"/>
-      <c r="C14" s="161"/>
-      <c r="D14" s="157"/>
-      <c r="E14" s="158" t="s">
+      <c r="A14" s="154"/>
+      <c r="B14" s="154"/>
+      <c r="C14" s="154"/>
+      <c r="D14" s="171"/>
+      <c r="E14" s="146" t="s">
         <v>32</v>
       </c>
-      <c r="F14" s="158" t="s">
+      <c r="F14" s="146" t="s">
         <v>150</v>
       </c>
-      <c r="G14" s="162">
+      <c r="G14" s="149">
         <v>83.2</v>
       </c>
-      <c r="H14" s="157"/>
-      <c r="I14" s="157"/>
-      <c r="J14" s="157"/>
-      <c r="K14" s="157"/>
+      <c r="H14" s="171"/>
+      <c r="I14" s="171"/>
+      <c r="J14" s="171"/>
+      <c r="K14" s="171"/>
     </row>
     <row r="15" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="161"/>
-      <c r="B15" s="161"/>
-      <c r="C15" s="161"/>
-      <c r="D15" s="157"/>
-      <c r="F15" s="160" t="s">
+      <c r="A15" s="154"/>
+      <c r="B15" s="154"/>
+      <c r="C15" s="154"/>
+      <c r="D15" s="171"/>
+      <c r="F15" s="148" t="s">
         <v>165</v>
       </c>
-      <c r="G15" s="164">
+      <c r="G15" s="151">
         <f>SUM(G6:G14)</f>
         <v>962.34</v>
       </c>
-      <c r="H15" s="157"/>
-      <c r="I15" s="157"/>
-      <c r="J15" s="157"/>
-      <c r="K15" s="157"/>
+      <c r="H15" s="171"/>
+      <c r="I15" s="171"/>
+      <c r="J15" s="171"/>
+      <c r="K15" s="171"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:K1"/>
     <mergeCell ref="H5:H15"/>
     <mergeCell ref="D5:D15"/>
     <mergeCell ref="A14:C15"/>
@@ -4060,14 +7157,13 @@
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="H3:I3"/>
     <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B104"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4886,6 +7982,520 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.21875" style="140" customWidth="1"/>
+    <col min="2" max="2" width="7" style="140" customWidth="1"/>
+    <col min="3" max="3" width="12.21875" style="140" customWidth="1"/>
+    <col min="4" max="4" width="5.109375" style="140" customWidth="1"/>
+    <col min="5" max="5" width="8.33203125" style="140" customWidth="1"/>
+    <col min="6" max="6" width="7.6640625" style="140" customWidth="1"/>
+    <col min="7" max="7" width="8" style="140" customWidth="1"/>
+    <col min="8" max="8" width="11.6640625" style="140" customWidth="1"/>
+    <col min="9" max="9" width="15.44140625" style="140" customWidth="1"/>
+    <col min="10" max="10" width="7.5546875" style="140" customWidth="1"/>
+    <col min="11" max="11" width="9" style="140" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="140"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="155" t="s">
+        <v>175</v>
+      </c>
+      <c r="B1" s="156"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
+      <c r="F1" s="156"/>
+      <c r="G1" s="156"/>
+      <c r="H1" s="156"/>
+      <c r="I1" s="156"/>
+      <c r="J1" s="156"/>
+      <c r="K1" s="156"/>
+    </row>
+    <row r="2" spans="1:11" s="153" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="141" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="157" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2" s="158"/>
+      <c r="D2" s="158"/>
+      <c r="E2" s="158"/>
+      <c r="F2" s="158"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="160" t="s">
+        <v>177</v>
+      </c>
+      <c r="I2" s="161"/>
+      <c r="J2" s="142" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="152" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="58.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="143">
+        <v>1</v>
+      </c>
+      <c r="B3" s="162" t="s">
+        <v>201</v>
+      </c>
+      <c r="C3" s="163"/>
+      <c r="D3" s="163"/>
+      <c r="E3" s="163"/>
+      <c r="F3" s="163"/>
+      <c r="G3" s="164"/>
+      <c r="H3" s="165" t="s">
+        <v>202</v>
+      </c>
+      <c r="I3" s="166"/>
+      <c r="J3" s="143" t="s">
+        <v>82</v>
+      </c>
+      <c r="K3" s="144">
+        <f>B9</f>
+        <v>127.953</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="167"/>
+      <c r="B4" s="167"/>
+      <c r="C4" s="167"/>
+      <c r="D4" s="167"/>
+      <c r="E4" s="167"/>
+      <c r="F4" s="167"/>
+      <c r="G4" s="167"/>
+      <c r="H4" s="167"/>
+      <c r="I4" s="167"/>
+      <c r="J4" s="167"/>
+      <c r="K4" s="167"/>
+    </row>
+    <row r="5" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="145" t="s">
+        <v>203</v>
+      </c>
+      <c r="B5" s="145" t="s">
+        <v>179</v>
+      </c>
+      <c r="C5" s="154"/>
+      <c r="D5" s="154"/>
+      <c r="E5" s="154"/>
+      <c r="F5" s="154"/>
+      <c r="G5" s="154"/>
+      <c r="H5" s="154"/>
+      <c r="I5" s="154"/>
+      <c r="J5" s="154"/>
+      <c r="K5" s="154"/>
+    </row>
+    <row r="6" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="146">
+        <v>1</v>
+      </c>
+      <c r="B6" s="149">
+        <f>10.47*3.9-1.72*3.9+1.72*0.8+1.99*3.9</f>
+        <v>43.262</v>
+      </c>
+      <c r="C6" s="154"/>
+      <c r="D6" s="154"/>
+      <c r="E6" s="154"/>
+      <c r="F6" s="154"/>
+      <c r="G6" s="154"/>
+      <c r="H6" s="154"/>
+      <c r="I6" s="154"/>
+      <c r="J6" s="154"/>
+      <c r="K6" s="154"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="147">
+        <v>2</v>
+      </c>
+      <c r="B7" s="150">
+        <f>10.37*3.9-1.72*3.9+1.72*0.8+1.99*3.9</f>
+        <v>42.872</v>
+      </c>
+      <c r="C7" s="154"/>
+      <c r="D7" s="154"/>
+      <c r="E7" s="154"/>
+      <c r="F7" s="154"/>
+      <c r="G7" s="154"/>
+      <c r="H7" s="154"/>
+      <c r="I7" s="154"/>
+      <c r="J7" s="154"/>
+      <c r="K7" s="154"/>
+    </row>
+    <row r="8" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="146">
+        <v>3</v>
+      </c>
+      <c r="B8" s="149">
+        <f>10.1*3.9-1.72*3.9+1.72*0.8+1.99*3.9</f>
+        <v>41.819000000000003</v>
+      </c>
+      <c r="C8" s="154"/>
+      <c r="D8" s="154"/>
+      <c r="E8" s="154"/>
+      <c r="F8" s="154"/>
+      <c r="G8" s="154"/>
+      <c r="H8" s="154"/>
+      <c r="I8" s="154"/>
+      <c r="J8" s="154"/>
+      <c r="K8" s="154"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="172" t="s">
+        <v>165</v>
+      </c>
+      <c r="B9" s="173">
+        <f>SUM(B6:B8)</f>
+        <v>127.953</v>
+      </c>
+      <c r="C9" s="154"/>
+      <c r="D9" s="154"/>
+      <c r="E9" s="154"/>
+      <c r="F9" s="154"/>
+      <c r="G9" s="154"/>
+      <c r="H9" s="154"/>
+      <c r="I9" s="154"/>
+      <c r="J9" s="154"/>
+      <c r="K9" s="154"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="C5:K9"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="A4:K4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.21875" style="140" customWidth="1"/>
+    <col min="2" max="2" width="7" style="140" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" style="140" customWidth="1"/>
+    <col min="4" max="4" width="5.5546875" style="140" customWidth="1"/>
+    <col min="5" max="5" width="7.109375" style="140" customWidth="1"/>
+    <col min="6" max="6" width="7.6640625" style="140" customWidth="1"/>
+    <col min="7" max="7" width="4.5546875" style="140" customWidth="1"/>
+    <col min="8" max="8" width="11.6640625" style="140" customWidth="1"/>
+    <col min="9" max="9" width="15.44140625" style="140" customWidth="1"/>
+    <col min="10" max="10" width="7.5546875" style="140" customWidth="1"/>
+    <col min="11" max="11" width="9" style="140" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="140"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="155" t="s">
+        <v>175</v>
+      </c>
+      <c r="B1" s="156"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
+      <c r="F1" s="156"/>
+      <c r="G1" s="156"/>
+      <c r="H1" s="156"/>
+      <c r="I1" s="156"/>
+      <c r="J1" s="156"/>
+      <c r="K1" s="156"/>
+    </row>
+    <row r="2" spans="1:11" s="153" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="141" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="157" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2" s="158"/>
+      <c r="D2" s="158"/>
+      <c r="E2" s="158"/>
+      <c r="F2" s="158"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="160" t="s">
+        <v>177</v>
+      </c>
+      <c r="I2" s="161"/>
+      <c r="J2" s="142" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="152" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="143">
+        <v>1</v>
+      </c>
+      <c r="B3" s="162" t="s">
+        <v>189</v>
+      </c>
+      <c r="C3" s="163"/>
+      <c r="D3" s="163"/>
+      <c r="E3" s="163"/>
+      <c r="F3" s="163"/>
+      <c r="G3" s="164"/>
+      <c r="H3" s="165" t="s">
+        <v>190</v>
+      </c>
+      <c r="I3" s="166"/>
+      <c r="J3" s="143" t="s">
+        <v>82</v>
+      </c>
+      <c r="K3" s="144">
+        <f>C15</f>
+        <v>3167.8690000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="167"/>
+      <c r="B4" s="167"/>
+      <c r="C4" s="167"/>
+      <c r="D4" s="167"/>
+      <c r="E4" s="167"/>
+      <c r="F4" s="167"/>
+      <c r="G4" s="167"/>
+      <c r="H4" s="167"/>
+      <c r="I4" s="167"/>
+      <c r="J4" s="167"/>
+      <c r="K4" s="167"/>
+    </row>
+    <row r="5" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="145" t="s">
+        <v>178</v>
+      </c>
+      <c r="B5" s="145" t="s">
+        <v>182</v>
+      </c>
+      <c r="C5" s="145" t="s">
+        <v>179</v>
+      </c>
+      <c r="D5" s="154"/>
+      <c r="E5" s="154"/>
+      <c r="F5" s="154"/>
+      <c r="G5" s="154"/>
+      <c r="H5" s="154"/>
+      <c r="I5" s="154"/>
+      <c r="J5" s="154"/>
+      <c r="K5" s="154"/>
+    </row>
+    <row r="6" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="146" t="s">
+        <v>191</v>
+      </c>
+      <c r="B6" s="146" t="s">
+        <v>200</v>
+      </c>
+      <c r="C6" s="149">
+        <v>590.38850000000002</v>
+      </c>
+      <c r="D6" s="154"/>
+      <c r="E6" s="154"/>
+      <c r="F6" s="154"/>
+      <c r="G6" s="154"/>
+      <c r="H6" s="154"/>
+      <c r="I6" s="154"/>
+      <c r="J6" s="154"/>
+      <c r="K6" s="154"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="147" t="s">
+        <v>192</v>
+      </c>
+      <c r="B7" s="147" t="s">
+        <v>200</v>
+      </c>
+      <c r="C7" s="150">
+        <v>141.96</v>
+      </c>
+      <c r="D7" s="154"/>
+      <c r="E7" s="154"/>
+      <c r="F7" s="154"/>
+      <c r="G7" s="154"/>
+      <c r="H7" s="154"/>
+      <c r="I7" s="154"/>
+      <c r="J7" s="154"/>
+      <c r="K7" s="154"/>
+    </row>
+    <row r="8" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="146" t="s">
+        <v>193</v>
+      </c>
+      <c r="B8" s="146" t="s">
+        <v>200</v>
+      </c>
+      <c r="C8" s="149">
+        <v>610.49</v>
+      </c>
+      <c r="D8" s="154"/>
+      <c r="E8" s="154"/>
+      <c r="F8" s="154"/>
+      <c r="G8" s="154"/>
+      <c r="H8" s="154"/>
+      <c r="I8" s="154"/>
+      <c r="J8" s="154"/>
+      <c r="K8" s="154"/>
+    </row>
+    <row r="9" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="147" t="s">
+        <v>194</v>
+      </c>
+      <c r="B9" s="147" t="s">
+        <v>200</v>
+      </c>
+      <c r="C9" s="150">
+        <v>736.31050000000005</v>
+      </c>
+      <c r="D9" s="154"/>
+      <c r="E9" s="154"/>
+      <c r="F9" s="154"/>
+      <c r="G9" s="154"/>
+      <c r="H9" s="154"/>
+      <c r="I9" s="154"/>
+      <c r="J9" s="154"/>
+      <c r="K9" s="154"/>
+    </row>
+    <row r="10" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="146" t="s">
+        <v>195</v>
+      </c>
+      <c r="B10" s="146" t="s">
+        <v>200</v>
+      </c>
+      <c r="C10" s="149">
+        <v>184.6</v>
+      </c>
+      <c r="D10" s="154"/>
+      <c r="E10" s="154"/>
+      <c r="F10" s="154"/>
+      <c r="G10" s="154"/>
+      <c r="H10" s="154"/>
+      <c r="I10" s="154"/>
+      <c r="J10" s="154"/>
+      <c r="K10" s="154"/>
+    </row>
+    <row r="11" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="147" t="s">
+        <v>196</v>
+      </c>
+      <c r="B11" s="147" t="s">
+        <v>200</v>
+      </c>
+      <c r="C11" s="150">
+        <v>714.72</v>
+      </c>
+      <c r="D11" s="154"/>
+      <c r="E11" s="154"/>
+      <c r="F11" s="154"/>
+      <c r="G11" s="154"/>
+      <c r="H11" s="154"/>
+      <c r="I11" s="154"/>
+      <c r="J11" s="154"/>
+      <c r="K11" s="154"/>
+    </row>
+    <row r="12" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="146" t="s">
+        <v>197</v>
+      </c>
+      <c r="B12" s="146" t="s">
+        <v>200</v>
+      </c>
+      <c r="C12" s="149">
+        <v>94.2</v>
+      </c>
+      <c r="D12" s="154"/>
+      <c r="E12" s="154"/>
+      <c r="F12" s="154"/>
+      <c r="G12" s="154"/>
+      <c r="H12" s="154"/>
+      <c r="I12" s="154"/>
+      <c r="J12" s="154"/>
+      <c r="K12" s="154"/>
+    </row>
+    <row r="13" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="147" t="s">
+        <v>198</v>
+      </c>
+      <c r="B13" s="147" t="s">
+        <v>200</v>
+      </c>
+      <c r="C13" s="150">
+        <v>42.8</v>
+      </c>
+      <c r="D13" s="154"/>
+      <c r="E13" s="154"/>
+      <c r="F13" s="154"/>
+      <c r="G13" s="154"/>
+      <c r="H13" s="154"/>
+      <c r="I13" s="154"/>
+      <c r="J13" s="154"/>
+      <c r="K13" s="154"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="146" t="s">
+        <v>199</v>
+      </c>
+      <c r="B14" s="146" t="s">
+        <v>200</v>
+      </c>
+      <c r="C14" s="149">
+        <v>52.4</v>
+      </c>
+      <c r="D14" s="154"/>
+      <c r="E14" s="154"/>
+      <c r="F14" s="154"/>
+      <c r="G14" s="154"/>
+      <c r="H14" s="154"/>
+      <c r="I14" s="154"/>
+      <c r="J14" s="154"/>
+      <c r="K14" s="154"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B15" s="148" t="s">
+        <v>165</v>
+      </c>
+      <c r="C15" s="151">
+        <f>SUM(C6:C14)</f>
+        <v>3167.8690000000001</v>
+      </c>
+      <c r="D15" s="154"/>
+      <c r="E15" s="154"/>
+      <c r="F15" s="154"/>
+      <c r="G15" s="154"/>
+      <c r="H15" s="154"/>
+      <c r="I15" s="154"/>
+      <c r="J15" s="154"/>
+      <c r="K15" s="154"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="D5:K15"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="A4:K4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -4909,26 +8519,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="140" t="s">
+      <c r="A1" s="168" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="168"/>
+      <c r="G1" s="168"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="141" t="s">
+      <c r="A2" s="169" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="141"/>
-      <c r="C2" s="141"/>
-      <c r="D2" s="141"/>
-      <c r="E2" s="141"/>
-      <c r="F2" s="141"/>
-      <c r="G2" s="141"/>
+      <c r="B2" s="169"/>
+      <c r="C2" s="169"/>
+      <c r="D2" s="169"/>
+      <c r="E2" s="169"/>
+      <c r="F2" s="169"/>
+      <c r="G2" s="169"/>
     </row>
     <row r="3" spans="1:16" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
@@ -6505,7 +10115,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
@@ -6983,7 +10593,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
@@ -7013,26 +10623,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A1" s="140" t="s">
+      <c r="A1" s="168" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="168"/>
+      <c r="G1" s="168"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A2" s="141" t="s">
+      <c r="A2" s="169" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="141"/>
-      <c r="C2" s="141"/>
-      <c r="D2" s="141"/>
-      <c r="E2" s="141"/>
-      <c r="F2" s="141"/>
-      <c r="G2" s="141"/>
+      <c r="B2" s="169"/>
+      <c r="C2" s="169"/>
+      <c r="D2" s="169"/>
+      <c r="E2" s="169"/>
+      <c r="F2" s="169"/>
+      <c r="G2" s="169"/>
       <c r="O2" s="39"/>
       <c r="Q2" s="41"/>
     </row>
@@ -8746,7 +12356,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="5" tint="0.79998168889431442"/>
@@ -9223,7 +12833,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="5" tint="0.79998168889431442"/>
@@ -9239,26 +12849,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="140" t="s">
+      <c r="A1" s="168" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="168"/>
+      <c r="G1" s="168"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="141" t="s">
+      <c r="A2" s="169" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="141"/>
-      <c r="C2" s="141"/>
-      <c r="D2" s="141"/>
-      <c r="E2" s="141"/>
-      <c r="F2" s="141"/>
-      <c r="G2" s="141"/>
+      <c r="B2" s="169"/>
+      <c r="C2" s="169"/>
+      <c r="D2" s="169"/>
+      <c r="E2" s="169"/>
+      <c r="F2" s="169"/>
+      <c r="G2" s="169"/>
     </row>
     <row r="3" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A3" s="72"/>
@@ -9662,7 +13272,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -9871,3048 +13481,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor theme="2" tint="-9.9978637043366805E-2"/>
-  </sheetPr>
-  <dimension ref="A1:AD93"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="2" width="9.109375" style="78"/>
-    <col min="3" max="3" width="11.5546875" style="78" customWidth="1"/>
-    <col min="4" max="7" width="10.5546875" style="78" customWidth="1"/>
-    <col min="8" max="16384" width="9.109375" style="78"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A1" s="142" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="142"/>
-      <c r="C1" s="142"/>
-      <c r="D1" s="142"/>
-      <c r="E1" s="142"/>
-      <c r="F1" s="142"/>
-      <c r="G1" s="142"/>
-    </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="95" t="s">
-        <v>150</v>
-      </c>
-      <c r="E2" s="96" t="s">
-        <v>152</v>
-      </c>
-      <c r="F2" s="96" t="s">
-        <v>153</v>
-      </c>
-      <c r="G2" s="80" t="s">
-        <v>3</v>
-      </c>
-      <c r="S2" s="105"/>
-      <c r="T2" s="105"/>
-      <c r="U2" s="105" t="s">
-        <v>172</v>
-      </c>
-      <c r="V2" s="105"/>
-      <c r="W2" s="105"/>
-      <c r="Y2" s="108" t="s">
-        <v>173</v>
-      </c>
-      <c r="Z2" s="108"/>
-      <c r="AA2" s="108"/>
-      <c r="AC2" s="78" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A3" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="79" t="s">
-        <v>154</v>
-      </c>
-      <c r="C3" s="97" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="98" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="98" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="98" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" s="99" t="s">
-        <v>4</v>
-      </c>
-      <c r="S3" s="106"/>
-      <c r="T3" s="106"/>
-      <c r="U3" s="106">
-        <v>1</v>
-      </c>
-      <c r="V3" s="106">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="W3" s="106" t="s">
-        <v>165</v>
-      </c>
-      <c r="Y3" s="109">
-        <v>1</v>
-      </c>
-      <c r="Z3" s="109">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="AA3" s="109" t="s">
-        <v>165</v>
-      </c>
-      <c r="AC3" s="78" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A4" s="79">
-        <v>1</v>
-      </c>
-      <c r="B4" s="79">
-        <v>1</v>
-      </c>
-      <c r="C4" s="119">
-        <v>1.028</v>
-      </c>
-      <c r="D4" s="100">
-        <f>VLOOKUP($C4,Лист5!$A$1:$B$104,2,)+15</f>
-        <v>118.27</v>
-      </c>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="99">
-        <f>SUM(D4:F4)</f>
-        <v>118.27</v>
-      </c>
-      <c r="S4" s="106" t="s">
-        <v>161</v>
-      </c>
-      <c r="T4" s="106" t="s">
-        <v>156</v>
-      </c>
-      <c r="U4" s="107">
-        <v>1469.99</v>
-      </c>
-      <c r="V4" s="106">
-        <v>1225.93</v>
-      </c>
-      <c r="W4" s="107">
-        <f>SUM(U4:V4)</f>
-        <v>2695.92</v>
-      </c>
-      <c r="Y4" s="109">
-        <v>1469.31</v>
-      </c>
-      <c r="Z4" s="109">
-        <v>1224.44</v>
-      </c>
-      <c r="AA4" s="110">
-        <f>SUM(Y4:Z4)</f>
-        <v>2693.75</v>
-      </c>
-      <c r="AC4" s="101">
-        <f>W4-AA4</f>
-        <v>2.1700000000000728</v>
-      </c>
-    </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A5" s="79">
-        <v>2</v>
-      </c>
-      <c r="B5" s="79">
-        <v>1</v>
-      </c>
-      <c r="C5" s="119">
-        <v>1.0269999999999999</v>
-      </c>
-      <c r="D5" s="100">
-        <f>VLOOKUP($C5,Лист5!$A$1:$B$104,2,)+15</f>
-        <v>125.55</v>
-      </c>
-      <c r="E5" s="99"/>
-      <c r="F5" s="99"/>
-      <c r="G5" s="99">
-        <f t="shared" ref="G5:G24" si="0">SUM(D5:F5)</f>
-        <v>125.55</v>
-      </c>
-      <c r="S5" s="111"/>
-      <c r="T5" s="111" t="s">
-        <v>157</v>
-      </c>
-      <c r="U5" s="111" t="s">
-        <v>164</v>
-      </c>
-      <c r="V5" s="111">
-        <v>378.74</v>
-      </c>
-      <c r="W5" s="112">
-        <f t="shared" ref="W5:W23" si="1">SUM(U5:V5)</f>
-        <v>378.74</v>
-      </c>
-      <c r="X5" s="113"/>
-      <c r="Y5" s="111" t="s">
-        <v>164</v>
-      </c>
-      <c r="Z5" s="111">
-        <v>348.14</v>
-      </c>
-      <c r="AA5" s="112">
-        <f t="shared" ref="AA5:AA21" si="2">SUM(Y5:Z5)</f>
-        <v>348.14</v>
-      </c>
-      <c r="AB5" s="113"/>
-      <c r="AC5" s="114">
-        <f t="shared" ref="AC5:AC21" si="3">W5-AA5</f>
-        <v>30.600000000000023</v>
-      </c>
-      <c r="AD5" s="113"/>
-    </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A6" s="79">
-        <v>3</v>
-      </c>
-      <c r="B6" s="79">
-        <v>1</v>
-      </c>
-      <c r="C6" s="119">
-        <v>1.026</v>
-      </c>
-      <c r="D6" s="100">
-        <f>284.86+35</f>
-        <v>319.86</v>
-      </c>
-      <c r="E6" s="99"/>
-      <c r="F6" s="99"/>
-      <c r="G6" s="99">
-        <f t="shared" si="0"/>
-        <v>319.86</v>
-      </c>
-      <c r="S6" s="106"/>
-      <c r="T6" s="106" t="s">
-        <v>158</v>
-      </c>
-      <c r="U6" s="106" t="s">
-        <v>164</v>
-      </c>
-      <c r="V6" s="106" t="s">
-        <v>164</v>
-      </c>
-      <c r="W6" s="107">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y6" s="109">
-        <v>57.81</v>
-      </c>
-      <c r="Z6" s="109">
-        <v>5.85</v>
-      </c>
-      <c r="AA6" s="110">
-        <f t="shared" si="2"/>
-        <v>63.660000000000004</v>
-      </c>
-      <c r="AC6" s="101">
-        <f t="shared" si="3"/>
-        <v>-63.660000000000004</v>
-      </c>
-    </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A7" s="135">
-        <v>4</v>
-      </c>
-      <c r="B7" s="135">
-        <v>1</v>
-      </c>
-      <c r="C7" s="136">
-        <v>1.024</v>
-      </c>
-      <c r="D7" s="137">
-        <f>53.84</f>
-        <v>53.84</v>
-      </c>
-      <c r="E7" s="137"/>
-      <c r="F7" s="137"/>
-      <c r="G7" s="137">
-        <f t="shared" si="0"/>
-        <v>53.84</v>
-      </c>
-      <c r="S7" s="111"/>
-      <c r="T7" s="111" t="s">
-        <v>159</v>
-      </c>
-      <c r="U7" s="112">
-        <v>13.59</v>
-      </c>
-      <c r="V7" s="111">
-        <v>1.8</v>
-      </c>
-      <c r="W7" s="112">
-        <f t="shared" si="1"/>
-        <v>15.39</v>
-      </c>
-      <c r="X7" s="113"/>
-      <c r="Y7" s="111" t="s">
-        <v>164</v>
-      </c>
-      <c r="Z7" s="111" t="s">
-        <v>164</v>
-      </c>
-      <c r="AA7" s="112">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AB7" s="113"/>
-      <c r="AC7" s="114">
-        <f t="shared" si="3"/>
-        <v>15.39</v>
-      </c>
-      <c r="AD7" s="113"/>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A8" s="79">
-        <v>5</v>
-      </c>
-      <c r="B8" s="79">
-        <v>1</v>
-      </c>
-      <c r="C8" s="119">
-        <v>1.0289999999999999</v>
-      </c>
-      <c r="D8" s="100">
-        <f>VLOOKUP($C8,Лист5!$A$1:$B$104,2,)+10</f>
-        <v>102.42</v>
-      </c>
-      <c r="E8" s="99"/>
-      <c r="F8" s="99"/>
-      <c r="G8" s="99">
-        <f t="shared" si="0"/>
-        <v>102.42</v>
-      </c>
-      <c r="S8" s="106"/>
-      <c r="T8" s="106" t="s">
-        <v>160</v>
-      </c>
-      <c r="U8" s="106">
-        <v>2.4</v>
-      </c>
-      <c r="V8" s="106" t="s">
-        <v>164</v>
-      </c>
-      <c r="W8" s="107">
-        <f t="shared" si="1"/>
-        <v>2.4</v>
-      </c>
-      <c r="Y8" s="109" t="s">
-        <v>164</v>
-      </c>
-      <c r="Z8" s="109" t="s">
-        <v>164</v>
-      </c>
-      <c r="AA8" s="110">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC8" s="101">
-        <f t="shared" si="3"/>
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A9" s="79">
-        <v>6</v>
-      </c>
-      <c r="B9" s="79">
-        <v>1</v>
-      </c>
-      <c r="C9" s="119">
-        <v>1.03</v>
-      </c>
-      <c r="D9" s="100">
-        <f>VLOOKUP($C9,Лист5!$A$1:$B$104,2,)+7</f>
-        <v>101.91</v>
-      </c>
-      <c r="E9" s="99"/>
-      <c r="F9" s="99"/>
-      <c r="G9" s="99">
-        <f t="shared" si="0"/>
-        <v>101.91</v>
-      </c>
-      <c r="S9" s="111"/>
-      <c r="T9" s="111"/>
-      <c r="U9" s="111"/>
-      <c r="V9" s="111"/>
-      <c r="W9" s="112"/>
-      <c r="X9" s="113"/>
-      <c r="Y9" s="111"/>
-      <c r="Z9" s="111"/>
-      <c r="AA9" s="112"/>
-      <c r="AB9" s="113"/>
-      <c r="AC9" s="114"/>
-      <c r="AD9" s="113"/>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A10" s="79">
-        <v>7</v>
-      </c>
-      <c r="B10" s="79">
-        <v>1</v>
-      </c>
-      <c r="C10" s="119">
-        <v>1.0309999999999999</v>
-      </c>
-      <c r="D10" s="100">
-        <f>VLOOKUP($C10,Лист5!$A$1:$B$104,2,)+8</f>
-        <v>98.2</v>
-      </c>
-      <c r="E10" s="99"/>
-      <c r="F10" s="99"/>
-      <c r="G10" s="99">
-        <f t="shared" si="0"/>
-        <v>98.2</v>
-      </c>
-      <c r="S10" s="106" t="s">
-        <v>162</v>
-      </c>
-      <c r="T10" s="106" t="s">
-        <v>156</v>
-      </c>
-      <c r="U10" s="106">
-        <v>1537.74</v>
-      </c>
-      <c r="V10" s="106">
-        <v>1995.77</v>
-      </c>
-      <c r="W10" s="107">
-        <f t="shared" si="1"/>
-        <v>3533.51</v>
-      </c>
-      <c r="Y10" s="109">
-        <v>1537.34</v>
-      </c>
-      <c r="Z10" s="109">
-        <v>1673.16</v>
-      </c>
-      <c r="AA10" s="110">
-        <f t="shared" si="2"/>
-        <v>3210.5</v>
-      </c>
-      <c r="AC10" s="101">
-        <f t="shared" si="3"/>
-        <v>323.01000000000022</v>
-      </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A11" s="79">
-        <v>8</v>
-      </c>
-      <c r="B11" s="79">
-        <v>1</v>
-      </c>
-      <c r="C11" s="119">
-        <v>1.032</v>
-      </c>
-      <c r="D11" s="100">
-        <f>VLOOKUP($C11,Лист5!$A$1:$B$104,2,)+7</f>
-        <v>94.76</v>
-      </c>
-      <c r="E11" s="99"/>
-      <c r="F11" s="99"/>
-      <c r="G11" s="99">
-        <f t="shared" si="0"/>
-        <v>94.76</v>
-      </c>
-      <c r="S11" s="111"/>
-      <c r="T11" s="111" t="s">
-        <v>157</v>
-      </c>
-      <c r="U11" s="111">
-        <v>51.07</v>
-      </c>
-      <c r="V11" s="111">
-        <v>409.01</v>
-      </c>
-      <c r="W11" s="112">
-        <f t="shared" si="1"/>
-        <v>460.08</v>
-      </c>
-      <c r="X11" s="113"/>
-      <c r="Y11" s="111">
-        <v>51.07</v>
-      </c>
-      <c r="Z11" s="111">
-        <v>409.01</v>
-      </c>
-      <c r="AA11" s="112">
-        <f t="shared" si="2"/>
-        <v>460.08</v>
-      </c>
-      <c r="AB11" s="113"/>
-      <c r="AC11" s="114">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AD11" s="113"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A12" s="79">
-        <v>9</v>
-      </c>
-      <c r="B12" s="79">
-        <v>1</v>
-      </c>
-      <c r="C12" s="119">
-        <v>1.0329999999999999</v>
-      </c>
-      <c r="D12" s="100">
-        <f>VLOOKUP($C12,Лист5!$A$1:$B$104,2,)+10</f>
-        <v>152.44</v>
-      </c>
-      <c r="E12" s="99"/>
-      <c r="F12" s="99"/>
-      <c r="G12" s="99">
-        <f t="shared" si="0"/>
-        <v>152.44</v>
-      </c>
-      <c r="S12" s="106"/>
-      <c r="T12" s="106" t="s">
-        <v>158</v>
-      </c>
-      <c r="U12" s="106" t="s">
-        <v>164</v>
-      </c>
-      <c r="V12" s="106" t="s">
-        <v>164</v>
-      </c>
-      <c r="W12" s="107">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y12" s="109">
-        <v>60.14</v>
-      </c>
-      <c r="Z12" s="109">
-        <v>338.43</v>
-      </c>
-      <c r="AA12" s="110">
-        <f t="shared" si="2"/>
-        <v>398.57</v>
-      </c>
-      <c r="AC12" s="101">
-        <f t="shared" si="3"/>
-        <v>-398.57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A13" s="79">
-        <v>10</v>
-      </c>
-      <c r="B13" s="79">
-        <v>1</v>
-      </c>
-      <c r="C13" s="119">
-        <v>1.0389999999999999</v>
-      </c>
-      <c r="D13" s="100">
-        <f>VLOOKUP($C13,Лист5!$A$1:$B$104,2,)+15</f>
-        <v>181.2</v>
-      </c>
-      <c r="E13" s="99"/>
-      <c r="F13" s="99"/>
-      <c r="G13" s="99">
-        <f t="shared" si="0"/>
-        <v>181.2</v>
-      </c>
-      <c r="S13" s="111"/>
-      <c r="T13" s="111" t="s">
-        <v>159</v>
-      </c>
-      <c r="U13" s="111">
-        <v>16.09</v>
-      </c>
-      <c r="V13" s="111" t="s">
-        <v>164</v>
-      </c>
-      <c r="W13" s="112">
-        <f t="shared" si="1"/>
-        <v>16.09</v>
-      </c>
-      <c r="X13" s="113"/>
-      <c r="Y13" s="111" t="s">
-        <v>164</v>
-      </c>
-      <c r="Z13" s="111" t="s">
-        <v>164</v>
-      </c>
-      <c r="AA13" s="112">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AB13" s="113"/>
-      <c r="AC13" s="114">
-        <f t="shared" si="3"/>
-        <v>16.09</v>
-      </c>
-      <c r="AD13" s="113"/>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A14" s="79">
-        <v>11</v>
-      </c>
-      <c r="B14" s="79">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C14" s="119">
-        <v>1.04</v>
-      </c>
-      <c r="D14" s="100">
-        <f>164+32.45+20</f>
-        <v>216.45</v>
-      </c>
-      <c r="E14" s="99"/>
-      <c r="F14" s="99"/>
-      <c r="G14" s="99">
-        <f t="shared" si="0"/>
-        <v>216.45</v>
-      </c>
-      <c r="S14" s="106"/>
-      <c r="T14" s="106" t="s">
-        <v>160</v>
-      </c>
-      <c r="U14" s="106">
-        <v>2.4</v>
-      </c>
-      <c r="V14" s="106" t="s">
-        <v>164</v>
-      </c>
-      <c r="W14" s="107">
-        <f t="shared" si="1"/>
-        <v>2.4</v>
-      </c>
-      <c r="Y14" s="109" t="s">
-        <v>164</v>
-      </c>
-      <c r="Z14" s="109" t="s">
-        <v>164</v>
-      </c>
-      <c r="AA14" s="110">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC14" s="101">
-        <f t="shared" si="3"/>
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A15" s="79">
-        <v>12</v>
-      </c>
-      <c r="B15" s="79">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C15" s="119">
-        <v>1.0429999999999999</v>
-      </c>
-      <c r="D15" s="100">
-        <f>18+83.8</f>
-        <v>101.8</v>
-      </c>
-      <c r="E15" s="99"/>
-      <c r="F15" s="99"/>
-      <c r="G15" s="99">
-        <f t="shared" si="0"/>
-        <v>101.8</v>
-      </c>
-      <c r="S15" s="111"/>
-      <c r="T15" s="111"/>
-      <c r="U15" s="111"/>
-      <c r="V15" s="111"/>
-      <c r="W15" s="112"/>
-      <c r="X15" s="113"/>
-      <c r="Y15" s="111"/>
-      <c r="Z15" s="111"/>
-      <c r="AA15" s="112"/>
-      <c r="AB15" s="113"/>
-      <c r="AC15" s="114"/>
-      <c r="AD15" s="113"/>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A16" s="79">
-        <v>13</v>
-      </c>
-      <c r="B16" s="79">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C16" s="119">
-        <v>1.044</v>
-      </c>
-      <c r="D16" s="100">
-        <v>67.3</v>
-      </c>
-      <c r="E16" s="99"/>
-      <c r="F16" s="99"/>
-      <c r="G16" s="99">
-        <f t="shared" si="0"/>
-        <v>67.3</v>
-      </c>
-      <c r="S16" s="111" t="s">
-        <v>163</v>
-      </c>
-      <c r="T16" s="111" t="s">
-        <v>156</v>
-      </c>
-      <c r="U16" s="111">
-        <v>1765.15</v>
-      </c>
-      <c r="V16" s="111">
-        <v>642.66</v>
-      </c>
-      <c r="W16" s="112">
-        <f t="shared" si="1"/>
-        <v>2407.81</v>
-      </c>
-      <c r="X16" s="113"/>
-      <c r="Y16" s="111">
-        <v>1762.76</v>
-      </c>
-      <c r="Z16" s="111">
-        <v>642.66</v>
-      </c>
-      <c r="AA16" s="112">
-        <f t="shared" si="2"/>
-        <v>2405.42</v>
-      </c>
-      <c r="AB16" s="113"/>
-      <c r="AC16" s="114">
-        <f t="shared" si="3"/>
-        <v>2.3899999999998727</v>
-      </c>
-      <c r="AD16" s="113"/>
-    </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A17" s="79">
-        <v>14</v>
-      </c>
-      <c r="B17" s="79">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C17" s="119">
-        <v>1.046</v>
-      </c>
-      <c r="D17" s="100">
-        <f>185.78+30</f>
-        <v>215.78</v>
-      </c>
-      <c r="E17" s="99"/>
-      <c r="F17" s="99"/>
-      <c r="G17" s="99">
-        <f t="shared" si="0"/>
-        <v>215.78</v>
-      </c>
-      <c r="J17" s="106" t="s">
-        <v>161</v>
-      </c>
-      <c r="K17" s="106" t="s">
-        <v>156</v>
-      </c>
-      <c r="L17" s="107">
-        <v>1469.99</v>
-      </c>
-      <c r="M17" s="106">
-        <v>1225.93</v>
-      </c>
-      <c r="N17" s="107">
-        <f>SUM(L17:M17)</f>
-        <v>2695.92</v>
-      </c>
-      <c r="S17" s="106"/>
-      <c r="T17" s="106" t="s">
-        <v>166</v>
-      </c>
-      <c r="U17" s="106"/>
-      <c r="V17" s="106">
-        <v>182.74</v>
-      </c>
-      <c r="W17" s="107">
-        <f t="shared" si="1"/>
-        <v>182.74</v>
-      </c>
-      <c r="Y17" s="109"/>
-      <c r="Z17" s="109">
-        <v>182.74</v>
-      </c>
-      <c r="AA17" s="110">
-        <f t="shared" si="2"/>
-        <v>182.74</v>
-      </c>
-      <c r="AC17" s="101">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A18" s="79">
-        <v>15</v>
-      </c>
-      <c r="B18" s="79">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C18" s="119">
-        <v>1.0449999999999999</v>
-      </c>
-      <c r="D18" s="100">
-        <f>372.12-D17+20</f>
-        <v>176.34</v>
-      </c>
-      <c r="E18" s="99"/>
-      <c r="F18" s="99"/>
-      <c r="G18" s="99">
-        <f t="shared" si="0"/>
-        <v>176.34</v>
-      </c>
-      <c r="J18" s="111"/>
-      <c r="K18" s="111" t="s">
-        <v>157</v>
-      </c>
-      <c r="L18" s="111" t="s">
-        <v>164</v>
-      </c>
-      <c r="M18" s="111">
-        <v>378.74</v>
-      </c>
-      <c r="N18" s="112">
-        <f t="shared" ref="N18:N21" si="4">SUM(L18:M18)</f>
-        <v>378.74</v>
-      </c>
-      <c r="S18" s="111"/>
-      <c r="T18" s="111" t="s">
-        <v>157</v>
-      </c>
-      <c r="U18" s="111">
-        <v>49.99</v>
-      </c>
-      <c r="V18" s="111">
-        <v>189.76</v>
-      </c>
-      <c r="W18" s="112">
-        <f t="shared" si="1"/>
-        <v>239.75</v>
-      </c>
-      <c r="X18" s="113"/>
-      <c r="Y18" s="111">
-        <v>51.07</v>
-      </c>
-      <c r="Z18" s="111">
-        <v>193.9</v>
-      </c>
-      <c r="AA18" s="112">
-        <f t="shared" si="2"/>
-        <v>244.97</v>
-      </c>
-      <c r="AB18" s="113"/>
-      <c r="AC18" s="114">
-        <f t="shared" si="3"/>
-        <v>-5.2199999999999989</v>
-      </c>
-      <c r="AD18" s="113"/>
-    </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A19" s="79">
-        <v>16</v>
-      </c>
-      <c r="B19" s="79">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C19" s="119">
-        <v>1.0489999999999999</v>
-      </c>
-      <c r="D19" s="100">
-        <f>VLOOKUP($C19,Лист5!$A$1:$B$104,2,)+15</f>
-        <v>167.54</v>
-      </c>
-      <c r="E19" s="99"/>
-      <c r="F19" s="99"/>
-      <c r="G19" s="99">
-        <f t="shared" si="0"/>
-        <v>167.54</v>
-      </c>
-      <c r="J19" s="106"/>
-      <c r="K19" s="106" t="s">
-        <v>158</v>
-      </c>
-      <c r="L19" s="106" t="s">
-        <v>164</v>
-      </c>
-      <c r="M19" s="106" t="s">
-        <v>164</v>
-      </c>
-      <c r="N19" s="107">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S19" s="106"/>
-      <c r="T19" s="106" t="s">
-        <v>158</v>
-      </c>
-      <c r="U19" s="106" t="s">
-        <v>164</v>
-      </c>
-      <c r="V19" s="106" t="s">
-        <v>164</v>
-      </c>
-      <c r="W19" s="107">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y19" s="109">
-        <v>60.25</v>
-      </c>
-      <c r="Z19" s="109" t="s">
-        <v>164</v>
-      </c>
-      <c r="AA19" s="110">
-        <f t="shared" si="2"/>
-        <v>60.25</v>
-      </c>
-      <c r="AC19" s="101">
-        <f t="shared" si="3"/>
-        <v>-60.25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A20" s="79">
-        <v>17</v>
-      </c>
-      <c r="B20" s="79">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C20" s="119">
-        <v>1.05</v>
-      </c>
-      <c r="D20" s="100">
-        <f>VLOOKUP($C20,Лист5!$A$1:$B$104,2,)+3</f>
-        <v>88.4</v>
-      </c>
-      <c r="E20" s="99"/>
-      <c r="F20" s="99"/>
-      <c r="G20" s="99">
-        <f t="shared" si="0"/>
-        <v>88.4</v>
-      </c>
-      <c r="J20" s="111"/>
-      <c r="K20" s="111" t="s">
-        <v>159</v>
-      </c>
-      <c r="L20" s="112">
-        <v>13.59</v>
-      </c>
-      <c r="M20" s="111">
-        <v>1.8</v>
-      </c>
-      <c r="N20" s="112">
-        <f t="shared" si="4"/>
-        <v>15.39</v>
-      </c>
-      <c r="S20" s="111"/>
-      <c r="T20" s="111" t="s">
-        <v>159</v>
-      </c>
-      <c r="U20" s="111">
-        <v>17.940000000000001</v>
-      </c>
-      <c r="V20" s="111"/>
-      <c r="W20" s="112">
-        <f t="shared" si="1"/>
-        <v>17.940000000000001</v>
-      </c>
-      <c r="X20" s="113"/>
-      <c r="Y20" s="111" t="s">
-        <v>164</v>
-      </c>
-      <c r="Z20" s="111" t="s">
-        <v>164</v>
-      </c>
-      <c r="AA20" s="112">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AB20" s="113"/>
-      <c r="AC20" s="114">
-        <f t="shared" si="3"/>
-        <v>17.940000000000001</v>
-      </c>
-      <c r="AD20" s="113"/>
-    </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A21" s="79">
-        <v>18</v>
-      </c>
-      <c r="B21" s="79">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C21" s="119">
-        <v>1.0509999999999999</v>
-      </c>
-      <c r="D21" s="100">
-        <f>VLOOKUP($C21,Лист5!$A$1:$B$104,2,)+3</f>
-        <v>91.85</v>
-      </c>
-      <c r="E21" s="99"/>
-      <c r="F21" s="99"/>
-      <c r="G21" s="99">
-        <f t="shared" si="0"/>
-        <v>91.85</v>
-      </c>
-      <c r="J21" s="106"/>
-      <c r="K21" s="106" t="s">
-        <v>160</v>
-      </c>
-      <c r="L21" s="106">
-        <v>2.4</v>
-      </c>
-      <c r="M21" s="106" t="s">
-        <v>164</v>
-      </c>
-      <c r="N21" s="107">
-        <f t="shared" si="4"/>
-        <v>2.4</v>
-      </c>
-      <c r="S21" s="106"/>
-      <c r="T21" s="106" t="s">
-        <v>160</v>
-      </c>
-      <c r="U21" s="106">
-        <v>3.6</v>
-      </c>
-      <c r="V21" s="106"/>
-      <c r="W21" s="107">
-        <f t="shared" si="1"/>
-        <v>3.6</v>
-      </c>
-      <c r="Y21" s="109" t="s">
-        <v>164</v>
-      </c>
-      <c r="Z21" s="109" t="s">
-        <v>164</v>
-      </c>
-      <c r="AA21" s="110">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC21" s="101">
-        <f t="shared" si="3"/>
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A22" s="79">
-        <v>19</v>
-      </c>
-      <c r="B22" s="79">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C22" s="119">
-        <v>1.048</v>
-      </c>
-      <c r="D22" s="99"/>
-      <c r="E22" s="100">
-        <f>VLOOKUP($C22,Лист5!$A$1:$B$104,2,)</f>
-        <v>75.8</v>
-      </c>
-      <c r="F22" s="99"/>
-      <c r="G22" s="99">
-        <f t="shared" si="0"/>
-        <v>75.8</v>
-      </c>
-      <c r="S22" s="113"/>
-      <c r="T22" s="113"/>
-      <c r="U22" s="113"/>
-      <c r="V22" s="113"/>
-      <c r="W22" s="113"/>
-      <c r="X22" s="113"/>
-      <c r="Y22" s="113"/>
-      <c r="Z22" s="113"/>
-      <c r="AA22" s="113"/>
-      <c r="AB22" s="113"/>
-      <c r="AC22" s="113"/>
-      <c r="AD22" s="113"/>
-    </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A23" s="79">
-        <v>20</v>
-      </c>
-      <c r="B23" s="79">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C23" s="119">
-        <v>1.0529999999999999</v>
-      </c>
-      <c r="D23" s="99"/>
-      <c r="E23" s="100">
-        <v>254.19</v>
-      </c>
-      <c r="F23" s="99"/>
-      <c r="G23" s="99">
-        <f t="shared" si="0"/>
-        <v>254.19</v>
-      </c>
-      <c r="S23" s="105"/>
-      <c r="T23" s="106" t="s">
-        <v>165</v>
-      </c>
-      <c r="U23" s="107">
-        <f>SUM(U4:U21)</f>
-        <v>4929.96</v>
-      </c>
-      <c r="V23" s="107">
-        <f>SUM(V4:V21)</f>
-        <v>5026.41</v>
-      </c>
-      <c r="W23" s="107">
-        <f t="shared" si="1"/>
-        <v>9956.369999999999</v>
-      </c>
-      <c r="Y23" s="110">
-        <f>SUM(Y4:Y21)</f>
-        <v>5049.75</v>
-      </c>
-      <c r="Z23" s="110">
-        <f>SUM(Z4:Z21)</f>
-        <v>5018.33</v>
-      </c>
-      <c r="AA23" s="110">
-        <f t="shared" ref="AA23" si="5">SUM(Y23:Z23)</f>
-        <v>10068.08</v>
-      </c>
-      <c r="AC23" s="101">
-        <f>W23-AA23</f>
-        <v>-111.71000000000095</v>
-      </c>
-    </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A24" s="79">
-        <v>21</v>
-      </c>
-      <c r="B24" s="79">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C24" s="119">
-        <v>1.054</v>
-      </c>
-      <c r="D24" s="99"/>
-      <c r="E24" s="100">
-        <f>26+8+8.48</f>
-        <v>42.480000000000004</v>
-      </c>
-      <c r="F24" s="99"/>
-      <c r="G24" s="99">
-        <f t="shared" si="0"/>
-        <v>42.480000000000004</v>
-      </c>
-    </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A25" s="79"/>
-      <c r="B25" s="79"/>
-      <c r="C25" s="79" t="s">
-        <v>19</v>
-      </c>
-      <c r="D25" s="99">
-        <f>SUM(D4:D24)</f>
-        <v>2473.91</v>
-      </c>
-      <c r="E25" s="99">
-        <f>SUM(E4:E24)</f>
-        <v>372.47</v>
-      </c>
-      <c r="F25" s="99">
-        <f t="shared" ref="F25:G25" si="6">SUM(F4:F24)</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="99">
-        <f t="shared" si="6"/>
-        <v>2846.38</v>
-      </c>
-    </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="B28" s="93" t="s">
-        <v>154</v>
-      </c>
-      <c r="C28" s="130"/>
-      <c r="D28" s="95" t="s">
-        <v>150</v>
-      </c>
-      <c r="E28" s="96" t="s">
-        <v>152</v>
-      </c>
-      <c r="F28" s="96" t="s">
-        <v>153</v>
-      </c>
-      <c r="J28" s="132" t="s">
-        <v>154</v>
-      </c>
-      <c r="K28" s="130"/>
-      <c r="L28" s="95" t="s">
-        <v>150</v>
-      </c>
-      <c r="M28" s="96" t="s">
-        <v>152</v>
-      </c>
-      <c r="N28" s="96" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="B29" s="130">
-        <v>1</v>
-      </c>
-      <c r="C29" s="130"/>
-      <c r="D29" s="131">
-        <f>SUM(D4:D13)</f>
-        <v>1348.45</v>
-      </c>
-      <c r="E29" s="131">
-        <v>0</v>
-      </c>
-      <c r="F29" s="131">
-        <f>F22</f>
-        <v>0</v>
-      </c>
-      <c r="J29" s="130">
-        <v>1</v>
-      </c>
-      <c r="K29" s="130"/>
-      <c r="L29" s="131">
-        <f>L17</f>
-        <v>1469.99</v>
-      </c>
-      <c r="M29" s="131" t="str">
-        <f>L18</f>
-        <v>-</v>
-      </c>
-      <c r="N29" s="131">
-        <f>N22</f>
-        <v>0</v>
-      </c>
-      <c r="P29" s="101">
-        <f>L29-D29</f>
-        <v>121.53999999999996</v>
-      </c>
-      <c r="Q29" s="101" t="e">
-        <f>M29-E29</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="B30" s="130">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C30" s="130"/>
-      <c r="D30" s="131">
-        <f>SUM(D14:D21)</f>
-        <v>1125.46</v>
-      </c>
-      <c r="E30" s="131">
-        <f>SUM(E22:E24)</f>
-        <v>372.47</v>
-      </c>
-      <c r="F30" s="131">
-        <f>SUM(F23:F25)</f>
-        <v>0</v>
-      </c>
-      <c r="J30" s="130">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="K30" s="130"/>
-      <c r="L30" s="131">
-        <f>M17</f>
-        <v>1225.93</v>
-      </c>
-      <c r="M30" s="131">
-        <f>M18</f>
-        <v>378.74</v>
-      </c>
-      <c r="N30" s="131">
-        <f>SUM(N23:N25)</f>
-        <v>0</v>
-      </c>
-      <c r="P30" s="101">
-        <f>L30-D30</f>
-        <v>100.47000000000003</v>
-      </c>
-      <c r="Q30" s="101">
-        <f>M30-E30</f>
-        <v>6.2699999999999818</v>
-      </c>
-    </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A32" s="142" t="s">
-        <v>2</v>
-      </c>
-      <c r="B32" s="142"/>
-      <c r="C32" s="142"/>
-      <c r="D32" s="142"/>
-      <c r="E32" s="142"/>
-      <c r="F32" s="142"/>
-      <c r="G32" s="142"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="79"/>
-      <c r="B33" s="79"/>
-      <c r="C33" s="94"/>
-      <c r="D33" s="95" t="s">
-        <v>150</v>
-      </c>
-      <c r="E33" s="96" t="s">
-        <v>152</v>
-      </c>
-      <c r="F33" s="96" t="s">
-        <v>153</v>
-      </c>
-      <c r="G33" s="80" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="B34" s="79" t="s">
-        <v>154</v>
-      </c>
-      <c r="C34" s="97" t="s">
-        <v>5</v>
-      </c>
-      <c r="D34" s="98" t="s">
-        <v>4</v>
-      </c>
-      <c r="E34" s="98" t="s">
-        <v>4</v>
-      </c>
-      <c r="F34" s="98" t="s">
-        <v>4</v>
-      </c>
-      <c r="G34" s="99" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="79">
-        <v>1</v>
-      </c>
-      <c r="B35" s="102">
-        <v>1</v>
-      </c>
-      <c r="C35" s="104">
-        <v>2.0009999999999999</v>
-      </c>
-      <c r="D35" s="100">
-        <f>VLOOKUP($C35,Лист5!$A$1:$B$104,2,)</f>
-        <v>118.17750000000001</v>
-      </c>
-      <c r="E35" s="103"/>
-      <c r="F35" s="103"/>
-      <c r="G35" s="99">
-        <f>SUM(D35:F35)</f>
-        <v>118.17750000000001</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="79">
-        <v>2</v>
-      </c>
-      <c r="B36" s="102">
-        <v>1</v>
-      </c>
-      <c r="C36" s="104">
-        <v>2.0019999999999998</v>
-      </c>
-      <c r="D36" s="100">
-        <f>VLOOKUP($C36,Лист5!$A$1:$B$104,2,)</f>
-        <v>113.73599999999999</v>
-      </c>
-      <c r="E36" s="103"/>
-      <c r="F36" s="103"/>
-      <c r="G36" s="99">
-        <f t="shared" ref="G36:G57" si="7">SUM(D36:F36)</f>
-        <v>113.73599999999999</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="79">
-        <v>3</v>
-      </c>
-      <c r="B37" s="102">
-        <v>1</v>
-      </c>
-      <c r="C37" s="104">
-        <v>2.0030000000000001</v>
-      </c>
-      <c r="D37" s="100">
-        <f>VLOOKUP($C37,Лист5!$A$1:$B$104,2,)</f>
-        <v>122.50349999999997</v>
-      </c>
-      <c r="E37" s="103"/>
-      <c r="F37" s="103"/>
-      <c r="G37" s="99">
-        <f t="shared" si="7"/>
-        <v>122.50349999999997</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="79">
-        <v>4</v>
-      </c>
-      <c r="B38" s="102">
-        <v>1</v>
-      </c>
-      <c r="C38" s="104">
-        <v>2.004</v>
-      </c>
-      <c r="D38" s="100">
-        <f>VLOOKUP($C38,Лист5!$A$1:$B$104,2,)</f>
-        <v>314.601</v>
-      </c>
-      <c r="E38" s="103"/>
-      <c r="F38" s="103"/>
-      <c r="G38" s="99">
-        <f t="shared" si="7"/>
-        <v>314.601</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="79">
-        <v>5</v>
-      </c>
-      <c r="B39" s="102">
-        <v>1</v>
-      </c>
-      <c r="C39" s="104">
-        <v>2.0070000000000001</v>
-      </c>
-      <c r="D39" s="100">
-        <f>VLOOKUP($C39,Лист5!$A$1:$B$104,2,)</f>
-        <v>106.77449999999999</v>
-      </c>
-      <c r="E39" s="103"/>
-      <c r="F39" s="103"/>
-      <c r="G39" s="99">
-        <f t="shared" si="7"/>
-        <v>106.77449999999999</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="79">
-        <v>6</v>
-      </c>
-      <c r="B40" s="102">
-        <v>1</v>
-      </c>
-      <c r="C40" s="104">
-        <v>2.008</v>
-      </c>
-      <c r="D40" s="100">
-        <f>VLOOKUP($C40,Лист5!$A$1:$B$104,2,)</f>
-        <v>111.50999999999999</v>
-      </c>
-      <c r="E40" s="103"/>
-      <c r="F40" s="103"/>
-      <c r="G40" s="99">
-        <f t="shared" si="7"/>
-        <v>111.50999999999999</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="79">
-        <v>7</v>
-      </c>
-      <c r="B41" s="102">
-        <v>1</v>
-      </c>
-      <c r="C41" s="104">
-        <v>2.0089999999999999</v>
-      </c>
-      <c r="D41" s="100">
-        <f>VLOOKUP($C41,Лист5!$A$1:$B$104,2,)</f>
-        <v>106.77449999999999</v>
-      </c>
-      <c r="E41" s="103"/>
-      <c r="F41" s="103"/>
-      <c r="G41" s="99">
-        <f t="shared" si="7"/>
-        <v>106.77449999999999</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="79">
-        <v>8</v>
-      </c>
-      <c r="B42" s="102">
-        <v>1</v>
-      </c>
-      <c r="C42" s="115">
-        <v>2.0099999999999998</v>
-      </c>
-      <c r="D42" s="100">
-        <f>VLOOKUP($C42,Лист5!$A$1:$B$104,2,)</f>
-        <v>93.03</v>
-      </c>
-      <c r="E42" s="103"/>
-      <c r="F42" s="103"/>
-      <c r="G42" s="99">
-        <f t="shared" si="7"/>
-        <v>93.03</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="79">
-        <v>9</v>
-      </c>
-      <c r="B43" s="102">
-        <v>1</v>
-      </c>
-      <c r="C43" s="104">
-        <v>2.0110000000000001</v>
-      </c>
-      <c r="D43" s="100">
-        <f>VLOOKUP($C43,Лист5!$A$1:$B$104,2,)</f>
-        <v>106.63800000000001</v>
-      </c>
-      <c r="E43" s="103"/>
-      <c r="F43" s="103"/>
-      <c r="G43" s="99">
-        <f t="shared" si="7"/>
-        <v>106.63800000000001</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="79">
-        <v>10</v>
-      </c>
-      <c r="B44" s="102">
-        <v>1</v>
-      </c>
-      <c r="C44" s="104">
-        <v>2.012</v>
-      </c>
-      <c r="D44" s="100">
-        <f>VLOOKUP($C44,Лист5!$A$1:$B$104,2,)</f>
-        <v>234.72750000000002</v>
-      </c>
-      <c r="E44" s="103"/>
-      <c r="F44" s="103"/>
-      <c r="G44" s="99">
-        <f t="shared" si="7"/>
-        <v>234.72750000000002</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="79">
-        <v>11</v>
-      </c>
-      <c r="B45" s="102">
-        <v>1</v>
-      </c>
-      <c r="C45" s="104">
-        <v>2.0129999999999999</v>
-      </c>
-      <c r="D45" s="100">
-        <f>VLOOKUP($C45,Лист5!$A$1:$B$104,2,)</f>
-        <v>83.201999999999998</v>
-      </c>
-      <c r="E45" s="103"/>
-      <c r="F45" s="103"/>
-      <c r="G45" s="99">
-        <f t="shared" si="7"/>
-        <v>83.201999999999998</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="79">
-        <v>12</v>
-      </c>
-      <c r="B46" s="102">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C46" s="104">
-        <v>2.0750000000000002</v>
-      </c>
-      <c r="D46" s="100">
-        <f>VLOOKUP($C46,Лист5!$A$1:$B$104,2,)+19</f>
-        <v>303.05650000000003</v>
-      </c>
-      <c r="E46" s="103"/>
-      <c r="F46" s="103"/>
-      <c r="G46" s="99">
-        <f t="shared" si="7"/>
-        <v>303.05650000000003</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="79">
-        <v>13</v>
-      </c>
-      <c r="B47" s="102">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C47" s="115">
-        <v>2.08</v>
-      </c>
-      <c r="D47" s="100">
-        <f>447.447/2+20</f>
-        <v>243.7235</v>
-      </c>
-      <c r="E47" s="103"/>
-      <c r="F47" s="103"/>
-      <c r="G47" s="99">
-        <f t="shared" si="7"/>
-        <v>243.7235</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" s="79">
-        <v>14</v>
-      </c>
-      <c r="B48" s="102">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C48" s="104">
-        <v>2.081</v>
-      </c>
-      <c r="D48" s="100">
-        <f>VLOOKUP($C48,Лист5!$A$1:$B$104,2,)+210</f>
-        <v>637.24</v>
-      </c>
-      <c r="E48" s="103"/>
-      <c r="F48" s="103"/>
-      <c r="G48" s="99">
-        <f t="shared" si="7"/>
-        <v>637.24</v>
-      </c>
-    </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A49" s="79">
-        <v>15</v>
-      </c>
-      <c r="B49" s="102">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C49" s="104">
-        <v>2.0819999999999999</v>
-      </c>
-      <c r="D49" s="100">
-        <f>447.447/2-30</f>
-        <v>193.7235</v>
-      </c>
-      <c r="E49" s="103"/>
-      <c r="F49" s="103"/>
-      <c r="G49" s="99">
-        <f t="shared" si="7"/>
-        <v>193.7235</v>
-      </c>
-      <c r="J49" s="106" t="s">
-        <v>162</v>
-      </c>
-      <c r="K49" s="106" t="s">
-        <v>156</v>
-      </c>
-      <c r="L49" s="106">
-        <v>1537.74</v>
-      </c>
-      <c r="M49" s="106">
-        <v>1995.77</v>
-      </c>
-      <c r="N49" s="107">
-        <f>SUM(L49:M49)</f>
-        <v>3533.51</v>
-      </c>
-      <c r="P49" s="109">
-        <v>1537.34</v>
-      </c>
-      <c r="Q49" s="109">
-        <v>1673.16</v>
-      </c>
-      <c r="R49" s="110">
-        <f t="shared" ref="R49:R53" si="8">SUM(P49:Q49)</f>
-        <v>3210.5</v>
-      </c>
-      <c r="T49" s="101">
-        <f>N49-R49</f>
-        <v>323.01000000000022</v>
-      </c>
-    </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A50" s="79">
-        <v>16</v>
-      </c>
-      <c r="B50" s="102">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C50" s="104">
-        <v>2.085</v>
-      </c>
-      <c r="D50" s="100">
-        <f>VLOOKUP($C50,Лист5!$A$1:$B$104,2,)+160</f>
-        <v>479.92</v>
-      </c>
-      <c r="E50" s="103"/>
-      <c r="F50" s="103"/>
-      <c r="G50" s="99">
-        <f t="shared" si="7"/>
-        <v>479.92</v>
-      </c>
-      <c r="J50" s="111"/>
-      <c r="K50" s="111" t="s">
-        <v>157</v>
-      </c>
-      <c r="L50" s="111">
-        <v>51.07</v>
-      </c>
-      <c r="M50" s="111">
-        <v>409.01</v>
-      </c>
-      <c r="N50" s="112">
-        <f>SUM(L50:M50)</f>
-        <v>460.08</v>
-      </c>
-      <c r="O50" s="113"/>
-      <c r="P50" s="111">
-        <v>51.07</v>
-      </c>
-      <c r="Q50" s="111">
-        <v>409.01</v>
-      </c>
-      <c r="R50" s="112">
-        <f t="shared" si="8"/>
-        <v>460.08</v>
-      </c>
-      <c r="S50" s="113"/>
-      <c r="T50" s="114">
-        <f>N50-R50</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A51" s="79">
-        <v>17</v>
-      </c>
-      <c r="B51" s="102">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C51" s="104">
-        <v>2.0880000000000001</v>
-      </c>
-      <c r="D51" s="100">
-        <f>VLOOKUP($C51,Лист5!$A$1:$B$104,2,)+8</f>
-        <v>61.171999999999997</v>
-      </c>
-      <c r="E51" s="103"/>
-      <c r="F51" s="103"/>
-      <c r="G51" s="99">
-        <f t="shared" si="7"/>
-        <v>61.171999999999997</v>
-      </c>
-      <c r="J51" s="106"/>
-      <c r="K51" s="106" t="s">
-        <v>158</v>
-      </c>
-      <c r="L51" s="106" t="s">
-        <v>164</v>
-      </c>
-      <c r="M51" s="106" t="s">
-        <v>164</v>
-      </c>
-      <c r="N51" s="107">
-        <f>SUM(L51:M51)</f>
-        <v>0</v>
-      </c>
-      <c r="P51" s="109">
-        <v>60.14</v>
-      </c>
-      <c r="Q51" s="109">
-        <v>338.43</v>
-      </c>
-      <c r="R51" s="110">
-        <f t="shared" si="8"/>
-        <v>398.57</v>
-      </c>
-      <c r="T51" s="101">
-        <f>N51-R51</f>
-        <v>-398.57</v>
-      </c>
-    </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A52" s="135">
-        <v>18</v>
-      </c>
-      <c r="B52" s="135">
-        <v>1</v>
-      </c>
-      <c r="C52" s="136">
-        <v>2.0049999999999999</v>
-      </c>
-      <c r="D52" s="137"/>
-      <c r="E52" s="137">
-        <v>48.22</v>
-      </c>
-      <c r="F52" s="137"/>
-      <c r="G52" s="137">
-        <f t="shared" si="7"/>
-        <v>48.22</v>
-      </c>
-      <c r="J52" s="111"/>
-      <c r="K52" s="111" t="s">
-        <v>159</v>
-      </c>
-      <c r="L52" s="111">
-        <v>16.09</v>
-      </c>
-      <c r="M52" s="111" t="s">
-        <v>164</v>
-      </c>
-      <c r="N52" s="112">
-        <f>SUM(L52:M52)</f>
-        <v>16.09</v>
-      </c>
-      <c r="O52" s="113"/>
-      <c r="P52" s="111" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q52" s="111" t="s">
-        <v>164</v>
-      </c>
-      <c r="R52" s="112">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="S52" s="113"/>
-      <c r="T52" s="114">
-        <f>N52-R52</f>
-        <v>16.09</v>
-      </c>
-    </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A53" s="79">
-        <v>19</v>
-      </c>
-      <c r="B53" s="102">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C53" s="115">
-        <v>2.0840000000000001</v>
-      </c>
-      <c r="D53" s="117"/>
-      <c r="E53" s="100">
-        <f>VLOOKUP($C53,Лист5!$A$1:$B$104,2,)</f>
-        <v>77.849999999999994</v>
-      </c>
-      <c r="F53" s="103"/>
-      <c r="G53" s="99">
-        <f t="shared" si="7"/>
-        <v>77.849999999999994</v>
-      </c>
-      <c r="J53" s="106"/>
-      <c r="K53" s="106" t="s">
-        <v>160</v>
-      </c>
-      <c r="L53" s="106">
-        <v>2.4</v>
-      </c>
-      <c r="M53" s="106" t="s">
-        <v>164</v>
-      </c>
-      <c r="N53" s="107">
-        <f>SUM(L53:M53)</f>
-        <v>2.4</v>
-      </c>
-      <c r="P53" s="109" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q53" s="109" t="s">
-        <v>164</v>
-      </c>
-      <c r="R53" s="110">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="T53" s="101">
-        <f>N53-R53</f>
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A54" s="79">
-        <v>20</v>
-      </c>
-      <c r="B54" s="102">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C54" s="115">
-        <v>2.0870000000000002</v>
-      </c>
-      <c r="D54" s="117"/>
-      <c r="E54" s="100">
-        <f>VLOOKUP($C54,Лист5!$A$1:$B$104,2,)</f>
-        <v>83.33</v>
-      </c>
-      <c r="F54" s="103"/>
-      <c r="G54" s="99">
-        <f t="shared" si="7"/>
-        <v>83.33</v>
-      </c>
-    </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A55" s="79">
-        <v>21</v>
-      </c>
-      <c r="B55" s="102">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C55" s="115">
-        <v>2.109</v>
-      </c>
-      <c r="D55" s="117"/>
-      <c r="E55" s="100">
-        <f>VLOOKUP($C55,Лист5!$A$1:$B$104,2,)</f>
-        <v>105.714</v>
-      </c>
-      <c r="F55" s="103"/>
-      <c r="G55" s="99">
-        <f t="shared" si="7"/>
-        <v>105.714</v>
-      </c>
-    </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A56" s="135">
-        <v>22</v>
-      </c>
-      <c r="B56" s="135">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C56" s="136">
-        <v>2.16</v>
-      </c>
-      <c r="D56" s="138"/>
-      <c r="E56" s="137">
-        <f>VLOOKUP($C56,Лист5!$A$1:$B$104,2,)</f>
-        <v>78.209999999999994</v>
-      </c>
-      <c r="F56" s="137"/>
-      <c r="G56" s="137">
-        <f t="shared" si="7"/>
-        <v>78.209999999999994</v>
-      </c>
-    </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A57" s="79">
-        <v>23</v>
-      </c>
-      <c r="B57" s="102">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C57" s="115">
-        <v>2.1680000000000001</v>
-      </c>
-      <c r="D57" s="117"/>
-      <c r="E57" s="100">
-        <f>VLOOKUP($C57,Лист5!$A$1:$B$104,2,)</f>
-        <v>42</v>
-      </c>
-      <c r="F57" s="103"/>
-      <c r="G57" s="99">
-        <f t="shared" si="7"/>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A58" s="79"/>
-      <c r="B58" s="79"/>
-      <c r="C58" s="79" t="s">
-        <v>19</v>
-      </c>
-      <c r="D58" s="99">
-        <f t="shared" ref="D58:E58" si="9">SUM(D35:D57)</f>
-        <v>3430.5099999999998</v>
-      </c>
-      <c r="E58" s="99">
-        <f t="shared" si="9"/>
-        <v>435.32399999999996</v>
-      </c>
-      <c r="F58" s="99">
-        <f>SUM(F35:F57)</f>
-        <v>0</v>
-      </c>
-      <c r="G58" s="99">
-        <f>SUM(G35:G51)</f>
-        <v>3430.5099999999998</v>
-      </c>
-    </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="B60" s="93" t="s">
-        <v>154</v>
-      </c>
-      <c r="C60" s="130"/>
-      <c r="D60" s="95" t="s">
-        <v>150</v>
-      </c>
-      <c r="E60" s="96" t="s">
-        <v>152</v>
-      </c>
-      <c r="F60" s="96" t="s">
-        <v>153</v>
-      </c>
-      <c r="J60" s="132" t="s">
-        <v>154</v>
-      </c>
-      <c r="K60" s="130"/>
-      <c r="L60" s="95" t="s">
-        <v>150</v>
-      </c>
-      <c r="M60" s="96" t="s">
-        <v>152</v>
-      </c>
-      <c r="N60" s="96" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="B61" s="130">
-        <v>1</v>
-      </c>
-      <c r="C61" s="130"/>
-      <c r="D61" s="131">
-        <f>SUM(D35:D45)</f>
-        <v>1511.6744999999999</v>
-      </c>
-      <c r="E61" s="131">
-        <f>E52</f>
-        <v>48.22</v>
-      </c>
-      <c r="F61" s="131">
-        <f>F54</f>
-        <v>0</v>
-      </c>
-      <c r="J61" s="130">
-        <v>1</v>
-      </c>
-      <c r="K61" s="130"/>
-      <c r="L61" s="131">
-        <f>L49</f>
-        <v>1537.74</v>
-      </c>
-      <c r="M61" s="131">
-        <f>L50</f>
-        <v>51.07</v>
-      </c>
-      <c r="N61" s="131">
-        <f>N54</f>
-        <v>0</v>
-      </c>
-      <c r="P61" s="101">
-        <f>L61-D61</f>
-        <v>26.065500000000156</v>
-      </c>
-      <c r="Q61" s="101">
-        <f>M61-E61</f>
-        <v>2.8500000000000014</v>
-      </c>
-    </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="B62" s="130">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C62" s="130"/>
-      <c r="D62" s="131">
-        <f>SUM(D46:D51)</f>
-        <v>1918.8355000000001</v>
-      </c>
-      <c r="E62" s="131">
-        <f>SUM(E53:E57)</f>
-        <v>387.10399999999998</v>
-      </c>
-      <c r="F62" s="131">
-        <f>SUM(F55:F57)</f>
-        <v>0</v>
-      </c>
-      <c r="J62" s="130">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="K62" s="130"/>
-      <c r="L62" s="131">
-        <f>M49</f>
-        <v>1995.77</v>
-      </c>
-      <c r="M62" s="131">
-        <f>M50</f>
-        <v>409.01</v>
-      </c>
-      <c r="N62" s="131">
-        <f>SUM(N55:N57)</f>
-        <v>0</v>
-      </c>
-      <c r="P62" s="101">
-        <f>L62-D62</f>
-        <v>76.934499999999844</v>
-      </c>
-      <c r="Q62" s="101">
-        <f>M62-E62</f>
-        <v>21.906000000000006</v>
-      </c>
-    </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="D63" s="101"/>
-      <c r="E63" s="101"/>
-      <c r="F63" s="101"/>
-    </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="D64" s="101"/>
-      <c r="E64" s="101"/>
-      <c r="F64" s="101"/>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D65" s="101"/>
-      <c r="E65" s="101"/>
-      <c r="F65" s="101"/>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D66" s="101"/>
-      <c r="E66" s="101"/>
-      <c r="F66" s="101"/>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A67" s="142" t="s">
-        <v>2</v>
-      </c>
-      <c r="B67" s="142"/>
-      <c r="C67" s="142"/>
-      <c r="D67" s="142"/>
-      <c r="E67" s="142"/>
-      <c r="F67" s="142"/>
-      <c r="G67" s="142"/>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A68" s="79"/>
-      <c r="B68" s="79"/>
-      <c r="C68" s="94"/>
-      <c r="D68" s="95" t="s">
-        <v>150</v>
-      </c>
-      <c r="E68" s="95" t="s">
-        <v>151</v>
-      </c>
-      <c r="F68" s="96" t="s">
-        <v>152</v>
-      </c>
-      <c r="G68" s="96" t="s">
-        <v>153</v>
-      </c>
-      <c r="H68" s="80" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A69" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="B69" s="79" t="s">
-        <v>154</v>
-      </c>
-      <c r="C69" s="97" t="s">
-        <v>5</v>
-      </c>
-      <c r="D69" s="98" t="s">
-        <v>4</v>
-      </c>
-      <c r="E69" s="98" t="s">
-        <v>4</v>
-      </c>
-      <c r="F69" s="98" t="s">
-        <v>4</v>
-      </c>
-      <c r="G69" s="98" t="s">
-        <v>4</v>
-      </c>
-      <c r="H69" s="99" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A70" s="135">
-        <v>1</v>
-      </c>
-      <c r="B70" s="135">
-        <v>1</v>
-      </c>
-      <c r="C70" s="136">
-        <v>3.0009999999999999</v>
-      </c>
-      <c r="D70" s="137">
-        <f>VLOOKUP($C70,Лист5!$A$1:$B$104,2,)</f>
-        <v>168.78</v>
-      </c>
-      <c r="E70" s="137"/>
-      <c r="F70" s="137"/>
-      <c r="G70" s="137"/>
-      <c r="H70" s="137">
-        <f t="shared" ref="H70:H88" si="10">SUM(D70:G70)</f>
-        <v>168.78</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A71" s="135">
-        <v>2</v>
-      </c>
-      <c r="B71" s="135">
-        <v>1</v>
-      </c>
-      <c r="C71" s="136">
-        <v>3.0019999999999998</v>
-      </c>
-      <c r="D71" s="137">
-        <f>VLOOKUP($C71,Лист5!$A$1:$B$104,2,)</f>
-        <v>105.58</v>
-      </c>
-      <c r="E71" s="137"/>
-      <c r="F71" s="137"/>
-      <c r="G71" s="137"/>
-      <c r="H71" s="137">
-        <f t="shared" si="10"/>
-        <v>105.58</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A72" s="135">
-        <v>3</v>
-      </c>
-      <c r="B72" s="135">
-        <v>1</v>
-      </c>
-      <c r="C72" s="136">
-        <v>3.0030000000000001</v>
-      </c>
-      <c r="D72" s="137">
-        <f>VLOOKUP($C72,Лист5!$A$1:$B$104,2,)</f>
-        <v>105.79</v>
-      </c>
-      <c r="E72" s="137"/>
-      <c r="F72" s="137"/>
-      <c r="G72" s="137"/>
-      <c r="H72" s="137">
-        <f t="shared" si="10"/>
-        <v>105.79</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A73" s="79">
-        <v>4</v>
-      </c>
-      <c r="B73" s="79">
-        <v>1</v>
-      </c>
-      <c r="C73" s="115">
-        <v>3.004</v>
-      </c>
-      <c r="D73" s="100">
-        <f>VLOOKUP($C73,Лист5!$A$1:$B$104,2,)</f>
-        <v>116.51</v>
-      </c>
-      <c r="E73" s="103"/>
-      <c r="F73" s="103"/>
-      <c r="G73" s="103"/>
-      <c r="H73" s="99">
-        <f t="shared" si="10"/>
-        <v>116.51</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A74" s="135">
-        <v>5</v>
-      </c>
-      <c r="B74" s="135">
-        <v>1</v>
-      </c>
-      <c r="C74" s="136">
-        <v>3.0049999999999999</v>
-      </c>
-      <c r="D74" s="137">
-        <f>VLOOKUP($C74,Лист5!$A$1:$B$104,2,)</f>
-        <v>402.53</v>
-      </c>
-      <c r="E74" s="137"/>
-      <c r="F74" s="137"/>
-      <c r="G74" s="137"/>
-      <c r="H74" s="137">
-        <f t="shared" si="10"/>
-        <v>402.53</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A75" s="79">
-        <v>6</v>
-      </c>
-      <c r="B75" s="79">
-        <v>1</v>
-      </c>
-      <c r="C75" s="115">
-        <v>3.008</v>
-      </c>
-      <c r="D75" s="100">
-        <f>VLOOKUP($C75,Лист5!$A$1:$B$104,2,)</f>
-        <v>102.57</v>
-      </c>
-      <c r="E75" s="103"/>
-      <c r="F75" s="103"/>
-      <c r="G75" s="103"/>
-      <c r="H75" s="99">
-        <f t="shared" si="10"/>
-        <v>102.57</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A76" s="79">
-        <v>7</v>
-      </c>
-      <c r="B76" s="79">
-        <v>1</v>
-      </c>
-      <c r="C76" s="115">
-        <v>3.0089999999999999</v>
-      </c>
-      <c r="D76" s="100">
-        <f>VLOOKUP($C76,Лист5!$A$1:$B$104,2,)</f>
-        <v>104.69999999999999</v>
-      </c>
-      <c r="E76" s="103"/>
-      <c r="F76" s="103"/>
-      <c r="G76" s="103"/>
-      <c r="H76" s="99">
-        <f t="shared" si="10"/>
-        <v>104.69999999999999</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A77" s="79">
-        <v>8</v>
-      </c>
-      <c r="B77" s="79">
-        <v>1</v>
-      </c>
-      <c r="C77" s="115">
-        <v>3.01</v>
-      </c>
-      <c r="D77" s="100">
-        <f>VLOOKUP($C77,Лист5!$A$1:$B$104,2,)</f>
-        <v>101.61</v>
-      </c>
-      <c r="E77" s="103"/>
-      <c r="F77" s="103"/>
-      <c r="G77" s="103"/>
-      <c r="H77" s="99">
-        <f t="shared" si="10"/>
-        <v>101.61</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A78" s="79">
-        <v>9</v>
-      </c>
-      <c r="B78" s="79">
-        <v>1</v>
-      </c>
-      <c r="C78" s="115">
-        <v>3.0110000000000001</v>
-      </c>
-      <c r="D78" s="100">
-        <f>VLOOKUP($C78,Лист5!$A$1:$B$104,2,)</f>
-        <v>105.25</v>
-      </c>
-      <c r="E78" s="103"/>
-      <c r="F78" s="103"/>
-      <c r="G78" s="103"/>
-      <c r="H78" s="99">
-        <f t="shared" si="10"/>
-        <v>105.25</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A79" s="79">
-        <v>10</v>
-      </c>
-      <c r="B79" s="79">
-        <v>1</v>
-      </c>
-      <c r="C79" s="115">
-        <v>3.012</v>
-      </c>
-      <c r="D79" s="100">
-        <f>VLOOKUP($C79,Лист5!$A$1:$B$104,2,)</f>
-        <v>105.33</v>
-      </c>
-      <c r="E79" s="103"/>
-      <c r="F79" s="103"/>
-      <c r="G79" s="103"/>
-      <c r="H79" s="99">
-        <f t="shared" si="10"/>
-        <v>105.33</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A80" s="79">
-        <v>11</v>
-      </c>
-      <c r="B80" s="79">
-        <v>1</v>
-      </c>
-      <c r="C80" s="115">
-        <v>3.0129999999999999</v>
-      </c>
-      <c r="D80" s="100">
-        <f>VLOOKUP($C80,Лист5!$A$1:$B$104,2,)</f>
-        <v>101.95</v>
-      </c>
-      <c r="E80" s="103"/>
-      <c r="F80" s="103"/>
-      <c r="G80" s="103"/>
-      <c r="H80" s="99">
-        <f t="shared" si="10"/>
-        <v>101.95</v>
-      </c>
-    </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A81" s="79">
-        <v>12</v>
-      </c>
-      <c r="B81" s="79">
-        <v>1</v>
-      </c>
-      <c r="C81" s="115">
-        <v>3.0139999999999998</v>
-      </c>
-      <c r="D81" s="100">
-        <f>VLOOKUP($C81,Лист5!$A$1:$B$104,2,)</f>
-        <v>221.42</v>
-      </c>
-      <c r="E81" s="103"/>
-      <c r="F81" s="103"/>
-      <c r="G81" s="103"/>
-      <c r="H81" s="99">
-        <f t="shared" si="10"/>
-        <v>221.42</v>
-      </c>
-    </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A82" s="79">
-        <v>13</v>
-      </c>
-      <c r="B82" s="102">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C82" s="115">
-        <v>3.0190000000000001</v>
-      </c>
-      <c r="D82" s="100">
-        <f>VLOOKUP($C82,Лист5!$A$1:$B$104,2,)</f>
-        <v>283.38</v>
-      </c>
-      <c r="E82" s="103"/>
-      <c r="F82" s="103"/>
-      <c r="G82" s="103"/>
-      <c r="H82" s="99">
-        <f t="shared" si="10"/>
-        <v>283.38</v>
-      </c>
-      <c r="J82" s="111" t="s">
-        <v>163</v>
-      </c>
-      <c r="K82" s="111" t="s">
-        <v>156</v>
-      </c>
-      <c r="L82" s="111">
-        <v>1765.15</v>
-      </c>
-      <c r="M82" s="111">
-        <v>642.66</v>
-      </c>
-      <c r="N82" s="112">
-        <f t="shared" ref="N82:N87" si="11">SUM(L82:M82)</f>
-        <v>2407.81</v>
-      </c>
-      <c r="O82" s="113"/>
-      <c r="P82" s="111">
-        <v>1762.76</v>
-      </c>
-      <c r="Q82" s="111">
-        <v>642.66</v>
-      </c>
-      <c r="R82" s="112">
-        <f t="shared" ref="R82:R87" si="12">SUM(P82:Q82)</f>
-        <v>2405.42</v>
-      </c>
-      <c r="S82" s="113"/>
-      <c r="T82" s="114">
-        <f t="shared" ref="T82:T87" si="13">N82-R82</f>
-        <v>2.3899999999998727</v>
-      </c>
-    </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A83" s="79">
-        <v>14</v>
-      </c>
-      <c r="B83" s="102">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C83" s="115">
-        <v>3.02</v>
-      </c>
-      <c r="D83" s="100">
-        <f>VLOOKUP($C83,Лист5!$A$1:$B$104,2,)</f>
-        <v>317.98</v>
-      </c>
-      <c r="E83" s="103"/>
-      <c r="F83" s="103"/>
-      <c r="G83" s="103"/>
-      <c r="H83" s="99">
-        <f t="shared" si="10"/>
-        <v>317.98</v>
-      </c>
-      <c r="J83" s="106"/>
-      <c r="K83" s="106" t="s">
-        <v>166</v>
-      </c>
-      <c r="L83" s="106"/>
-      <c r="M83" s="106">
-        <v>182.74</v>
-      </c>
-      <c r="N83" s="107">
-        <f t="shared" si="11"/>
-        <v>182.74</v>
-      </c>
-      <c r="P83" s="109"/>
-      <c r="Q83" s="109">
-        <v>182.74</v>
-      </c>
-      <c r="R83" s="110">
-        <f t="shared" si="12"/>
-        <v>182.74</v>
-      </c>
-      <c r="T83" s="101">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A84" s="79">
-        <v>15</v>
-      </c>
-      <c r="B84" s="102">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C84" s="104" t="s">
-        <v>121</v>
-      </c>
-      <c r="D84" s="103"/>
-      <c r="E84" s="100">
-        <v>182.74</v>
-      </c>
-      <c r="F84" s="103"/>
-      <c r="G84" s="103"/>
-      <c r="H84" s="99">
-        <f t="shared" si="10"/>
-        <v>182.74</v>
-      </c>
-      <c r="J84" s="111"/>
-      <c r="K84" s="111" t="s">
-        <v>157</v>
-      </c>
-      <c r="L84" s="111">
-        <v>49.99</v>
-      </c>
-      <c r="M84" s="111">
-        <v>189.76</v>
-      </c>
-      <c r="N84" s="112">
-        <f t="shared" si="11"/>
-        <v>239.75</v>
-      </c>
-      <c r="O84" s="113"/>
-      <c r="P84" s="111">
-        <v>51.07</v>
-      </c>
-      <c r="Q84" s="111">
-        <v>193.9</v>
-      </c>
-      <c r="R84" s="112">
-        <f t="shared" si="12"/>
-        <v>244.97</v>
-      </c>
-      <c r="S84" s="113"/>
-      <c r="T84" s="114">
-        <f t="shared" si="13"/>
-        <v>-5.2199999999999989</v>
-      </c>
-    </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A85" s="135">
-        <v>16</v>
-      </c>
-      <c r="B85" s="135">
-        <v>1</v>
-      </c>
-      <c r="C85" s="139">
-        <v>3.0059999999999998</v>
-      </c>
-      <c r="D85" s="137"/>
-      <c r="E85" s="137"/>
-      <c r="F85" s="137">
-        <f>VLOOKUP($C85,Лист5!$A$1:$B$104,2,)</f>
-        <v>48.730000000000004</v>
-      </c>
-      <c r="G85" s="137"/>
-      <c r="H85" s="137">
-        <f t="shared" si="10"/>
-        <v>48.730000000000004</v>
-      </c>
-      <c r="J85" s="106"/>
-      <c r="K85" s="106" t="s">
-        <v>158</v>
-      </c>
-      <c r="L85" s="106" t="s">
-        <v>164</v>
-      </c>
-      <c r="M85" s="106" t="s">
-        <v>164</v>
-      </c>
-      <c r="N85" s="107">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P85" s="109">
-        <v>60.25</v>
-      </c>
-      <c r="Q85" s="109" t="s">
-        <v>164</v>
-      </c>
-      <c r="R85" s="110">
-        <f t="shared" si="12"/>
-        <v>60.25</v>
-      </c>
-      <c r="T85" s="101">
-        <f t="shared" si="13"/>
-        <v>-60.25</v>
-      </c>
-    </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A86" s="79">
-        <v>17</v>
-      </c>
-      <c r="B86" s="102">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C86" s="104">
-        <v>3.0209999999999999</v>
-      </c>
-      <c r="D86" s="103"/>
-      <c r="E86" s="103"/>
-      <c r="F86" s="100">
-        <f>VLOOKUP($C86,Лист5!$A$1:$B$104,2,)</f>
-        <v>85.69</v>
-      </c>
-      <c r="G86" s="103"/>
-      <c r="H86" s="99">
-        <f t="shared" si="10"/>
-        <v>85.69</v>
-      </c>
-      <c r="J86" s="111"/>
-      <c r="K86" s="111" t="s">
-        <v>159</v>
-      </c>
-      <c r="L86" s="111">
-        <v>17.940000000000001</v>
-      </c>
-      <c r="M86" s="111"/>
-      <c r="N86" s="112">
-        <f t="shared" si="11"/>
-        <v>17.940000000000001</v>
-      </c>
-      <c r="O86" s="113"/>
-      <c r="P86" s="111" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q86" s="111" t="s">
-        <v>164</v>
-      </c>
-      <c r="R86" s="112">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S86" s="113"/>
-      <c r="T86" s="114">
-        <f t="shared" si="13"/>
-        <v>17.940000000000001</v>
-      </c>
-    </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A87" s="135">
-        <v>18</v>
-      </c>
-      <c r="B87" s="135">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C87" s="139">
-        <v>3.085</v>
-      </c>
-      <c r="D87" s="137"/>
-      <c r="E87" s="137"/>
-      <c r="F87" s="137">
-        <f>VLOOKUP($C87,Лист5!$A$1:$B$104,2,)</f>
-        <v>54.81</v>
-      </c>
-      <c r="G87" s="137"/>
-      <c r="H87" s="137">
-        <f t="shared" si="10"/>
-        <v>54.81</v>
-      </c>
-      <c r="J87" s="106"/>
-      <c r="K87" s="106" t="s">
-        <v>160</v>
-      </c>
-      <c r="L87" s="106">
-        <v>3.6</v>
-      </c>
-      <c r="M87" s="106"/>
-      <c r="N87" s="107">
-        <f t="shared" si="11"/>
-        <v>3.6</v>
-      </c>
-      <c r="P87" s="109" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q87" s="109" t="s">
-        <v>164</v>
-      </c>
-      <c r="R87" s="110">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="T87" s="101">
-        <f t="shared" si="13"/>
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A88" s="79">
-        <v>19</v>
-      </c>
-      <c r="B88" s="102">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C88" s="104">
-        <v>3.0939999999999999</v>
-      </c>
-      <c r="D88" s="103"/>
-      <c r="E88" s="103"/>
-      <c r="F88" s="100">
-        <f>VLOOKUP($C88,Лист5!$A$1:$B$104,2,)</f>
-        <v>62.410000000000004</v>
-      </c>
-      <c r="G88" s="103"/>
-      <c r="H88" s="99">
-        <f t="shared" si="10"/>
-        <v>62.410000000000004</v>
-      </c>
-    </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A89" s="79"/>
-      <c r="B89" s="79"/>
-      <c r="C89" s="79" t="s">
-        <v>19</v>
-      </c>
-      <c r="D89" s="99">
-        <f>SUM(D70:D88)</f>
-        <v>2343.38</v>
-      </c>
-      <c r="E89" s="99">
-        <f t="shared" ref="E89:F89" si="14">SUM(E70:E88)</f>
-        <v>182.74</v>
-      </c>
-      <c r="F89" s="99">
-        <f t="shared" si="14"/>
-        <v>251.64000000000001</v>
-      </c>
-      <c r="G89" s="99">
-        <f t="shared" ref="G89" si="15">SUM(G70:G88)</f>
-        <v>0</v>
-      </c>
-      <c r="H89" s="99">
-        <f t="shared" ref="H89" si="16">SUM(H70:H88)</f>
-        <v>2777.7599999999998</v>
-      </c>
-    </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="B91" s="93" t="s">
-        <v>154</v>
-      </c>
-      <c r="C91" s="130"/>
-      <c r="D91" s="95" t="s">
-        <v>150</v>
-      </c>
-      <c r="E91" s="95" t="s">
-        <v>151</v>
-      </c>
-      <c r="F91" s="96" t="s">
-        <v>152</v>
-      </c>
-      <c r="G91" s="96" t="s">
-        <v>153</v>
-      </c>
-      <c r="J91" s="132" t="s">
-        <v>154</v>
-      </c>
-      <c r="K91" s="130"/>
-      <c r="L91" s="95" t="s">
-        <v>150</v>
-      </c>
-      <c r="M91" s="95" t="s">
-        <v>151</v>
-      </c>
-      <c r="N91" s="96" t="s">
-        <v>152</v>
-      </c>
-      <c r="O91" s="96" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="B92" s="130">
-        <v>1</v>
-      </c>
-      <c r="C92" s="130"/>
-      <c r="D92" s="131">
-        <f>SUM(D70:D81)</f>
-        <v>1742.02</v>
-      </c>
-      <c r="E92" s="130"/>
-      <c r="F92" s="131">
-        <f>F85</f>
-        <v>48.730000000000004</v>
-      </c>
-      <c r="G92" s="130"/>
-      <c r="J92" s="130">
-        <v>1</v>
-      </c>
-      <c r="K92" s="130"/>
-      <c r="L92" s="131">
-        <f>L82</f>
-        <v>1765.15</v>
-      </c>
-      <c r="M92" s="130">
-        <f>L83</f>
-        <v>0</v>
-      </c>
-      <c r="N92" s="131">
-        <f>L84</f>
-        <v>49.99</v>
-      </c>
-      <c r="O92" s="130"/>
-      <c r="P92" s="101">
-        <f t="shared" ref="P92:S93" si="17">L92-D92</f>
-        <v>23.130000000000109</v>
-      </c>
-      <c r="Q92" s="101">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R92" s="101">
-        <f t="shared" si="17"/>
-        <v>1.259999999999998</v>
-      </c>
-      <c r="S92" s="101">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="B93" s="130">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C93" s="130"/>
-      <c r="D93" s="131">
-        <f>SUM(D82:D83)</f>
-        <v>601.36</v>
-      </c>
-      <c r="E93" s="131">
-        <f>E84</f>
-        <v>182.74</v>
-      </c>
-      <c r="F93" s="131">
-        <f>SUM(F86:F88)</f>
-        <v>202.91</v>
-      </c>
-      <c r="G93" s="130"/>
-      <c r="J93" s="130">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="K93" s="130"/>
-      <c r="L93" s="131">
-        <f>M82</f>
-        <v>642.66</v>
-      </c>
-      <c r="M93" s="131">
-        <f>M83</f>
-        <v>182.74</v>
-      </c>
-      <c r="N93" s="131">
-        <f>M84</f>
-        <v>189.76</v>
-      </c>
-      <c r="O93" s="130"/>
-      <c r="P93" s="101">
-        <f t="shared" si="17"/>
-        <v>41.299999999999955</v>
-      </c>
-      <c r="Q93" s="101">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R93" s="101">
-        <f t="shared" si="17"/>
-        <v>-13.150000000000006</v>
-      </c>
-      <c r="S93" s="101">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A67:G67"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor theme="4" tint="0.79998168889431442"/>
-  </sheetPr>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="7.5546875" style="86" customWidth="1"/>
-    <col min="2" max="2" width="61.6640625" style="90" customWidth="1"/>
-    <col min="3" max="3" width="49.109375" style="90" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" style="86" customWidth="1"/>
-    <col min="5" max="5" width="19.44140625" style="86" customWidth="1"/>
-    <col min="6" max="6" width="11.44140625" style="86" customWidth="1"/>
-    <col min="7" max="16384" width="9.109375" style="86"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="81"/>
-      <c r="B1" s="82" t="s">
-        <v>148</v>
-      </c>
-      <c r="C1" s="82"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="85"/>
-    </row>
-    <row r="2" spans="1:6" s="92" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="81" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="91" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="91" t="s">
-        <v>149</v>
-      </c>
-      <c r="D2" s="83" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="84" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="83" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="54" x14ac:dyDescent="0.35">
-      <c r="A3" s="87">
-        <v>1</v>
-      </c>
-      <c r="B3" s="88" t="s">
-        <v>145</v>
-      </c>
-      <c r="C3" s="88" t="s">
-        <v>174</v>
-      </c>
-      <c r="D3" s="87" t="s">
-        <v>82</v>
-      </c>
-      <c r="E3" s="87">
-        <v>1</v>
-      </c>
-      <c r="F3" s="129">
-        <f>'2.2)Шп1эт'!F24+'2.3)Шп2эт'!F25+'2.4)Шп3эт'!G17</f>
-        <v>8114.59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="36" x14ac:dyDescent="0.35">
-      <c r="A4" s="87">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B4" s="88" t="s">
-        <v>146</v>
-      </c>
-      <c r="C4" s="88"/>
-      <c r="D4" s="87" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="87">
-        <v>1.8</v>
-      </c>
-      <c r="F4" s="129">
-        <f>E4*F3</f>
-        <v>14606.262000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="36" x14ac:dyDescent="0.35">
-      <c r="A5" s="87">
-        <v>1.2</v>
-      </c>
-      <c r="B5" s="88" t="s">
-        <v>147</v>
-      </c>
-      <c r="C5" s="88"/>
-      <c r="D5" s="87" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="87">
-        <v>0.15</v>
-      </c>
-      <c r="F5" s="89">
-        <f>E5*F3</f>
-        <v>1217.1885</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/school_lublino/walls/vor_lublino_walls.xlsx
+++ b/school_lublino/walls/vor_lublino_walls.xlsx
@@ -13,28 +13,30 @@
   </bookViews>
   <sheets>
     <sheet name="ВОР 2 э. шт." sheetId="8" state="hidden" r:id="rId1"/>
-    <sheet name="1.7ГКЛ" sheetId="25" r:id="rId2"/>
-    <sheet name="2.5Шт5блСпртЗл" sheetId="24" r:id="rId3"/>
-    <sheet name="Спец 2 э. шт." sheetId="7" r:id="rId4"/>
-    <sheet name="ВОР 3 э. шт." sheetId="10" state="hidden" r:id="rId5"/>
-    <sheet name="Спец 3 э. шт." sheetId="9" state="hidden" r:id="rId6"/>
-    <sheet name="ВОР 1.2.3 э. шт." sheetId="15" state="hidden" r:id="rId7"/>
-    <sheet name="сп1.2.3эт" sheetId="11" state="hidden" r:id="rId8"/>
-    <sheet name="Лист4" sheetId="14" state="hidden" r:id="rId9"/>
-    <sheet name="Лист2" sheetId="17" r:id="rId10"/>
-    <sheet name="2.1ШпВор" sheetId="16" r:id="rId11"/>
-    <sheet name="2.2)Шп1эт" sheetId="20" r:id="rId12"/>
-    <sheet name="2.3)Шп2эт" sheetId="21" r:id="rId13"/>
-    <sheet name="2.4)Шп3эт" sheetId="22" r:id="rId14"/>
-    <sheet name="3.1ШпФин" sheetId="23" r:id="rId15"/>
-    <sheet name="Лист5" sheetId="19" state="hidden" r:id="rId16"/>
+    <sheet name="3.2ШпФин" sheetId="27" r:id="rId2"/>
+    <sheet name="2.6ЧСТ3" sheetId="26" r:id="rId3"/>
+    <sheet name="1.7ГКЛ" sheetId="25" r:id="rId4"/>
+    <sheet name="2.5Шт5блСпртЗл" sheetId="24" r:id="rId5"/>
+    <sheet name="Спец 2 э. шт." sheetId="7" r:id="rId6"/>
+    <sheet name="ВОР 3 э. шт." sheetId="10" r:id="rId7"/>
+    <sheet name="Спец 3 э. шт." sheetId="9" r:id="rId8"/>
+    <sheet name="ВОР 1.2.3 э. шт." sheetId="15" state="hidden" r:id="rId9"/>
+    <sheet name="сп1.2.3эт" sheetId="11" r:id="rId10"/>
+    <sheet name="Лист4" sheetId="14" state="hidden" r:id="rId11"/>
+    <sheet name="Лист2" sheetId="17" r:id="rId12"/>
+    <sheet name="2.1ШпВор" sheetId="16" r:id="rId13"/>
+    <sheet name="2.2)Шп1эт" sheetId="20" r:id="rId14"/>
+    <sheet name="2.3)Шп2эт" sheetId="21" r:id="rId15"/>
+    <sheet name="2.4)Шп3эт" sheetId="22" r:id="rId16"/>
+    <sheet name="3.1ШпФин" sheetId="23" r:id="rId17"/>
+    <sheet name="Лист5" sheetId="19" state="hidden" r:id="rId18"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="210">
   <si>
     <t>№ п.п.</t>
   </si>
@@ -658,6 +660,24 @@
   </si>
   <si>
     <t>Этаж</t>
+  </si>
+  <si>
+    <t>Подготовка поверхности СКБ / стен / ГКЛ, ПГП / 2мм</t>
+  </si>
+  <si>
+    <t>Поз</t>
+  </si>
+  <si>
+    <t>ЧСТ-3</t>
+  </si>
+  <si>
+    <t>Подготовка поверхности СКБ / стен / по штукатурке / 2мм</t>
+  </si>
+  <si>
+    <t>Поз.</t>
+  </si>
+  <si>
+    <t>Блок 1. 1, 2, 3, этажи. Шпаклевка финишная.</t>
   </si>
 </sst>
 </file>
@@ -1118,7 +1138,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="174">
+  <cellXfs count="178">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1509,7 +1529,21 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1548,7 +1582,10 @@
     <xf numFmtId="165" fontId="12" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1560,11 +1597,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2350,6 +2382,656 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
+    <tabColor theme="5" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7" style="10" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" style="10" customWidth="1"/>
+    <col min="3" max="6" width="8.6640625" style="10" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" style="27" customWidth="1"/>
+    <col min="8" max="16384" width="9.109375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="175" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="175"/>
+      <c r="C1" s="175"/>
+      <c r="D1" s="175"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="175"/>
+      <c r="G1" s="175"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="176" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" s="176"/>
+      <c r="C2" s="176"/>
+      <c r="D2" s="176"/>
+      <c r="E2" s="176"/>
+      <c r="F2" s="176"/>
+      <c r="G2" s="176"/>
+    </row>
+    <row r="3" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A3" s="72"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" s="73" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="73" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3" s="73" t="s">
+        <v>67</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="72">
+        <v>1</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25">
+        <v>75.790000000000006</v>
+      </c>
+      <c r="G5" s="25">
+        <f>SUM(C5:F5)</f>
+        <v>75.790000000000006</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="74">
+        <v>2</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25">
+        <v>93.93</v>
+      </c>
+      <c r="G6" s="25">
+        <f t="shared" ref="G6:G21" si="0">SUM(C6:F6)</f>
+        <v>93.93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="74">
+        <v>3</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25">
+        <v>34.979999999999997</v>
+      </c>
+      <c r="G7" s="25">
+        <f t="shared" si="0"/>
+        <v>34.979999999999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="74">
+        <v>4</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25">
+        <v>20.85</v>
+      </c>
+      <c r="G8" s="25">
+        <f t="shared" si="0"/>
+        <v>20.85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="74">
+        <v>5</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25">
+        <v>38.89</v>
+      </c>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25">
+        <f t="shared" si="0"/>
+        <v>38.89</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="74">
+        <v>6</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="C10" s="25">
+        <v>1.89</v>
+      </c>
+      <c r="D10" s="25">
+        <v>83.51</v>
+      </c>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25">
+        <f t="shared" si="0"/>
+        <v>85.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="74">
+        <v>7</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="C11" s="25">
+        <v>1.63</v>
+      </c>
+      <c r="D11" s="25">
+        <v>87.22</v>
+      </c>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25">
+        <f t="shared" si="0"/>
+        <v>88.85</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="74">
+        <v>8</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="C12" s="25">
+        <v>66.650000000000006</v>
+      </c>
+      <c r="D12" s="25">
+        <v>161.4</v>
+      </c>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25">
+        <f t="shared" si="0"/>
+        <v>228.05</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="74">
+        <v>9</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="C13" s="25">
+        <v>69.88</v>
+      </c>
+      <c r="D13" s="25">
+        <v>357.36</v>
+      </c>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25">
+        <f t="shared" si="0"/>
+        <v>427.24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="74">
+        <v>10</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="C14" s="25">
+        <v>36.6</v>
+      </c>
+      <c r="D14" s="25">
+        <v>41.25</v>
+      </c>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25">
+        <f t="shared" si="0"/>
+        <v>77.849999999999994</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="74">
+        <v>11</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="C15" s="25">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="D15" s="25">
+        <v>287.72000000000003</v>
+      </c>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25">
+        <f t="shared" si="0"/>
+        <v>319.92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="74">
+        <v>12</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="C16" s="25">
+        <v>1.02</v>
+      </c>
+      <c r="D16" s="25">
+        <v>82.31</v>
+      </c>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25">
+        <f t="shared" si="0"/>
+        <v>83.33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="74">
+        <v>13</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25">
+        <v>28.81</v>
+      </c>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25">
+        <f t="shared" si="0"/>
+        <v>28.81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="74">
+        <v>14</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25">
+        <v>28.19</v>
+      </c>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25">
+        <f t="shared" si="0"/>
+        <v>28.19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="74">
+        <v>15</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25">
+        <v>28.36</v>
+      </c>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25">
+        <f t="shared" si="0"/>
+        <v>28.36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="74">
+        <v>16</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="C20" s="25">
+        <v>24.7</v>
+      </c>
+      <c r="D20" s="25">
+        <v>53.51</v>
+      </c>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25">
+        <f t="shared" si="0"/>
+        <v>78.209999999999994</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="74">
+        <v>17</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="C21" s="25">
+        <v>1.02</v>
+      </c>
+      <c r="D21" s="25">
+        <v>53.79</v>
+      </c>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25">
+        <f t="shared" si="0"/>
+        <v>54.81</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="72"/>
+      <c r="B22" s="72" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="25">
+        <f>SUM(C5:C21)</f>
+        <v>235.59000000000003</v>
+      </c>
+      <c r="D22" s="25">
+        <f>SUM(D5:D21)</f>
+        <v>1208.07</v>
+      </c>
+      <c r="E22" s="25">
+        <f>SUM(E5:E21)</f>
+        <v>124.25</v>
+      </c>
+      <c r="F22" s="25">
+        <f>SUM(F5:F21)</f>
+        <v>225.55</v>
+      </c>
+      <c r="G22" s="25">
+        <f>SUM(G5:G21)</f>
+        <v>1793.4599999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="76">
+        <v>544.88</v>
+      </c>
+      <c r="C2" s="76">
+        <v>528.22</v>
+      </c>
+      <c r="D2" s="76">
+        <v>563.80999999999995</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B4" s="76">
+        <v>492.07</v>
+      </c>
+      <c r="C4" s="76">
+        <v>542.94000000000005</v>
+      </c>
+      <c r="D4" s="76">
+        <v>303.39999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B5" s="77">
+        <f>B4+B2</f>
+        <v>1036.95</v>
+      </c>
+      <c r="C5" s="77">
+        <f>C4+C2</f>
+        <v>1071.1600000000001</v>
+      </c>
+      <c r="D5" s="77">
+        <f>D4+D2</f>
+        <v>867.20999999999992</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B6" s="75"/>
+      <c r="C6" s="75"/>
+      <c r="D6" s="75"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>144</v>
+      </c>
+      <c r="B7" s="75">
+        <f>991.77</f>
+        <v>991.77</v>
+      </c>
+      <c r="C7" s="75">
+        <f>'ВОР 2 э. шт.'!E6</f>
+        <v>907.35119999999995</v>
+      </c>
+      <c r="D7" s="75">
+        <f>'ВОР 3 э. шт.'!E6</f>
+        <v>840.60999999999979</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B8" s="75">
+        <f>B5-B7</f>
+        <v>45.180000000000064</v>
+      </c>
+      <c r="C8" s="75">
+        <f t="shared" ref="C8" si="0">C5-C7</f>
+        <v>163.80880000000013</v>
+      </c>
+      <c r="D8" s="75">
+        <f t="shared" ref="D8" si="1">D5-D7</f>
+        <v>26.600000000000136</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10" s="76">
+        <v>771.83</v>
+      </c>
+      <c r="C10" s="76">
+        <v>972.84</v>
+      </c>
+      <c r="D10" s="76">
+        <v>1176.67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B11" s="76"/>
+      <c r="C11" s="76"/>
+      <c r="D11" s="76"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B12" s="76">
+        <v>927.42</v>
+      </c>
+      <c r="C12" s="76">
+        <v>1669.68</v>
+      </c>
+      <c r="D12" s="76">
+        <v>707.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>129</v>
+      </c>
+      <c r="B13" s="77">
+        <f>B12+B10</f>
+        <v>1699.25</v>
+      </c>
+      <c r="C13" s="77">
+        <f>C12+C10</f>
+        <v>2642.52</v>
+      </c>
+      <c r="D13" s="77">
+        <f>D12+D10</f>
+        <v>1884.47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>144</v>
+      </c>
+      <c r="B15">
+        <f>1615</f>
+        <v>1615</v>
+      </c>
+      <c r="C15" s="75">
+        <f>'ВОР 2 э. шт.'!E21</f>
+        <v>1761.3287999999998</v>
+      </c>
+      <c r="D15" s="75">
+        <f>'ВОР 3 э. шт.'!E21</f>
+        <v>1864.9899999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B16" s="75">
+        <f>B13-B15</f>
+        <v>84.25</v>
+      </c>
+      <c r="C16" s="75">
+        <f t="shared" ref="C16:D16" si="2">C13-C15</f>
+        <v>881.19120000000021</v>
+      </c>
+      <c r="D16" s="75">
+        <f t="shared" si="2"/>
+        <v>19.480000000000246</v>
+      </c>
+    </row>
+    <row r="21" spans="3:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="22" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C22" s="55">
+        <f>(1432.33)/100 * 71</f>
+        <v>1016.9543</v>
+      </c>
+      <c r="D22" s="55">
+        <f>(2736)/100 * 71</f>
+        <v>1942.56</v>
+      </c>
+      <c r="E22" s="75">
+        <f>3617-D22-C22</f>
+        <v>657.48570000000007</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
     <tabColor theme="2" tint="-9.9978637043366805E-2"/>
   </sheetPr>
   <dimension ref="A1:AD93"/>
@@ -2362,15 +3044,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="177" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="170"/>
-      <c r="C1" s="170"/>
-      <c r="D1" s="170"/>
-      <c r="E1" s="170"/>
-      <c r="F1" s="170"/>
-      <c r="G1" s="170"/>
+      <c r="B1" s="177"/>
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="177"/>
+      <c r="F1" s="177"/>
+      <c r="G1" s="177"/>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" s="79"/>
@@ -3631,15 +4313,15 @@
       </c>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A32" s="170" t="s">
+      <c r="A32" s="177" t="s">
         <v>2</v>
       </c>
-      <c r="B32" s="170"/>
-      <c r="C32" s="170"/>
-      <c r="D32" s="170"/>
-      <c r="E32" s="170"/>
-      <c r="F32" s="170"/>
-      <c r="G32" s="170"/>
+      <c r="B32" s="177"/>
+      <c r="C32" s="177"/>
+      <c r="D32" s="177"/>
+      <c r="E32" s="177"/>
+      <c r="F32" s="177"/>
+      <c r="G32" s="177"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="79"/>
@@ -4465,15 +5147,15 @@
       <c r="F66" s="101"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A67" s="170" t="s">
+      <c r="A67" s="177" t="s">
         <v>2</v>
       </c>
-      <c r="B67" s="170"/>
-      <c r="C67" s="170"/>
-      <c r="D67" s="170"/>
-      <c r="E67" s="170"/>
-      <c r="F67" s="170"/>
-      <c r="G67" s="170"/>
+      <c r="B67" s="177"/>
+      <c r="C67" s="177"/>
+      <c r="D67" s="177"/>
+      <c r="E67" s="177"/>
+      <c r="F67" s="177"/>
+      <c r="G67" s="177"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="79"/>
@@ -5279,7 +5961,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
@@ -5391,7 +6073,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
@@ -5404,14 +6086,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="177" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="170"/>
-      <c r="C1" s="170"/>
-      <c r="D1" s="170"/>
-      <c r="E1" s="170"/>
-      <c r="F1" s="170"/>
+      <c r="B1" s="177"/>
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="177"/>
+      <c r="F1" s="177"/>
     </row>
     <row r="2" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="133"/>
@@ -5872,7 +6554,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
@@ -5885,14 +6567,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="177" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="170"/>
-      <c r="C1" s="170"/>
-      <c r="D1" s="170"/>
-      <c r="E1" s="170"/>
-      <c r="F1" s="170"/>
+      <c r="B1" s="177"/>
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="177"/>
+      <c r="F1" s="177"/>
     </row>
     <row r="2" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="133"/>
@@ -6375,7 +7057,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
@@ -6388,15 +7070,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="177" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="170"/>
-      <c r="C1" s="170"/>
-      <c r="D1" s="170"/>
-      <c r="E1" s="170"/>
-      <c r="F1" s="170"/>
-      <c r="G1" s="170"/>
+      <c r="B1" s="177"/>
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="177"/>
+      <c r="F1" s="177"/>
+      <c r="G1" s="177"/>
     </row>
     <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="133"/>
@@ -6741,7 +7423,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6760,36 +7442,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="155" t="s">
+      <c r="A1" s="161" t="s">
         <v>175</v>
       </c>
-      <c r="B1" s="156"/>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
-      <c r="E1" s="156"/>
-      <c r="F1" s="156"/>
-      <c r="G1" s="156"/>
-      <c r="H1" s="156"/>
-      <c r="I1" s="156"/>
-      <c r="J1" s="156"/>
-      <c r="K1" s="156"/>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="162"/>
+      <c r="G1" s="162"/>
+      <c r="H1" s="162"/>
+      <c r="I1" s="162"/>
+      <c r="J1" s="162"/>
+      <c r="K1" s="162"/>
     </row>
     <row r="2" spans="1:11" s="153" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A2" s="141" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="157" t="s">
+      <c r="B2" s="163" t="s">
         <v>176</v>
       </c>
-      <c r="C2" s="158"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="159"/>
-      <c r="H2" s="160" t="s">
+      <c r="C2" s="164"/>
+      <c r="D2" s="164"/>
+      <c r="E2" s="164"/>
+      <c r="F2" s="164"/>
+      <c r="G2" s="165"/>
+      <c r="H2" s="166" t="s">
         <v>177</v>
       </c>
-      <c r="I2" s="161"/>
+      <c r="I2" s="167"/>
       <c r="J2" s="142" t="s">
         <v>15</v>
       </c>
@@ -6801,18 +7483,18 @@
       <c r="A3" s="143">
         <v>1</v>
       </c>
-      <c r="B3" s="162" t="s">
+      <c r="B3" s="168" t="s">
         <v>145</v>
       </c>
-      <c r="C3" s="163"/>
-      <c r="D3" s="163"/>
-      <c r="E3" s="163"/>
-      <c r="F3" s="163"/>
-      <c r="G3" s="164"/>
-      <c r="H3" s="165" t="s">
+      <c r="C3" s="169"/>
+      <c r="D3" s="169"/>
+      <c r="E3" s="169"/>
+      <c r="F3" s="169"/>
+      <c r="G3" s="170"/>
+      <c r="H3" s="171" t="s">
         <v>188</v>
       </c>
-      <c r="I3" s="166"/>
+      <c r="I3" s="172"/>
       <c r="J3" s="143" t="s">
         <v>82</v>
       </c>
@@ -6822,17 +7504,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="167"/>
-      <c r="B4" s="167"/>
-      <c r="C4" s="167"/>
-      <c r="D4" s="167"/>
-      <c r="E4" s="167"/>
-      <c r="F4" s="167"/>
-      <c r="G4" s="167"/>
-      <c r="H4" s="167"/>
-      <c r="I4" s="167"/>
-      <c r="J4" s="167"/>
-      <c r="K4" s="167"/>
+      <c r="A4" s="160"/>
+      <c r="B4" s="160"/>
+      <c r="C4" s="160"/>
+      <c r="D4" s="160"/>
+      <c r="E4" s="160"/>
+      <c r="F4" s="160"/>
+      <c r="G4" s="160"/>
+      <c r="H4" s="160"/>
+      <c r="I4" s="160"/>
+      <c r="J4" s="160"/>
+      <c r="K4" s="160"/>
     </row>
     <row r="5" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="145" t="s">
@@ -6844,7 +7526,7 @@
       <c r="C5" s="145" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="171"/>
+      <c r="D5" s="174"/>
       <c r="E5" s="145" t="s">
         <v>178</v>
       </c>
@@ -6854,7 +7536,7 @@
       <c r="G5" s="145" t="s">
         <v>179</v>
       </c>
-      <c r="H5" s="171"/>
+      <c r="H5" s="174"/>
       <c r="I5" s="145" t="s">
         <v>178</v>
       </c>
@@ -6875,7 +7557,7 @@
       <c r="C6" s="149">
         <v>125.55</v>
       </c>
-      <c r="D6" s="171"/>
+      <c r="D6" s="174"/>
       <c r="E6" s="146" t="s">
         <v>21</v>
       </c>
@@ -6885,7 +7567,7 @@
       <c r="G6" s="149">
         <v>118.18</v>
       </c>
-      <c r="H6" s="171"/>
+      <c r="H6" s="174"/>
       <c r="I6" s="146" t="s">
         <v>93</v>
       </c>
@@ -6906,7 +7588,7 @@
       <c r="C7" s="150">
         <v>118.27</v>
       </c>
-      <c r="D7" s="171"/>
+      <c r="D7" s="174"/>
       <c r="E7" s="147" t="s">
         <v>22</v>
       </c>
@@ -6916,7 +7598,7 @@
       <c r="G7" s="150">
         <v>113.74</v>
       </c>
-      <c r="H7" s="171"/>
+      <c r="H7" s="174"/>
       <c r="I7" s="147" t="s">
         <v>96</v>
       </c>
@@ -6937,7 +7619,7 @@
       <c r="C8" s="149">
         <v>102.42</v>
       </c>
-      <c r="D8" s="171"/>
+      <c r="D8" s="174"/>
       <c r="E8" s="146" t="s">
         <v>23</v>
       </c>
@@ -6947,7 +7629,7 @@
       <c r="G8" s="149">
         <v>122.5</v>
       </c>
-      <c r="H8" s="171"/>
+      <c r="H8" s="174"/>
       <c r="I8" s="146" t="s">
         <v>97</v>
       </c>
@@ -6968,7 +7650,7 @@
       <c r="C9" s="150">
         <v>101.91</v>
       </c>
-      <c r="D9" s="171"/>
+      <c r="D9" s="174"/>
       <c r="E9" s="147" t="s">
         <v>26</v>
       </c>
@@ -6978,7 +7660,7 @@
       <c r="G9" s="150">
         <v>106.77</v>
       </c>
-      <c r="H9" s="171"/>
+      <c r="H9" s="174"/>
       <c r="I9" s="147" t="s">
         <v>98</v>
       </c>
@@ -6999,7 +7681,7 @@
       <c r="C10" s="149">
         <v>98.2</v>
       </c>
-      <c r="D10" s="171"/>
+      <c r="D10" s="174"/>
       <c r="E10" s="146" t="s">
         <v>27</v>
       </c>
@@ -7009,7 +7691,7 @@
       <c r="G10" s="149">
         <v>111.51</v>
       </c>
-      <c r="H10" s="171"/>
+      <c r="H10" s="174"/>
       <c r="I10" s="146" t="s">
         <v>99</v>
       </c>
@@ -7030,7 +7712,7 @@
       <c r="C11" s="150">
         <v>94.76</v>
       </c>
-      <c r="D11" s="171"/>
+      <c r="D11" s="174"/>
       <c r="E11" s="147" t="s">
         <v>28</v>
       </c>
@@ -7040,7 +7722,7 @@
       <c r="G11" s="150">
         <v>106.77</v>
       </c>
-      <c r="H11" s="171"/>
+      <c r="H11" s="174"/>
       <c r="I11" s="147" t="s">
         <v>100</v>
       </c>
@@ -7061,7 +7743,7 @@
       <c r="C12" s="149">
         <v>152.44</v>
       </c>
-      <c r="D12" s="171"/>
+      <c r="D12" s="174"/>
       <c r="E12" s="146" t="s">
         <v>29</v>
       </c>
@@ -7071,7 +7753,7 @@
       <c r="G12" s="149">
         <v>93.03</v>
       </c>
-      <c r="H12" s="171"/>
+      <c r="H12" s="174"/>
       <c r="I12" s="146" t="s">
         <v>101</v>
       </c>
@@ -7090,7 +7772,7 @@
         <f>SUM(C6:C12)</f>
         <v>793.55</v>
       </c>
-      <c r="D13" s="171"/>
+      <c r="D13" s="174"/>
       <c r="E13" s="147" t="s">
         <v>30</v>
       </c>
@@ -7100,7 +7782,7 @@
       <c r="G13" s="150">
         <v>106.64</v>
       </c>
-      <c r="H13" s="171"/>
+      <c r="H13" s="174"/>
       <c r="J13" s="148" t="s">
         <v>165</v>
       </c>
@@ -7110,10 +7792,10 @@
       </c>
     </row>
     <row r="14" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="154"/>
-      <c r="B14" s="154"/>
-      <c r="C14" s="154"/>
-      <c r="D14" s="171"/>
+      <c r="A14" s="173"/>
+      <c r="B14" s="173"/>
+      <c r="C14" s="173"/>
+      <c r="D14" s="174"/>
       <c r="E14" s="146" t="s">
         <v>32</v>
       </c>
@@ -7123,16 +7805,16 @@
       <c r="G14" s="149">
         <v>83.2</v>
       </c>
-      <c r="H14" s="171"/>
-      <c r="I14" s="171"/>
-      <c r="J14" s="171"/>
-      <c r="K14" s="171"/>
+      <c r="H14" s="174"/>
+      <c r="I14" s="174"/>
+      <c r="J14" s="174"/>
+      <c r="K14" s="174"/>
     </row>
     <row r="15" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="154"/>
-      <c r="B15" s="154"/>
-      <c r="C15" s="154"/>
-      <c r="D15" s="171"/>
+      <c r="A15" s="173"/>
+      <c r="B15" s="173"/>
+      <c r="C15" s="173"/>
+      <c r="D15" s="174"/>
       <c r="F15" s="148" t="s">
         <v>165</v>
       </c>
@@ -7140,10 +7822,10 @@
         <f>SUM(G6:G14)</f>
         <v>962.34</v>
       </c>
-      <c r="H15" s="171"/>
-      <c r="I15" s="171"/>
-      <c r="J15" s="171"/>
-      <c r="K15" s="171"/>
+      <c r="H15" s="174"/>
+      <c r="I15" s="174"/>
+      <c r="J15" s="174"/>
+      <c r="K15" s="174"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -7163,7 +7845,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B104"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7982,6 +8664,635 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.21875" style="140" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" style="140" customWidth="1"/>
+    <col min="3" max="3" width="3.88671875" style="140" customWidth="1"/>
+    <col min="4" max="4" width="9.88671875" style="140" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" style="140" customWidth="1"/>
+    <col min="6" max="6" width="2.33203125" style="140" customWidth="1"/>
+    <col min="7" max="7" width="2.6640625" style="140" customWidth="1"/>
+    <col min="8" max="8" width="3.77734375" style="140" customWidth="1"/>
+    <col min="9" max="9" width="8.44140625" style="140" customWidth="1"/>
+    <col min="10" max="10" width="10.77734375" style="140" customWidth="1"/>
+    <col min="11" max="11" width="8.21875" style="140" customWidth="1"/>
+    <col min="12" max="12" width="9.88671875" style="140" customWidth="1"/>
+    <col min="13" max="16384" width="8.88671875" style="140"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="161" t="s">
+        <v>175</v>
+      </c>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="162"/>
+      <c r="G1" s="162"/>
+      <c r="H1" s="162"/>
+      <c r="I1" s="162"/>
+      <c r="J1" s="162"/>
+      <c r="K1" s="162"/>
+      <c r="L1" s="162"/>
+    </row>
+    <row r="2" spans="1:12" s="153" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="141" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="156" t="s">
+        <v>208</v>
+      </c>
+      <c r="C2" s="163" t="s">
+        <v>176</v>
+      </c>
+      <c r="D2" s="164"/>
+      <c r="E2" s="164"/>
+      <c r="F2" s="164"/>
+      <c r="G2" s="164"/>
+      <c r="H2" s="165"/>
+      <c r="I2" s="166" t="s">
+        <v>177</v>
+      </c>
+      <c r="J2" s="167"/>
+      <c r="K2" s="142" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" s="152" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="143">
+        <v>1</v>
+      </c>
+      <c r="B3" s="157">
+        <v>234</v>
+      </c>
+      <c r="C3" s="168" t="s">
+        <v>207</v>
+      </c>
+      <c r="D3" s="169"/>
+      <c r="E3" s="169"/>
+      <c r="F3" s="169"/>
+      <c r="G3" s="169"/>
+      <c r="H3" s="170"/>
+      <c r="I3" s="171" t="s">
+        <v>209</v>
+      </c>
+      <c r="J3" s="172"/>
+      <c r="K3" s="143" t="s">
+        <v>82</v>
+      </c>
+      <c r="L3" s="144">
+        <f>B13+E15+J16</f>
+        <v>2873.96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="160"/>
+      <c r="B4" s="160"/>
+      <c r="C4" s="160"/>
+      <c r="D4" s="160"/>
+      <c r="E4" s="160"/>
+      <c r="F4" s="160"/>
+      <c r="G4" s="160"/>
+      <c r="H4" s="160"/>
+      <c r="I4" s="160"/>
+      <c r="J4" s="160"/>
+      <c r="K4" s="160"/>
+      <c r="L4" s="160"/>
+    </row>
+    <row r="5" spans="1:12" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="145" t="s">
+        <v>178</v>
+      </c>
+      <c r="B5" s="145" t="s">
+        <v>179</v>
+      </c>
+      <c r="C5" s="174"/>
+      <c r="D5" s="145" t="s">
+        <v>178</v>
+      </c>
+      <c r="E5" s="145" t="s">
+        <v>179</v>
+      </c>
+      <c r="F5" s="174"/>
+      <c r="G5" s="174"/>
+      <c r="H5" s="174"/>
+      <c r="I5" s="145" t="s">
+        <v>178</v>
+      </c>
+      <c r="J5" s="145" t="s">
+        <v>179</v>
+      </c>
+      <c r="K5" s="173"/>
+      <c r="L5" s="173"/>
+    </row>
+    <row r="6" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="146" t="s">
+        <v>183</v>
+      </c>
+      <c r="B6" s="149">
+        <v>125.55</v>
+      </c>
+      <c r="C6" s="174"/>
+      <c r="D6" s="146" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="149">
+        <v>118.18</v>
+      </c>
+      <c r="F6" s="174"/>
+      <c r="G6" s="174"/>
+      <c r="H6" s="174"/>
+      <c r="I6" s="146" t="s">
+        <v>93</v>
+      </c>
+      <c r="J6" s="149">
+        <v>116.51</v>
+      </c>
+      <c r="K6" s="173"/>
+      <c r="L6" s="173"/>
+    </row>
+    <row r="7" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="147" t="s">
+        <v>184</v>
+      </c>
+      <c r="B7" s="150">
+        <v>118.27</v>
+      </c>
+      <c r="C7" s="174"/>
+      <c r="D7" s="147" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="150">
+        <v>113.74</v>
+      </c>
+      <c r="F7" s="174"/>
+      <c r="G7" s="174"/>
+      <c r="H7" s="174"/>
+      <c r="I7" s="147" t="s">
+        <v>96</v>
+      </c>
+      <c r="J7" s="150">
+        <v>102.57</v>
+      </c>
+      <c r="K7" s="173"/>
+      <c r="L7" s="173"/>
+    </row>
+    <row r="8" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="146" t="s">
+        <v>185</v>
+      </c>
+      <c r="B8" s="149">
+        <v>102.42</v>
+      </c>
+      <c r="C8" s="174"/>
+      <c r="D8" s="146" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="149">
+        <v>122.5</v>
+      </c>
+      <c r="F8" s="174"/>
+      <c r="G8" s="174"/>
+      <c r="H8" s="174"/>
+      <c r="I8" s="146" t="s">
+        <v>97</v>
+      </c>
+      <c r="J8" s="149">
+        <v>104.7</v>
+      </c>
+      <c r="K8" s="173"/>
+      <c r="L8" s="173"/>
+    </row>
+    <row r="9" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="147" t="s">
+        <v>186</v>
+      </c>
+      <c r="B9" s="150">
+        <v>101.91</v>
+      </c>
+      <c r="C9" s="174"/>
+      <c r="D9" s="147" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="150">
+        <v>106.77</v>
+      </c>
+      <c r="F9" s="174"/>
+      <c r="G9" s="174"/>
+      <c r="H9" s="174"/>
+      <c r="I9" s="147" t="s">
+        <v>98</v>
+      </c>
+      <c r="J9" s="150">
+        <v>101.61</v>
+      </c>
+      <c r="K9" s="173"/>
+      <c r="L9" s="173"/>
+    </row>
+    <row r="10" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="146" t="s">
+        <v>180</v>
+      </c>
+      <c r="B10" s="149">
+        <v>98.2</v>
+      </c>
+      <c r="C10" s="174"/>
+      <c r="D10" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="149">
+        <v>111.51</v>
+      </c>
+      <c r="F10" s="174"/>
+      <c r="G10" s="174"/>
+      <c r="H10" s="174"/>
+      <c r="I10" s="146" t="s">
+        <v>99</v>
+      </c>
+      <c r="J10" s="149">
+        <v>105.25</v>
+      </c>
+      <c r="K10" s="173"/>
+      <c r="L10" s="173"/>
+    </row>
+    <row r="11" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="147" t="s">
+        <v>187</v>
+      </c>
+      <c r="B11" s="150">
+        <v>94.76</v>
+      </c>
+      <c r="C11" s="174"/>
+      <c r="D11" s="147" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="150">
+        <v>106.77</v>
+      </c>
+      <c r="F11" s="174"/>
+      <c r="G11" s="174"/>
+      <c r="H11" s="174"/>
+      <c r="I11" s="147" t="s">
+        <v>100</v>
+      </c>
+      <c r="J11" s="150">
+        <v>105.33</v>
+      </c>
+      <c r="K11" s="173"/>
+      <c r="L11" s="173"/>
+    </row>
+    <row r="12" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="146" t="s">
+        <v>181</v>
+      </c>
+      <c r="B12" s="149">
+        <v>152.44</v>
+      </c>
+      <c r="C12" s="174"/>
+      <c r="D12" s="146" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="149">
+        <v>93.03</v>
+      </c>
+      <c r="F12" s="174"/>
+      <c r="G12" s="174"/>
+      <c r="H12" s="174"/>
+      <c r="I12" s="146" t="s">
+        <v>101</v>
+      </c>
+      <c r="J12" s="149">
+        <v>101.95</v>
+      </c>
+      <c r="K12" s="173"/>
+      <c r="L12" s="173"/>
+    </row>
+    <row r="13" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="148" t="s">
+        <v>165</v>
+      </c>
+      <c r="B13" s="151">
+        <f>SUM(B6:B12)</f>
+        <v>793.55</v>
+      </c>
+      <c r="C13" s="174"/>
+      <c r="D13" s="147" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="150">
+        <v>106.64</v>
+      </c>
+      <c r="F13" s="174"/>
+      <c r="G13" s="174"/>
+      <c r="H13" s="174"/>
+      <c r="I13" s="147" t="s">
+        <v>92</v>
+      </c>
+      <c r="J13" s="150">
+        <v>105.79</v>
+      </c>
+      <c r="K13" s="173"/>
+      <c r="L13" s="173"/>
+    </row>
+    <row r="14" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="173"/>
+      <c r="B14" s="173"/>
+      <c r="C14" s="174"/>
+      <c r="D14" s="146" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" s="149">
+        <v>83.2</v>
+      </c>
+      <c r="F14" s="174"/>
+      <c r="G14" s="174"/>
+      <c r="H14" s="174"/>
+      <c r="I14" s="146" t="s">
+        <v>91</v>
+      </c>
+      <c r="J14" s="149">
+        <v>105.58</v>
+      </c>
+      <c r="K14" s="173"/>
+      <c r="L14" s="173"/>
+    </row>
+    <row r="15" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="173"/>
+      <c r="B15" s="173"/>
+      <c r="C15" s="174"/>
+      <c r="D15" s="148" t="s">
+        <v>165</v>
+      </c>
+      <c r="E15" s="151">
+        <f>SUM(E6:E14)</f>
+        <v>962.34</v>
+      </c>
+      <c r="F15" s="174"/>
+      <c r="G15" s="174"/>
+      <c r="H15" s="174"/>
+      <c r="I15" s="147" t="s">
+        <v>90</v>
+      </c>
+      <c r="J15" s="150">
+        <v>168.78</v>
+      </c>
+      <c r="K15" s="173"/>
+      <c r="L15" s="173"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="173"/>
+      <c r="B16" s="173"/>
+      <c r="C16" s="173"/>
+      <c r="D16" s="173"/>
+      <c r="E16" s="173"/>
+      <c r="F16" s="173"/>
+      <c r="G16" s="173"/>
+      <c r="H16" s="173"/>
+      <c r="I16" s="148" t="s">
+        <v>165</v>
+      </c>
+      <c r="J16" s="151">
+        <f>SUM(J6:J15)</f>
+        <v>1118.0700000000002</v>
+      </c>
+      <c r="K16" s="173"/>
+      <c r="L16" s="173"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C5:C15"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="F5:H15"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="K5:L16"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="I3:J3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="7.21875" style="140" customWidth="1"/>
+    <col min="3" max="3" width="8.44140625" style="140" customWidth="1"/>
+    <col min="4" max="4" width="9.88671875" style="140" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" style="140" customWidth="1"/>
+    <col min="6" max="6" width="7.109375" style="140" customWidth="1"/>
+    <col min="7" max="7" width="7.6640625" style="140" customWidth="1"/>
+    <col min="8" max="8" width="4.5546875" style="140" customWidth="1"/>
+    <col min="9" max="9" width="11.6640625" style="140" customWidth="1"/>
+    <col min="10" max="10" width="15.44140625" style="140" customWidth="1"/>
+    <col min="11" max="11" width="7.5546875" style="140" customWidth="1"/>
+    <col min="12" max="12" width="9" style="140" customWidth="1"/>
+    <col min="13" max="16384" width="8.88671875" style="140"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="161" t="s">
+        <v>175</v>
+      </c>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="162"/>
+      <c r="G1" s="162"/>
+      <c r="H1" s="162"/>
+      <c r="I1" s="162"/>
+      <c r="J1" s="162"/>
+      <c r="K1" s="162"/>
+      <c r="L1" s="162"/>
+    </row>
+    <row r="2" spans="1:12" s="153" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="141" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="156" t="s">
+        <v>205</v>
+      </c>
+      <c r="C2" s="163" t="s">
+        <v>176</v>
+      </c>
+      <c r="D2" s="164"/>
+      <c r="E2" s="164"/>
+      <c r="F2" s="164"/>
+      <c r="G2" s="164"/>
+      <c r="H2" s="165"/>
+      <c r="I2" s="166" t="s">
+        <v>177</v>
+      </c>
+      <c r="J2" s="167"/>
+      <c r="K2" s="142" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" s="152" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="143">
+        <v>1</v>
+      </c>
+      <c r="B3" s="157">
+        <v>214</v>
+      </c>
+      <c r="C3" s="168" t="s">
+        <v>204</v>
+      </c>
+      <c r="D3" s="169"/>
+      <c r="E3" s="169"/>
+      <c r="F3" s="169"/>
+      <c r="G3" s="169"/>
+      <c r="H3" s="170"/>
+      <c r="I3" s="171" t="s">
+        <v>206</v>
+      </c>
+      <c r="J3" s="172"/>
+      <c r="K3" s="143" t="s">
+        <v>82</v>
+      </c>
+      <c r="L3" s="144">
+        <f>B9</f>
+        <v>458.76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="160"/>
+      <c r="B4" s="160"/>
+      <c r="C4" s="160"/>
+      <c r="D4" s="160"/>
+      <c r="E4" s="160"/>
+      <c r="F4" s="160"/>
+      <c r="G4" s="160"/>
+      <c r="H4" s="160"/>
+      <c r="I4" s="160"/>
+      <c r="J4" s="160"/>
+      <c r="K4" s="160"/>
+      <c r="L4" s="160"/>
+    </row>
+    <row r="5" spans="1:12" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="145" t="s">
+        <v>203</v>
+      </c>
+      <c r="B5" s="145" t="s">
+        <v>179</v>
+      </c>
+      <c r="C5" s="173"/>
+      <c r="D5" s="173"/>
+      <c r="E5" s="173"/>
+      <c r="F5" s="173"/>
+      <c r="G5" s="173"/>
+      <c r="H5" s="173"/>
+      <c r="I5" s="173"/>
+      <c r="J5" s="173"/>
+      <c r="K5" s="173"/>
+      <c r="L5" s="173"/>
+    </row>
+    <row r="6" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="159">
+        <v>1</v>
+      </c>
+      <c r="B6" s="150">
+        <f>4*40.94</f>
+        <v>163.76</v>
+      </c>
+      <c r="C6" s="173"/>
+      <c r="D6" s="173"/>
+      <c r="E6" s="173"/>
+      <c r="F6" s="173"/>
+      <c r="G6" s="173"/>
+      <c r="H6" s="173"/>
+      <c r="I6" s="173"/>
+      <c r="J6" s="173"/>
+      <c r="K6" s="173"/>
+      <c r="L6" s="173"/>
+    </row>
+    <row r="7" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="158">
+        <v>2</v>
+      </c>
+      <c r="B7" s="149">
+        <f>4*42</f>
+        <v>168</v>
+      </c>
+      <c r="C7" s="173"/>
+      <c r="D7" s="173"/>
+      <c r="E7" s="173"/>
+      <c r="F7" s="173"/>
+      <c r="G7" s="173"/>
+      <c r="H7" s="173"/>
+      <c r="I7" s="173"/>
+      <c r="J7" s="173"/>
+      <c r="K7" s="173"/>
+      <c r="L7" s="173"/>
+    </row>
+    <row r="8" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="158">
+        <v>3</v>
+      </c>
+      <c r="B8" s="149">
+        <f>4*31.75</f>
+        <v>127</v>
+      </c>
+      <c r="C8" s="173"/>
+      <c r="D8" s="173"/>
+      <c r="E8" s="173"/>
+      <c r="F8" s="173"/>
+      <c r="G8" s="173"/>
+      <c r="H8" s="173"/>
+      <c r="I8" s="173"/>
+      <c r="J8" s="173"/>
+      <c r="K8" s="173"/>
+      <c r="L8" s="173"/>
+    </row>
+    <row r="9" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="151">
+        <f>SUM(B6:B8)</f>
+        <v>458.76</v>
+      </c>
+      <c r="C9" s="173"/>
+      <c r="D9" s="173"/>
+      <c r="E9" s="173"/>
+      <c r="F9" s="173"/>
+      <c r="G9" s="173"/>
+      <c r="H9" s="173"/>
+      <c r="I9" s="173"/>
+      <c r="J9" s="173"/>
+      <c r="K9" s="173"/>
+      <c r="L9" s="173"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="C5:L9"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="A4:L4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8001,36 +9312,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="155" t="s">
+      <c r="A1" s="161" t="s">
         <v>175</v>
       </c>
-      <c r="B1" s="156"/>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
-      <c r="E1" s="156"/>
-      <c r="F1" s="156"/>
-      <c r="G1" s="156"/>
-      <c r="H1" s="156"/>
-      <c r="I1" s="156"/>
-      <c r="J1" s="156"/>
-      <c r="K1" s="156"/>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="162"/>
+      <c r="G1" s="162"/>
+      <c r="H1" s="162"/>
+      <c r="I1" s="162"/>
+      <c r="J1" s="162"/>
+      <c r="K1" s="162"/>
     </row>
     <row r="2" spans="1:11" s="153" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A2" s="141" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="157" t="s">
+      <c r="B2" s="163" t="s">
         <v>176</v>
       </c>
-      <c r="C2" s="158"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="159"/>
-      <c r="H2" s="160" t="s">
+      <c r="C2" s="164"/>
+      <c r="D2" s="164"/>
+      <c r="E2" s="164"/>
+      <c r="F2" s="164"/>
+      <c r="G2" s="165"/>
+      <c r="H2" s="166" t="s">
         <v>177</v>
       </c>
-      <c r="I2" s="161"/>
+      <c r="I2" s="167"/>
       <c r="J2" s="142" t="s">
         <v>15</v>
       </c>
@@ -8042,18 +9353,18 @@
       <c r="A3" s="143">
         <v>1</v>
       </c>
-      <c r="B3" s="162" t="s">
+      <c r="B3" s="168" t="s">
         <v>201</v>
       </c>
-      <c r="C3" s="163"/>
-      <c r="D3" s="163"/>
-      <c r="E3" s="163"/>
-      <c r="F3" s="163"/>
-      <c r="G3" s="164"/>
-      <c r="H3" s="165" t="s">
+      <c r="C3" s="169"/>
+      <c r="D3" s="169"/>
+      <c r="E3" s="169"/>
+      <c r="F3" s="169"/>
+      <c r="G3" s="170"/>
+      <c r="H3" s="171" t="s">
         <v>202</v>
       </c>
-      <c r="I3" s="166"/>
+      <c r="I3" s="172"/>
       <c r="J3" s="143" t="s">
         <v>82</v>
       </c>
@@ -8063,17 +9374,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="167"/>
-      <c r="B4" s="167"/>
-      <c r="C4" s="167"/>
-      <c r="D4" s="167"/>
-      <c r="E4" s="167"/>
-      <c r="F4" s="167"/>
-      <c r="G4" s="167"/>
-      <c r="H4" s="167"/>
-      <c r="I4" s="167"/>
-      <c r="J4" s="167"/>
-      <c r="K4" s="167"/>
+      <c r="A4" s="160"/>
+      <c r="B4" s="160"/>
+      <c r="C4" s="160"/>
+      <c r="D4" s="160"/>
+      <c r="E4" s="160"/>
+      <c r="F4" s="160"/>
+      <c r="G4" s="160"/>
+      <c r="H4" s="160"/>
+      <c r="I4" s="160"/>
+      <c r="J4" s="160"/>
+      <c r="K4" s="160"/>
     </row>
     <row r="5" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="145" t="s">
@@ -8082,15 +9393,15 @@
       <c r="B5" s="145" t="s">
         <v>179</v>
       </c>
-      <c r="C5" s="154"/>
-      <c r="D5" s="154"/>
-      <c r="E5" s="154"/>
-      <c r="F5" s="154"/>
-      <c r="G5" s="154"/>
-      <c r="H5" s="154"/>
-      <c r="I5" s="154"/>
-      <c r="J5" s="154"/>
-      <c r="K5" s="154"/>
+      <c r="C5" s="173"/>
+      <c r="D5" s="173"/>
+      <c r="E5" s="173"/>
+      <c r="F5" s="173"/>
+      <c r="G5" s="173"/>
+      <c r="H5" s="173"/>
+      <c r="I5" s="173"/>
+      <c r="J5" s="173"/>
+      <c r="K5" s="173"/>
     </row>
     <row r="6" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="146">
@@ -8100,15 +9411,15 @@
         <f>10.47*3.9-1.72*3.9+1.72*0.8+1.99*3.9</f>
         <v>43.262</v>
       </c>
-      <c r="C6" s="154"/>
-      <c r="D6" s="154"/>
-      <c r="E6" s="154"/>
-      <c r="F6" s="154"/>
-      <c r="G6" s="154"/>
-      <c r="H6" s="154"/>
-      <c r="I6" s="154"/>
-      <c r="J6" s="154"/>
-      <c r="K6" s="154"/>
+      <c r="C6" s="173"/>
+      <c r="D6" s="173"/>
+      <c r="E6" s="173"/>
+      <c r="F6" s="173"/>
+      <c r="G6" s="173"/>
+      <c r="H6" s="173"/>
+      <c r="I6" s="173"/>
+      <c r="J6" s="173"/>
+      <c r="K6" s="173"/>
     </row>
     <row r="7" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="147">
@@ -8118,15 +9429,15 @@
         <f>10.37*3.9-1.72*3.9+1.72*0.8+1.99*3.9</f>
         <v>42.872</v>
       </c>
-      <c r="C7" s="154"/>
-      <c r="D7" s="154"/>
-      <c r="E7" s="154"/>
-      <c r="F7" s="154"/>
-      <c r="G7" s="154"/>
-      <c r="H7" s="154"/>
-      <c r="I7" s="154"/>
-      <c r="J7" s="154"/>
-      <c r="K7" s="154"/>
+      <c r="C7" s="173"/>
+      <c r="D7" s="173"/>
+      <c r="E7" s="173"/>
+      <c r="F7" s="173"/>
+      <c r="G7" s="173"/>
+      <c r="H7" s="173"/>
+      <c r="I7" s="173"/>
+      <c r="J7" s="173"/>
+      <c r="K7" s="173"/>
     </row>
     <row r="8" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="146">
@@ -8136,33 +9447,33 @@
         <f>10.1*3.9-1.72*3.9+1.72*0.8+1.99*3.9</f>
         <v>41.819000000000003</v>
       </c>
-      <c r="C8" s="154"/>
-      <c r="D8" s="154"/>
-      <c r="E8" s="154"/>
-      <c r="F8" s="154"/>
-      <c r="G8" s="154"/>
-      <c r="H8" s="154"/>
-      <c r="I8" s="154"/>
-      <c r="J8" s="154"/>
-      <c r="K8" s="154"/>
+      <c r="C8" s="173"/>
+      <c r="D8" s="173"/>
+      <c r="E8" s="173"/>
+      <c r="F8" s="173"/>
+      <c r="G8" s="173"/>
+      <c r="H8" s="173"/>
+      <c r="I8" s="173"/>
+      <c r="J8" s="173"/>
+      <c r="K8" s="173"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="172" t="s">
+      <c r="A9" s="154" t="s">
         <v>165</v>
       </c>
-      <c r="B9" s="173">
+      <c r="B9" s="155">
         <f>SUM(B6:B8)</f>
         <v>127.953</v>
       </c>
-      <c r="C9" s="154"/>
-      <c r="D9" s="154"/>
-      <c r="E9" s="154"/>
-      <c r="F9" s="154"/>
-      <c r="G9" s="154"/>
-      <c r="H9" s="154"/>
-      <c r="I9" s="154"/>
-      <c r="J9" s="154"/>
-      <c r="K9" s="154"/>
+      <c r="C9" s="173"/>
+      <c r="D9" s="173"/>
+      <c r="E9" s="173"/>
+      <c r="F9" s="173"/>
+      <c r="G9" s="173"/>
+      <c r="H9" s="173"/>
+      <c r="I9" s="173"/>
+      <c r="J9" s="173"/>
+      <c r="K9" s="173"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -8179,7 +9490,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8199,36 +9510,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="155" t="s">
+      <c r="A1" s="161" t="s">
         <v>175</v>
       </c>
-      <c r="B1" s="156"/>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
-      <c r="E1" s="156"/>
-      <c r="F1" s="156"/>
-      <c r="G1" s="156"/>
-      <c r="H1" s="156"/>
-      <c r="I1" s="156"/>
-      <c r="J1" s="156"/>
-      <c r="K1" s="156"/>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="162"/>
+      <c r="G1" s="162"/>
+      <c r="H1" s="162"/>
+      <c r="I1" s="162"/>
+      <c r="J1" s="162"/>
+      <c r="K1" s="162"/>
     </row>
     <row r="2" spans="1:11" s="153" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A2" s="141" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="157" t="s">
+      <c r="B2" s="163" t="s">
         <v>176</v>
       </c>
-      <c r="C2" s="158"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="159"/>
-      <c r="H2" s="160" t="s">
+      <c r="C2" s="164"/>
+      <c r="D2" s="164"/>
+      <c r="E2" s="164"/>
+      <c r="F2" s="164"/>
+      <c r="G2" s="165"/>
+      <c r="H2" s="166" t="s">
         <v>177</v>
       </c>
-      <c r="I2" s="161"/>
+      <c r="I2" s="167"/>
       <c r="J2" s="142" t="s">
         <v>15</v>
       </c>
@@ -8240,18 +9551,18 @@
       <c r="A3" s="143">
         <v>1</v>
       </c>
-      <c r="B3" s="162" t="s">
+      <c r="B3" s="168" t="s">
         <v>189</v>
       </c>
-      <c r="C3" s="163"/>
-      <c r="D3" s="163"/>
-      <c r="E3" s="163"/>
-      <c r="F3" s="163"/>
-      <c r="G3" s="164"/>
-      <c r="H3" s="165" t="s">
+      <c r="C3" s="169"/>
+      <c r="D3" s="169"/>
+      <c r="E3" s="169"/>
+      <c r="F3" s="169"/>
+      <c r="G3" s="170"/>
+      <c r="H3" s="171" t="s">
         <v>190</v>
       </c>
-      <c r="I3" s="166"/>
+      <c r="I3" s="172"/>
       <c r="J3" s="143" t="s">
         <v>82</v>
       </c>
@@ -8261,17 +9572,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="167"/>
-      <c r="B4" s="167"/>
-      <c r="C4" s="167"/>
-      <c r="D4" s="167"/>
-      <c r="E4" s="167"/>
-      <c r="F4" s="167"/>
-      <c r="G4" s="167"/>
-      <c r="H4" s="167"/>
-      <c r="I4" s="167"/>
-      <c r="J4" s="167"/>
-      <c r="K4" s="167"/>
+      <c r="A4" s="160"/>
+      <c r="B4" s="160"/>
+      <c r="C4" s="160"/>
+      <c r="D4" s="160"/>
+      <c r="E4" s="160"/>
+      <c r="F4" s="160"/>
+      <c r="G4" s="160"/>
+      <c r="H4" s="160"/>
+      <c r="I4" s="160"/>
+      <c r="J4" s="160"/>
+      <c r="K4" s="160"/>
     </row>
     <row r="5" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="145" t="s">
@@ -8283,14 +9594,14 @@
       <c r="C5" s="145" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="154"/>
-      <c r="E5" s="154"/>
-      <c r="F5" s="154"/>
-      <c r="G5" s="154"/>
-      <c r="H5" s="154"/>
-      <c r="I5" s="154"/>
-      <c r="J5" s="154"/>
-      <c r="K5" s="154"/>
+      <c r="D5" s="173"/>
+      <c r="E5" s="173"/>
+      <c r="F5" s="173"/>
+      <c r="G5" s="173"/>
+      <c r="H5" s="173"/>
+      <c r="I5" s="173"/>
+      <c r="J5" s="173"/>
+      <c r="K5" s="173"/>
     </row>
     <row r="6" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="146" t="s">
@@ -8302,14 +9613,14 @@
       <c r="C6" s="149">
         <v>590.38850000000002</v>
       </c>
-      <c r="D6" s="154"/>
-      <c r="E6" s="154"/>
-      <c r="F6" s="154"/>
-      <c r="G6" s="154"/>
-      <c r="H6" s="154"/>
-      <c r="I6" s="154"/>
-      <c r="J6" s="154"/>
-      <c r="K6" s="154"/>
+      <c r="D6" s="173"/>
+      <c r="E6" s="173"/>
+      <c r="F6" s="173"/>
+      <c r="G6" s="173"/>
+      <c r="H6" s="173"/>
+      <c r="I6" s="173"/>
+      <c r="J6" s="173"/>
+      <c r="K6" s="173"/>
     </row>
     <row r="7" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="147" t="s">
@@ -8321,14 +9632,14 @@
       <c r="C7" s="150">
         <v>141.96</v>
       </c>
-      <c r="D7" s="154"/>
-      <c r="E7" s="154"/>
-      <c r="F7" s="154"/>
-      <c r="G7" s="154"/>
-      <c r="H7" s="154"/>
-      <c r="I7" s="154"/>
-      <c r="J7" s="154"/>
-      <c r="K7" s="154"/>
+      <c r="D7" s="173"/>
+      <c r="E7" s="173"/>
+      <c r="F7" s="173"/>
+      <c r="G7" s="173"/>
+      <c r="H7" s="173"/>
+      <c r="I7" s="173"/>
+      <c r="J7" s="173"/>
+      <c r="K7" s="173"/>
     </row>
     <row r="8" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="146" t="s">
@@ -8340,14 +9651,14 @@
       <c r="C8" s="149">
         <v>610.49</v>
       </c>
-      <c r="D8" s="154"/>
-      <c r="E8" s="154"/>
-      <c r="F8" s="154"/>
-      <c r="G8" s="154"/>
-      <c r="H8" s="154"/>
-      <c r="I8" s="154"/>
-      <c r="J8" s="154"/>
-      <c r="K8" s="154"/>
+      <c r="D8" s="173"/>
+      <c r="E8" s="173"/>
+      <c r="F8" s="173"/>
+      <c r="G8" s="173"/>
+      <c r="H8" s="173"/>
+      <c r="I8" s="173"/>
+      <c r="J8" s="173"/>
+      <c r="K8" s="173"/>
     </row>
     <row r="9" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="147" t="s">
@@ -8359,14 +9670,14 @@
       <c r="C9" s="150">
         <v>736.31050000000005</v>
       </c>
-      <c r="D9" s="154"/>
-      <c r="E9" s="154"/>
-      <c r="F9" s="154"/>
-      <c r="G9" s="154"/>
-      <c r="H9" s="154"/>
-      <c r="I9" s="154"/>
-      <c r="J9" s="154"/>
-      <c r="K9" s="154"/>
+      <c r="D9" s="173"/>
+      <c r="E9" s="173"/>
+      <c r="F9" s="173"/>
+      <c r="G9" s="173"/>
+      <c r="H9" s="173"/>
+      <c r="I9" s="173"/>
+      <c r="J9" s="173"/>
+      <c r="K9" s="173"/>
     </row>
     <row r="10" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="146" t="s">
@@ -8378,14 +9689,14 @@
       <c r="C10" s="149">
         <v>184.6</v>
       </c>
-      <c r="D10" s="154"/>
-      <c r="E10" s="154"/>
-      <c r="F10" s="154"/>
-      <c r="G10" s="154"/>
-      <c r="H10" s="154"/>
-      <c r="I10" s="154"/>
-      <c r="J10" s="154"/>
-      <c r="K10" s="154"/>
+      <c r="D10" s="173"/>
+      <c r="E10" s="173"/>
+      <c r="F10" s="173"/>
+      <c r="G10" s="173"/>
+      <c r="H10" s="173"/>
+      <c r="I10" s="173"/>
+      <c r="J10" s="173"/>
+      <c r="K10" s="173"/>
     </row>
     <row r="11" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="147" t="s">
@@ -8397,14 +9708,14 @@
       <c r="C11" s="150">
         <v>714.72</v>
       </c>
-      <c r="D11" s="154"/>
-      <c r="E11" s="154"/>
-      <c r="F11" s="154"/>
-      <c r="G11" s="154"/>
-      <c r="H11" s="154"/>
-      <c r="I11" s="154"/>
-      <c r="J11" s="154"/>
-      <c r="K11" s="154"/>
+      <c r="D11" s="173"/>
+      <c r="E11" s="173"/>
+      <c r="F11" s="173"/>
+      <c r="G11" s="173"/>
+      <c r="H11" s="173"/>
+      <c r="I11" s="173"/>
+      <c r="J11" s="173"/>
+      <c r="K11" s="173"/>
     </row>
     <row r="12" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="146" t="s">
@@ -8416,14 +9727,14 @@
       <c r="C12" s="149">
         <v>94.2</v>
       </c>
-      <c r="D12" s="154"/>
-      <c r="E12" s="154"/>
-      <c r="F12" s="154"/>
-      <c r="G12" s="154"/>
-      <c r="H12" s="154"/>
-      <c r="I12" s="154"/>
-      <c r="J12" s="154"/>
-      <c r="K12" s="154"/>
+      <c r="D12" s="173"/>
+      <c r="E12" s="173"/>
+      <c r="F12" s="173"/>
+      <c r="G12" s="173"/>
+      <c r="H12" s="173"/>
+      <c r="I12" s="173"/>
+      <c r="J12" s="173"/>
+      <c r="K12" s="173"/>
     </row>
     <row r="13" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="147" t="s">
@@ -8435,14 +9746,14 @@
       <c r="C13" s="150">
         <v>42.8</v>
       </c>
-      <c r="D13" s="154"/>
-      <c r="E13" s="154"/>
-      <c r="F13" s="154"/>
-      <c r="G13" s="154"/>
-      <c r="H13" s="154"/>
-      <c r="I13" s="154"/>
-      <c r="J13" s="154"/>
-      <c r="K13" s="154"/>
+      <c r="D13" s="173"/>
+      <c r="E13" s="173"/>
+      <c r="F13" s="173"/>
+      <c r="G13" s="173"/>
+      <c r="H13" s="173"/>
+      <c r="I13" s="173"/>
+      <c r="J13" s="173"/>
+      <c r="K13" s="173"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="146" t="s">
@@ -8454,14 +9765,14 @@
       <c r="C14" s="149">
         <v>52.4</v>
       </c>
-      <c r="D14" s="154"/>
-      <c r="E14" s="154"/>
-      <c r="F14" s="154"/>
-      <c r="G14" s="154"/>
-      <c r="H14" s="154"/>
-      <c r="I14" s="154"/>
-      <c r="J14" s="154"/>
-      <c r="K14" s="154"/>
+      <c r="D14" s="173"/>
+      <c r="E14" s="173"/>
+      <c r="F14" s="173"/>
+      <c r="G14" s="173"/>
+      <c r="H14" s="173"/>
+      <c r="I14" s="173"/>
+      <c r="J14" s="173"/>
+      <c r="K14" s="173"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B15" s="148" t="s">
@@ -8471,14 +9782,14 @@
         <f>SUM(C6:C14)</f>
         <v>3167.8690000000001</v>
       </c>
-      <c r="D15" s="154"/>
-      <c r="E15" s="154"/>
-      <c r="F15" s="154"/>
-      <c r="G15" s="154"/>
-      <c r="H15" s="154"/>
-      <c r="I15" s="154"/>
-      <c r="J15" s="154"/>
-      <c r="K15" s="154"/>
+      <c r="D15" s="173"/>
+      <c r="E15" s="173"/>
+      <c r="F15" s="173"/>
+      <c r="G15" s="173"/>
+      <c r="H15" s="173"/>
+      <c r="I15" s="173"/>
+      <c r="J15" s="173"/>
+      <c r="K15" s="173"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -8495,7 +9806,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -8519,26 +9830,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="168" t="s">
+      <c r="A1" s="175" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="168"/>
+      <c r="B1" s="175"/>
+      <c r="C1" s="175"/>
+      <c r="D1" s="175"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="175"/>
+      <c r="G1" s="175"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="169" t="s">
+      <c r="A2" s="176" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="169"/>
-      <c r="C2" s="169"/>
-      <c r="D2" s="169"/>
-      <c r="E2" s="169"/>
-      <c r="F2" s="169"/>
-      <c r="G2" s="169"/>
+      <c r="B2" s="176"/>
+      <c r="C2" s="176"/>
+      <c r="D2" s="176"/>
+      <c r="E2" s="176"/>
+      <c r="F2" s="176"/>
+      <c r="G2" s="176"/>
     </row>
     <row r="3" spans="1:16" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
@@ -10115,7 +11426,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
@@ -10593,7 +11904,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
@@ -10623,26 +11934,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A1" s="168" t="s">
+      <c r="A1" s="175" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="168"/>
+      <c r="B1" s="175"/>
+      <c r="C1" s="175"/>
+      <c r="D1" s="175"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="175"/>
+      <c r="G1" s="175"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A2" s="169" t="s">
+      <c r="A2" s="176" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="169"/>
-      <c r="C2" s="169"/>
-      <c r="D2" s="169"/>
-      <c r="E2" s="169"/>
-      <c r="F2" s="169"/>
-      <c r="G2" s="169"/>
+      <c r="B2" s="176"/>
+      <c r="C2" s="176"/>
+      <c r="D2" s="176"/>
+      <c r="E2" s="176"/>
+      <c r="F2" s="176"/>
+      <c r="G2" s="176"/>
       <c r="O2" s="39"/>
       <c r="Q2" s="41"/>
     </row>
@@ -12356,7 +13667,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="5" tint="0.79998168889431442"/>
@@ -12831,654 +14142,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor theme="5" tint="0.79998168889431442"/>
-  </sheetPr>
-  <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="7" style="10" customWidth="1"/>
-    <col min="2" max="2" width="11.109375" style="10" customWidth="1"/>
-    <col min="3" max="6" width="8.6640625" style="10" customWidth="1"/>
-    <col min="7" max="7" width="8.6640625" style="27" customWidth="1"/>
-    <col min="8" max="16384" width="9.109375" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="168" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="168"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="169" t="s">
-        <v>64</v>
-      </c>
-      <c r="B2" s="169"/>
-      <c r="C2" s="169"/>
-      <c r="D2" s="169"/>
-      <c r="E2" s="169"/>
-      <c r="F2" s="169"/>
-      <c r="G2" s="169"/>
-    </row>
-    <row r="3" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A3" s="72"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" s="73" t="s">
-        <v>69</v>
-      </c>
-      <c r="E3" s="73" t="s">
-        <v>68</v>
-      </c>
-      <c r="F3" s="73" t="s">
-        <v>67</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="72" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4" s="25" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="72">
-        <v>1</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25">
-        <v>75.790000000000006</v>
-      </c>
-      <c r="G5" s="25">
-        <f>SUM(C5:F5)</f>
-        <v>75.790000000000006</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="74">
-        <v>2</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25">
-        <v>93.93</v>
-      </c>
-      <c r="G6" s="25">
-        <f t="shared" ref="G6:G21" si="0">SUM(C6:F6)</f>
-        <v>93.93</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="74">
-        <v>3</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25">
-        <v>34.979999999999997</v>
-      </c>
-      <c r="G7" s="25">
-        <f t="shared" si="0"/>
-        <v>34.979999999999997</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="74">
-        <v>4</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25">
-        <v>20.85</v>
-      </c>
-      <c r="G8" s="25">
-        <f t="shared" si="0"/>
-        <v>20.85</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="74">
-        <v>5</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25">
-        <v>38.89</v>
-      </c>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25">
-        <f t="shared" si="0"/>
-        <v>38.89</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="74">
-        <v>6</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="C10" s="25">
-        <v>1.89</v>
-      </c>
-      <c r="D10" s="25">
-        <v>83.51</v>
-      </c>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25">
-        <f t="shared" si="0"/>
-        <v>85.4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="74">
-        <v>7</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="C11" s="25">
-        <v>1.63</v>
-      </c>
-      <c r="D11" s="25">
-        <v>87.22</v>
-      </c>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25">
-        <f t="shared" si="0"/>
-        <v>88.85</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="74">
-        <v>8</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="C12" s="25">
-        <v>66.650000000000006</v>
-      </c>
-      <c r="D12" s="25">
-        <v>161.4</v>
-      </c>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25">
-        <f t="shared" si="0"/>
-        <v>228.05</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="74">
-        <v>9</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="C13" s="25">
-        <v>69.88</v>
-      </c>
-      <c r="D13" s="25">
-        <v>357.36</v>
-      </c>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25">
-        <f t="shared" si="0"/>
-        <v>427.24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="74">
-        <v>10</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="C14" s="25">
-        <v>36.6</v>
-      </c>
-      <c r="D14" s="25">
-        <v>41.25</v>
-      </c>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25">
-        <f t="shared" si="0"/>
-        <v>77.849999999999994</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="74">
-        <v>11</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="C15" s="25">
-        <v>32.200000000000003</v>
-      </c>
-      <c r="D15" s="25">
-        <v>287.72000000000003</v>
-      </c>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25">
-        <f t="shared" si="0"/>
-        <v>319.92</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="74">
-        <v>12</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="C16" s="25">
-        <v>1.02</v>
-      </c>
-      <c r="D16" s="25">
-        <v>82.31</v>
-      </c>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25">
-        <f t="shared" si="0"/>
-        <v>83.33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="74">
-        <v>13</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25">
-        <v>28.81</v>
-      </c>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25">
-        <f t="shared" si="0"/>
-        <v>28.81</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="74">
-        <v>14</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25">
-        <v>28.19</v>
-      </c>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25">
-        <f t="shared" si="0"/>
-        <v>28.19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="74">
-        <v>15</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25">
-        <v>28.36</v>
-      </c>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25">
-        <f t="shared" si="0"/>
-        <v>28.36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="74">
-        <v>16</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="C20" s="25">
-        <v>24.7</v>
-      </c>
-      <c r="D20" s="25">
-        <v>53.51</v>
-      </c>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25">
-        <f t="shared" si="0"/>
-        <v>78.209999999999994</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="74">
-        <v>17</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="C21" s="25">
-        <v>1.02</v>
-      </c>
-      <c r="D21" s="25">
-        <v>53.79</v>
-      </c>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25">
-        <f t="shared" si="0"/>
-        <v>54.81</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="72"/>
-      <c r="B22" s="72" t="s">
-        <v>19</v>
-      </c>
-      <c r="C22" s="25">
-        <f>SUM(C5:C21)</f>
-        <v>235.59000000000003</v>
-      </c>
-      <c r="D22" s="25">
-        <f>SUM(D5:D21)</f>
-        <v>1208.07</v>
-      </c>
-      <c r="E22" s="25">
-        <f>SUM(E5:E21)</f>
-        <v>124.25</v>
-      </c>
-      <c r="F22" s="25">
-        <f>SUM(F5:F21)</f>
-        <v>225.55</v>
-      </c>
-      <c r="G22" s="25">
-        <f>SUM(G5:G21)</f>
-        <v>1793.4599999999998</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C1" t="s">
-        <v>142</v>
-      </c>
-      <c r="D1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="76">
-        <v>544.88</v>
-      </c>
-      <c r="C2" s="76">
-        <v>528.22</v>
-      </c>
-      <c r="D2" s="76">
-        <v>563.80999999999995</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="B4" s="76">
-        <v>492.07</v>
-      </c>
-      <c r="C4" s="76">
-        <v>542.94000000000005</v>
-      </c>
-      <c r="D4" s="76">
-        <v>303.39999999999998</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B5" s="77">
-        <f>B4+B2</f>
-        <v>1036.95</v>
-      </c>
-      <c r="C5" s="77">
-        <f>C4+C2</f>
-        <v>1071.1600000000001</v>
-      </c>
-      <c r="D5" s="77">
-        <f>D4+D2</f>
-        <v>867.20999999999992</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B6" s="75"/>
-      <c r="C6" s="75"/>
-      <c r="D6" s="75"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>144</v>
-      </c>
-      <c r="B7" s="75">
-        <f>991.77</f>
-        <v>991.77</v>
-      </c>
-      <c r="C7" s="75">
-        <f>'ВОР 2 э. шт.'!E6</f>
-        <v>907.35119999999995</v>
-      </c>
-      <c r="D7" s="75">
-        <f>'ВОР 3 э. шт.'!E6</f>
-        <v>840.60999999999979</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B8" s="75">
-        <f>B5-B7</f>
-        <v>45.180000000000064</v>
-      </c>
-      <c r="C8" s="75">
-        <f t="shared" ref="C8" si="0">C5-C7</f>
-        <v>163.80880000000013</v>
-      </c>
-      <c r="D8" s="75">
-        <f t="shared" ref="D8" si="1">D5-D7</f>
-        <v>26.600000000000136</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>1</v>
-      </c>
-      <c r="B10" s="76">
-        <v>771.83</v>
-      </c>
-      <c r="C10" s="76">
-        <v>972.84</v>
-      </c>
-      <c r="D10" s="76">
-        <v>1176.67</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B11" s="76"/>
-      <c r="C11" s="76"/>
-      <c r="D11" s="76"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="B12" s="76">
-        <v>927.42</v>
-      </c>
-      <c r="C12" s="76">
-        <v>1669.68</v>
-      </c>
-      <c r="D12" s="76">
-        <v>707.8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>129</v>
-      </c>
-      <c r="B13" s="77">
-        <f>B12+B10</f>
-        <v>1699.25</v>
-      </c>
-      <c r="C13" s="77">
-        <f>C12+C10</f>
-        <v>2642.52</v>
-      </c>
-      <c r="D13" s="77">
-        <f>D12+D10</f>
-        <v>1884.47</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>144</v>
-      </c>
-      <c r="B15">
-        <f>1615</f>
-        <v>1615</v>
-      </c>
-      <c r="C15" s="75">
-        <f>'ВОР 2 э. шт.'!E21</f>
-        <v>1761.3287999999998</v>
-      </c>
-      <c r="D15" s="75">
-        <f>'ВОР 3 э. шт.'!E21</f>
-        <v>1864.9899999999998</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B16" s="75">
-        <f>B13-B15</f>
-        <v>84.25</v>
-      </c>
-      <c r="C16" s="75">
-        <f t="shared" ref="C16:D16" si="2">C13-C15</f>
-        <v>881.19120000000021</v>
-      </c>
-      <c r="D16" s="75">
-        <f t="shared" si="2"/>
-        <v>19.480000000000246</v>
-      </c>
-    </row>
-    <row r="21" spans="3:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="22" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C22" s="55">
-        <f>(1432.33)/100 * 71</f>
-        <v>1016.9543</v>
-      </c>
-      <c r="D22" s="55">
-        <f>(2736)/100 * 71</f>
-        <v>1942.56</v>
-      </c>
-      <c r="E22" s="75">
-        <f>3617-D22-C22</f>
-        <v>657.48570000000007</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>